--- a/data/final_tables /Table_S2.xlsx
+++ b/data/final_tables /Table_S2.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anthonyfuentes/Desktop/Submission/data/geochronology/final_tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anthonyfuentes/GitHub/Sed_Hematite_UPb/data/final_tables /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28340C4D-5931-5645-BCD2-5C69ACD2BA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3828BC1A-60B9-CA4A-BB2A-1D36775AD7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{983A3024-F279-4749-8013-AF771CBD574B}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{983A3024-F279-4749-8013-AF771CBD574B}"/>
   </bookViews>
   <sheets>
     <sheet name="U_Pb_data" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">U_Pb_data!$A$1:$R$261</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1763,7 +1766,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1828,25 +1831,10 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -5038,7 +5026,7 @@
         <v>0.53870587999999997</v>
       </c>
     </row>
-    <row r="79" spans="1:12" s="28" customFormat="1">
+    <row r="79" spans="1:12">
       <c r="A79" s="19" t="s">
         <v>74</v>
       </c>
@@ -5093,37 +5081,37 @@
       <c r="L80" s="8"/>
     </row>
     <row r="81" spans="1:12">
-      <c r="A81" s="22" t="s">
+      <c r="A81" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="B81" s="22" t="s">
+      <c r="B81" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C81" s="23">
+      <c r="C81" s="22">
         <v>7.6546751119989498</v>
       </c>
-      <c r="D81" s="23">
+      <c r="D81" s="22">
         <v>0.30117055577917901</v>
       </c>
-      <c r="E81" s="24">
+      <c r="E81" s="14">
         <v>0.13343742774568201</v>
       </c>
-      <c r="F81" s="24">
+      <c r="F81" s="14">
         <v>4.7399023135022804E-3</v>
       </c>
-      <c r="G81" s="24">
+      <c r="G81" s="14">
         <v>1.4248285317845699</v>
       </c>
-      <c r="H81" s="24">
+      <c r="H81" s="14">
         <v>9.3508133911208102E-2</v>
       </c>
-      <c r="I81" s="25">
+      <c r="I81" s="23">
         <v>7.8157563504278105E-2</v>
       </c>
-      <c r="J81" s="25">
+      <c r="J81" s="23">
         <v>5.1440510054855497E-3</v>
       </c>
-      <c r="K81" s="24">
+      <c r="K81" s="14">
         <v>0.35204370370742599</v>
       </c>
       <c r="L81" s="15">
@@ -5131,37 +5119,37 @@
       </c>
     </row>
     <row r="82" spans="1:12">
-      <c r="A82" s="22" t="s">
+      <c r="A82" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="B82" s="22" t="s">
+      <c r="B82" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C82" s="23">
+      <c r="C82" s="22">
         <v>7.70956339751916</v>
       </c>
-      <c r="D82" s="23">
+      <c r="D82" s="22">
         <v>0.29547427319708702</v>
       </c>
-      <c r="E82" s="24">
+      <c r="E82" s="14">
         <v>0.13269210579551299</v>
       </c>
-      <c r="F82" s="24">
+      <c r="F82" s="14">
         <v>4.5782882618740604E-3</v>
       </c>
-      <c r="G82" s="24">
+      <c r="G82" s="14">
         <v>1.3869574448539299</v>
       </c>
-      <c r="H82" s="24">
+      <c r="H82" s="14">
         <v>0.10073615320894901</v>
       </c>
-      <c r="I82" s="25">
+      <c r="I82" s="23">
         <v>7.5063456490199507E-2</v>
       </c>
-      <c r="J82" s="25">
+      <c r="J82" s="23">
         <v>5.4553015262768503E-3</v>
       </c>
-      <c r="K82" s="24">
+      <c r="K82" s="14">
         <v>0.38324470299628699</v>
       </c>
       <c r="L82" s="15">
@@ -5169,37 +5157,37 @@
       </c>
     </row>
     <row r="83" spans="1:12">
-      <c r="A83" s="22" t="s">
+      <c r="A83" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="B83" s="22" t="s">
+      <c r="B83" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C83" s="23">
+      <c r="C83" s="22">
         <v>7.6864374190485298</v>
       </c>
-      <c r="D83" s="23">
+      <c r="D83" s="22">
         <v>0.36097854829785903</v>
       </c>
-      <c r="E83" s="24">
+      <c r="E83" s="14">
         <v>0.13346365123496101</v>
       </c>
-      <c r="F83" s="24">
+      <c r="F83" s="14">
         <v>5.3332158950688997E-3</v>
       </c>
-      <c r="G83" s="24">
+      <c r="G83" s="14">
         <v>1.3073046266742501</v>
       </c>
-      <c r="H83" s="24">
+      <c r="H83" s="14">
         <v>8.8844817792494493E-2</v>
       </c>
-      <c r="I83" s="25">
+      <c r="I83" s="23">
         <v>7.1964466270158997E-2</v>
       </c>
-      <c r="J83" s="25">
+      <c r="J83" s="23">
         <v>5.2644439615020999E-3</v>
       </c>
-      <c r="K83" s="24">
+      <c r="K83" s="14">
         <v>0.42826221453823499</v>
       </c>
       <c r="L83" s="15">
@@ -5207,37 +5195,37 @@
       </c>
     </row>
     <row r="84" spans="1:12">
-      <c r="A84" s="22" t="s">
+      <c r="A84" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="B84" s="22" t="s">
+      <c r="B84" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C84" s="23">
+      <c r="C84" s="22">
         <v>8.5516800460629394</v>
       </c>
-      <c r="D84" s="23">
+      <c r="D84" s="22">
         <v>0.54256087403942599</v>
       </c>
-      <c r="E84" s="24">
+      <c r="E84" s="14">
         <v>0.12702646179570901</v>
       </c>
-      <c r="F84" s="24">
+      <c r="F84" s="14">
         <v>5.3850848923345102E-3</v>
       </c>
-      <c r="G84" s="24">
+      <c r="G84" s="14">
         <v>1.34032559345192</v>
       </c>
-      <c r="H84" s="24">
+      <c r="H84" s="14">
         <v>9.5906545251278494E-2</v>
       </c>
-      <c r="I84" s="25">
+      <c r="I84" s="23">
         <v>7.6249071600249005E-2</v>
       </c>
-      <c r="J84" s="25">
+      <c r="J84" s="23">
         <v>6.3168931317618901E-3</v>
       </c>
-      <c r="K84" s="24">
+      <c r="K84" s="14">
         <v>0.43152976773694901</v>
       </c>
       <c r="L84" s="15">
@@ -5245,37 +5233,37 @@
       </c>
     </row>
     <row r="85" spans="1:12">
-      <c r="A85" s="22" t="s">
+      <c r="A85" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B85" s="22" t="s">
+      <c r="B85" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C85" s="23">
+      <c r="C85" s="22">
         <v>7.6123588703214402</v>
       </c>
-      <c r="D85" s="23">
+      <c r="D85" s="22">
         <v>0.24895579441902899</v>
       </c>
-      <c r="E85" s="24">
+      <c r="E85" s="14">
         <v>0.13188223533229099</v>
       </c>
-      <c r="F85" s="24">
+      <c r="F85" s="14">
         <v>4.2439096933228502E-3</v>
       </c>
-      <c r="G85" s="24">
+      <c r="G85" s="14">
         <v>1.3154221856267101</v>
       </c>
-      <c r="H85" s="24">
+      <c r="H85" s="14">
         <v>9.3043477606862393E-2</v>
       </c>
-      <c r="I85" s="25">
+      <c r="I85" s="23">
         <v>7.0870291228634197E-2</v>
       </c>
-      <c r="J85" s="25">
+      <c r="J85" s="23">
         <v>4.7579458177908996E-3</v>
       </c>
-      <c r="K85" s="24">
+      <c r="K85" s="14">
         <v>0.33858546102570902</v>
       </c>
       <c r="L85" s="15">
@@ -5283,37 +5271,37 @@
       </c>
     </row>
     <row r="86" spans="1:12">
-      <c r="A86" s="22" t="s">
+      <c r="A86" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="B86" s="22" t="s">
+      <c r="B86" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C86" s="23">
+      <c r="C86" s="22">
         <v>8.0912832386076499</v>
       </c>
-      <c r="D86" s="23">
+      <c r="D86" s="22">
         <v>0.40614031235389803</v>
       </c>
-      <c r="E86" s="24">
+      <c r="E86" s="14">
         <v>0.128727267769633</v>
       </c>
-      <c r="F86" s="24">
+      <c r="F86" s="14">
         <v>5.0697093888452801E-3</v>
       </c>
-      <c r="G86" s="24">
+      <c r="G86" s="14">
         <v>1.3001373378807899</v>
       </c>
-      <c r="H86" s="24">
+      <c r="H86" s="14">
         <v>9.6754213337346504E-2</v>
       </c>
-      <c r="I86" s="25">
+      <c r="I86" s="23">
         <v>7.2680580168510894E-2</v>
       </c>
-      <c r="J86" s="25">
+      <c r="J86" s="23">
         <v>5.49892350259384E-3</v>
       </c>
-      <c r="K86" s="24">
+      <c r="K86" s="14">
         <v>0.43523368200518098</v>
       </c>
       <c r="L86" s="15">
@@ -5321,37 +5309,37 @@
       </c>
     </row>
     <row r="87" spans="1:12">
-      <c r="A87" s="22" t="s">
+      <c r="A87" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="B87" s="22" t="s">
+      <c r="B87" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C87" s="23">
+      <c r="C87" s="22">
         <v>8.0807269726709805</v>
       </c>
-      <c r="D87" s="23">
+      <c r="D87" s="22">
         <v>0.38667760221570002</v>
       </c>
-      <c r="E87" s="24">
+      <c r="E87" s="14">
         <v>0.131971322463834</v>
       </c>
-      <c r="F87" s="24">
+      <c r="F87" s="14">
         <v>5.3202462846382E-3</v>
       </c>
-      <c r="G87" s="24">
+      <c r="G87" s="14">
         <v>1.4648304851412399</v>
       </c>
-      <c r="H87" s="24">
+      <c r="H87" s="14">
         <v>0.103407914226631</v>
       </c>
-      <c r="I87" s="25">
+      <c r="I87" s="23">
         <v>7.9741308467537297E-2</v>
       </c>
-      <c r="J87" s="25">
+      <c r="J87" s="23">
         <v>5.3820914202625499E-3</v>
       </c>
-      <c r="K87" s="24">
+      <c r="K87" s="14">
         <v>0.54608197173808304</v>
       </c>
       <c r="L87" s="15">
@@ -5359,37 +5347,37 @@
       </c>
     </row>
     <row r="88" spans="1:12">
-      <c r="A88" s="22" t="s">
+      <c r="A88" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B88" s="22" t="s">
+      <c r="B88" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C88" s="23">
+      <c r="C88" s="22">
         <v>7.9448447513996898</v>
       </c>
-      <c r="D88" s="23">
+      <c r="D88" s="22">
         <v>0.32819491133839301</v>
       </c>
-      <c r="E88" s="24">
+      <c r="E88" s="14">
         <v>0.13149474620979801</v>
       </c>
-      <c r="F88" s="24">
+      <c r="F88" s="14">
         <v>4.7558075967049198E-3</v>
       </c>
-      <c r="G88" s="24">
+      <c r="G88" s="14">
         <v>1.33742663915864</v>
       </c>
-      <c r="H88" s="24">
+      <c r="H88" s="14">
         <v>9.4545360110868004E-2</v>
       </c>
-      <c r="I88" s="25">
+      <c r="I88" s="23">
         <v>7.1537742676647906E-2</v>
       </c>
-      <c r="J88" s="25">
+      <c r="J88" s="23">
         <v>4.5163952681979E-3</v>
       </c>
-      <c r="K88" s="24">
+      <c r="K88" s="14">
         <v>0.43859748292145301</v>
       </c>
       <c r="L88" s="15">
@@ -5397,37 +5385,37 @@
       </c>
     </row>
     <row r="89" spans="1:12">
-      <c r="A89" s="22" t="s">
+      <c r="A89" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="B89" s="22" t="s">
+      <c r="B89" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C89" s="23">
+      <c r="C89" s="22">
         <v>7.5562161259570297</v>
       </c>
-      <c r="D89" s="23">
+      <c r="D89" s="22">
         <v>0.41188837382599403</v>
       </c>
-      <c r="E89" s="24">
+      <c r="E89" s="14">
         <v>0.14155482739686501</v>
       </c>
-      <c r="F89" s="24">
+      <c r="F89" s="14">
         <v>6.1805126746967603E-3</v>
       </c>
-      <c r="G89" s="24">
+      <c r="G89" s="14">
         <v>1.5034931420651401</v>
       </c>
-      <c r="H89" s="24">
+      <c r="H89" s="14">
         <v>0.101579278133061</v>
       </c>
-      <c r="I89" s="25">
+      <c r="I89" s="23">
         <v>7.6412693195078096E-2</v>
       </c>
-      <c r="J89" s="25">
+      <c r="J89" s="23">
         <v>4.94569686443244E-3</v>
       </c>
-      <c r="K89" s="24">
+      <c r="K89" s="14">
         <v>0.33697715453369398</v>
       </c>
       <c r="L89" s="15">
@@ -5435,37 +5423,37 @@
       </c>
     </row>
     <row r="90" spans="1:12">
-      <c r="A90" s="22" t="s">
+      <c r="A90" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="B90" s="22" t="s">
+      <c r="B90" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C90" s="23">
+      <c r="C90" s="22">
         <v>7.3470906166834702</v>
       </c>
-      <c r="D90" s="23">
+      <c r="D90" s="22">
         <v>0.350542762087582</v>
       </c>
-      <c r="E90" s="24">
+      <c r="E90" s="14">
         <v>0.143267266206795</v>
       </c>
-      <c r="F90" s="24">
+      <c r="F90" s="14">
         <v>5.4231081099192302E-3</v>
       </c>
-      <c r="G90" s="24">
+      <c r="G90" s="14">
         <v>1.40118865047636</v>
       </c>
-      <c r="H90" s="24">
+      <c r="H90" s="14">
         <v>0.107837054847681</v>
       </c>
-      <c r="I90" s="25">
+      <c r="I90" s="23">
         <v>6.8872231768248998E-2</v>
       </c>
-      <c r="J90" s="25">
+      <c r="J90" s="23">
         <v>4.9888056857082703E-3</v>
       </c>
-      <c r="K90" s="24">
+      <c r="K90" s="14">
         <v>0.51244612786039101</v>
       </c>
       <c r="L90" s="15">
@@ -5473,37 +5461,37 @@
       </c>
     </row>
     <row r="91" spans="1:12">
-      <c r="A91" s="22" t="s">
+      <c r="A91" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B91" s="22" t="s">
+      <c r="B91" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C91" s="23">
+      <c r="C91" s="22">
         <v>7.7010540439831798</v>
       </c>
-      <c r="D91" s="23">
+      <c r="D91" s="22">
         <v>0.36899658008681602</v>
       </c>
-      <c r="E91" s="24">
+      <c r="E91" s="14">
         <v>0.137952178125716</v>
       </c>
-      <c r="F91" s="24">
+      <c r="F91" s="14">
         <v>5.3611501479213499E-3</v>
       </c>
-      <c r="G91" s="24">
+      <c r="G91" s="14">
         <v>1.4240766664208999</v>
       </c>
-      <c r="H91" s="24">
+      <c r="H91" s="14">
         <v>0.107665341177586</v>
       </c>
-      <c r="I91" s="25">
+      <c r="I91" s="23">
         <v>7.4943678002891895E-2</v>
       </c>
-      <c r="J91" s="25">
+      <c r="J91" s="23">
         <v>6.0278678671403596E-3</v>
       </c>
-      <c r="K91" s="24">
+      <c r="K91" s="14">
         <v>0.372054610861906</v>
       </c>
       <c r="L91" s="15">
@@ -5511,37 +5499,37 @@
       </c>
     </row>
     <row r="92" spans="1:12">
-      <c r="A92" s="22" t="s">
+      <c r="A92" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B92" s="22" t="s">
+      <c r="B92" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C92" s="23">
+      <c r="C92" s="22">
         <v>7.26230340281725</v>
       </c>
-      <c r="D92" s="23">
+      <c r="D92" s="22">
         <v>0.29192512294067802</v>
       </c>
-      <c r="E92" s="24">
+      <c r="E92" s="14">
         <v>0.143972949506944</v>
       </c>
-      <c r="F92" s="24">
+      <c r="F92" s="14">
         <v>5.1149589653330498E-3</v>
       </c>
-      <c r="G92" s="24">
+      <c r="G92" s="14">
         <v>1.4879036956662901</v>
       </c>
-      <c r="H92" s="24">
+      <c r="H92" s="14">
         <v>0.10547864357788</v>
       </c>
-      <c r="I92" s="25">
+      <c r="I92" s="23">
         <v>7.4868523288609198E-2</v>
       </c>
-      <c r="J92" s="25">
+      <c r="J92" s="23">
         <v>5.4613462058870398E-3</v>
       </c>
-      <c r="K92" s="24">
+      <c r="K92" s="14">
         <v>0.32932814735041999</v>
       </c>
       <c r="L92" s="15">
@@ -5549,37 +5537,37 @@
       </c>
     </row>
     <row r="93" spans="1:12">
-      <c r="A93" s="22" t="s">
+      <c r="A93" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="B93" s="22" t="s">
+      <c r="B93" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C93" s="23">
+      <c r="C93" s="22">
         <v>7.6593462668635599</v>
       </c>
-      <c r="D93" s="23">
+      <c r="D93" s="22">
         <v>0.34633732642756099</v>
       </c>
-      <c r="E93" s="24">
+      <c r="E93" s="14">
         <v>0.13538929418567799</v>
       </c>
-      <c r="F93" s="24">
+      <c r="F93" s="14">
         <v>5.0263074751577801E-3</v>
       </c>
-      <c r="G93" s="24">
+      <c r="G93" s="14">
         <v>1.3913236890537899</v>
       </c>
-      <c r="H93" s="24">
+      <c r="H93" s="14">
         <v>9.2193264080250498E-2</v>
       </c>
-      <c r="I93" s="25">
+      <c r="I93" s="23">
         <v>7.5030146631602707E-2</v>
       </c>
-      <c r="J93" s="25">
+      <c r="J93" s="23">
         <v>4.6681987593383198E-3</v>
       </c>
-      <c r="K93" s="24">
+      <c r="K93" s="14">
         <v>0.48295163803770402</v>
       </c>
       <c r="L93" s="15">
@@ -5587,37 +5575,37 @@
       </c>
     </row>
     <row r="94" spans="1:12">
-      <c r="A94" s="22" t="s">
+      <c r="A94" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="B94" s="22" t="s">
+      <c r="B94" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C94" s="23">
+      <c r="C94" s="22">
         <v>7.4903787806678404</v>
       </c>
-      <c r="D94" s="23">
+      <c r="D94" s="22">
         <v>0.27175987703112198</v>
       </c>
-      <c r="E94" s="24">
+      <c r="E94" s="14">
         <v>0.13498370317812899</v>
       </c>
-      <c r="F94" s="24">
+      <c r="F94" s="14">
         <v>4.6025355736710903E-3</v>
       </c>
-      <c r="G94" s="24">
+      <c r="G94" s="14">
         <v>1.2912467175478399</v>
       </c>
-      <c r="H94" s="24">
+      <c r="H94" s="14">
         <v>8.5135459302876401E-2</v>
       </c>
-      <c r="I94" s="25">
+      <c r="I94" s="23">
         <v>6.9840364294533802E-2</v>
       </c>
-      <c r="J94" s="25">
+      <c r="J94" s="23">
         <v>4.8450285792313802E-3</v>
       </c>
-      <c r="K94" s="24">
+      <c r="K94" s="14">
         <v>0.31499493514069199</v>
       </c>
       <c r="L94" s="15">
@@ -5625,37 +5613,37 @@
       </c>
     </row>
     <row r="95" spans="1:12">
-      <c r="A95" s="22" t="s">
+      <c r="A95" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="B95" s="22" t="s">
+      <c r="B95" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C95" s="23">
+      <c r="C95" s="22">
         <v>7.83139471213559</v>
       </c>
-      <c r="D95" s="23">
+      <c r="D95" s="22">
         <v>0.34997414300607299</v>
       </c>
-      <c r="E95" s="24">
+      <c r="E95" s="14">
         <v>0.13425361010562301</v>
       </c>
-      <c r="F95" s="24">
+      <c r="F95" s="14">
         <v>5.5216544453143297E-3</v>
       </c>
-      <c r="G95" s="24">
+      <c r="G95" s="14">
         <v>1.3203984069591901</v>
       </c>
-      <c r="H95" s="24">
+      <c r="H95" s="14">
         <v>0.105283376774901</v>
       </c>
-      <c r="I95" s="25">
+      <c r="I95" s="23">
         <v>7.0417295668674607E-2</v>
       </c>
-      <c r="J95" s="25">
+      <c r="J95" s="23">
         <v>5.4599727385774904E-3</v>
       </c>
-      <c r="K95" s="24">
+      <c r="K95" s="14">
         <v>0.48075507435264397</v>
       </c>
       <c r="L95" s="15">
@@ -5663,37 +5651,37 @@
       </c>
     </row>
     <row r="96" spans="1:12">
-      <c r="A96" s="22" t="s">
+      <c r="A96" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B96" s="22" t="s">
+      <c r="B96" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C96" s="23">
+      <c r="C96" s="22">
         <v>7.8515719893069704</v>
       </c>
-      <c r="D96" s="23">
+      <c r="D96" s="22">
         <v>0.385023958852444</v>
       </c>
-      <c r="E96" s="24">
+      <c r="E96" s="14">
         <v>0.13606450642397699</v>
       </c>
-      <c r="F96" s="24">
+      <c r="F96" s="14">
         <v>6.0278292902075301E-3</v>
       </c>
-      <c r="G96" s="24">
+      <c r="G96" s="14">
         <v>1.3976354471693999</v>
       </c>
-      <c r="H96" s="24">
+      <c r="H96" s="14">
         <v>0.110921525805514</v>
       </c>
-      <c r="I96" s="25">
+      <c r="I96" s="23">
         <v>7.5664292150494403E-2</v>
       </c>
-      <c r="J96" s="25">
+      <c r="J96" s="23">
         <v>6.4295196522557302E-3</v>
       </c>
-      <c r="K96" s="24">
+      <c r="K96" s="14">
         <v>0.359309928269751</v>
       </c>
       <c r="L96" s="15">
@@ -5701,37 +5689,37 @@
       </c>
     </row>
     <row r="97" spans="1:12">
-      <c r="A97" s="22" t="s">
+      <c r="A97" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B97" s="22" t="s">
+      <c r="B97" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C97" s="23">
+      <c r="C97" s="22">
         <v>7.4654877435534601</v>
       </c>
-      <c r="D97" s="23">
+      <c r="D97" s="22">
         <v>0.41571955452715298</v>
       </c>
-      <c r="E97" s="24">
+      <c r="E97" s="14">
         <v>0.14439412746883201</v>
       </c>
-      <c r="F97" s="24">
+      <c r="F97" s="14">
         <v>6.8701661935027299E-3</v>
       </c>
-      <c r="G97" s="24">
+      <c r="G97" s="14">
         <v>1.40558867266333</v>
       </c>
-      <c r="H97" s="24">
+      <c r="H97" s="14">
         <v>0.122802383192541</v>
       </c>
-      <c r="I97" s="25">
+      <c r="I97" s="23">
         <v>7.1169444424545203E-2</v>
       </c>
-      <c r="J97" s="25">
+      <c r="J97" s="23">
         <v>6.3955062228949399E-3</v>
       </c>
-      <c r="K97" s="24">
+      <c r="K97" s="14">
         <v>0.42110892665968802</v>
       </c>
       <c r="L97" s="15">
@@ -5739,37 +5727,37 @@
       </c>
     </row>
     <row r="98" spans="1:12">
-      <c r="A98" s="22" t="s">
+      <c r="A98" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="B98" s="22" t="s">
+      <c r="B98" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C98" s="23">
+      <c r="C98" s="22">
         <v>8.0151352383561907</v>
       </c>
-      <c r="D98" s="23">
+      <c r="D98" s="22">
         <v>0.58815352083429295</v>
       </c>
-      <c r="E98" s="24">
+      <c r="E98" s="14">
         <v>0.14190219387148501</v>
       </c>
-      <c r="F98" s="24">
+      <c r="F98" s="14">
         <v>8.3538574417167197E-3</v>
       </c>
-      <c r="G98" s="24">
+      <c r="G98" s="14">
         <v>1.3912578065904599</v>
       </c>
-      <c r="H98" s="24">
+      <c r="H98" s="14">
         <v>0.12849535966696499</v>
       </c>
-      <c r="I98" s="25">
+      <c r="I98" s="23">
         <v>6.9929381962366297E-2</v>
       </c>
-      <c r="J98" s="25">
+      <c r="J98" s="23">
         <v>6.58212868843516E-3</v>
       </c>
-      <c r="K98" s="24">
+      <c r="K98" s="14">
         <v>0.55292745612519001</v>
       </c>
       <c r="L98" s="15">
@@ -5777,37 +5765,37 @@
       </c>
     </row>
     <row r="99" spans="1:12">
-      <c r="A99" s="22" t="s">
+      <c r="A99" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="B99" s="22" t="s">
+      <c r="B99" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C99" s="23">
+      <c r="C99" s="22">
         <v>8.0587736727912294</v>
       </c>
-      <c r="D99" s="23">
+      <c r="D99" s="22">
         <v>0.32344914824760501</v>
       </c>
-      <c r="E99" s="24">
+      <c r="E99" s="14">
         <v>0.12750844308235701</v>
       </c>
-      <c r="F99" s="24">
+      <c r="F99" s="14">
         <v>4.7669570855565398E-3</v>
       </c>
-      <c r="G99" s="24">
+      <c r="G99" s="14">
         <v>1.2829435699345599</v>
       </c>
-      <c r="H99" s="24">
+      <c r="H99" s="14">
         <v>9.7375036863236702E-2</v>
       </c>
-      <c r="I99" s="25">
+      <c r="I99" s="23">
         <v>7.2067187137027894E-2</v>
       </c>
-      <c r="J99" s="25">
+      <c r="J99" s="23">
         <v>5.5495731997603796E-3</v>
       </c>
-      <c r="K99" s="24">
+      <c r="K99" s="14">
         <v>0.36756222673828398</v>
       </c>
       <c r="L99" s="15">
@@ -5815,37 +5803,37 @@
       </c>
     </row>
     <row r="100" spans="1:12">
-      <c r="A100" s="22" t="s">
+      <c r="A100" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="B100" s="22" t="s">
+      <c r="B100" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C100" s="23">
+      <c r="C100" s="22">
         <v>7.87372481473541</v>
       </c>
-      <c r="D100" s="23">
+      <c r="D100" s="22">
         <v>0.32085077508311999</v>
       </c>
-      <c r="E100" s="24">
+      <c r="E100" s="14">
         <v>0.130768903445345</v>
       </c>
-      <c r="F100" s="24">
+      <c r="F100" s="14">
         <v>4.6629960048398403E-3</v>
       </c>
-      <c r="G100" s="24">
+      <c r="G100" s="14">
         <v>1.3310439778563301</v>
       </c>
-      <c r="H100" s="24">
+      <c r="H100" s="14">
         <v>9.7810068655444393E-2</v>
       </c>
-      <c r="I100" s="25">
+      <c r="I100" s="23">
         <v>7.2279324312484697E-2</v>
       </c>
-      <c r="J100" s="25">
+      <c r="J100" s="23">
         <v>5.21705019404316E-3</v>
       </c>
-      <c r="K100" s="24">
+      <c r="K100" s="14">
         <v>0.42814591257449203</v>
       </c>
       <c r="L100" s="15">
@@ -5853,37 +5841,37 @@
       </c>
     </row>
     <row r="101" spans="1:12">
-      <c r="A101" s="22" t="s">
+      <c r="A101" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B101" s="22" t="s">
+      <c r="B101" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C101" s="23">
+      <c r="C101" s="22">
         <v>7.3044360908252397</v>
       </c>
-      <c r="D101" s="23">
+      <c r="D101" s="22">
         <v>0.33374430189281401</v>
       </c>
-      <c r="E101" s="24">
+      <c r="E101" s="14">
         <v>0.14354769125310099</v>
       </c>
-      <c r="F101" s="24">
+      <c r="F101" s="14">
         <v>5.4078325718691402E-3</v>
       </c>
-      <c r="G101" s="24">
+      <c r="G101" s="14">
         <v>1.4853789651229701</v>
       </c>
-      <c r="H101" s="24">
+      <c r="H101" s="14">
         <v>0.116950603928765</v>
       </c>
-      <c r="I101" s="25">
+      <c r="I101" s="23">
         <v>7.3641702061735703E-2</v>
       </c>
-      <c r="J101" s="25">
+      <c r="J101" s="23">
         <v>5.6144611191464603E-3</v>
       </c>
-      <c r="K101" s="24">
+      <c r="K101" s="14">
         <v>0.43099538167689999</v>
       </c>
       <c r="L101" s="15">
@@ -5891,37 +5879,37 @@
       </c>
     </row>
     <row r="102" spans="1:12">
-      <c r="A102" s="22" t="s">
+      <c r="A102" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B102" s="22" t="s">
+      <c r="B102" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C102" s="23">
+      <c r="C102" s="22">
         <v>7.63613948565248</v>
       </c>
-      <c r="D102" s="23">
+      <c r="D102" s="22">
         <v>0.38483287372755798</v>
       </c>
-      <c r="E102" s="24">
+      <c r="E102" s="14">
         <v>0.13957023926756801</v>
       </c>
-      <c r="F102" s="24">
+      <c r="F102" s="14">
         <v>5.9881580821249296E-3</v>
       </c>
-      <c r="G102" s="24">
+      <c r="G102" s="14">
         <v>1.47405061760259</v>
       </c>
-      <c r="H102" s="24">
+      <c r="H102" s="14">
         <v>0.13417266000249001</v>
       </c>
-      <c r="I102" s="25">
+      <c r="I102" s="23">
         <v>7.3251873213697694E-2</v>
       </c>
-      <c r="J102" s="25">
+      <c r="J102" s="23">
         <v>6.48681681678678E-3</v>
       </c>
-      <c r="K102" s="24">
+      <c r="K102" s="14">
         <v>0.36775801886305898</v>
       </c>
       <c r="L102" s="15">
@@ -5929,37 +5917,37 @@
       </c>
     </row>
     <row r="103" spans="1:12">
-      <c r="A103" s="22" t="s">
+      <c r="A103" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="B103" s="22" t="s">
+      <c r="B103" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C103" s="23">
+      <c r="C103" s="22">
         <v>8.0139193274172609</v>
       </c>
-      <c r="D103" s="23">
+      <c r="D103" s="22">
         <v>0.259802695178874</v>
       </c>
-      <c r="E103" s="24">
+      <c r="E103" s="14">
         <v>0.12597737606690401</v>
       </c>
-      <c r="F103" s="24">
+      <c r="F103" s="14">
         <v>4.0345132575954198E-3</v>
       </c>
-      <c r="G103" s="24">
+      <c r="G103" s="14">
         <v>1.30324293091336</v>
       </c>
-      <c r="H103" s="24">
+      <c r="H103" s="14">
         <v>8.8794253442670196E-2</v>
       </c>
-      <c r="I103" s="25">
+      <c r="I103" s="23">
         <v>7.4020535515848099E-2</v>
       </c>
-      <c r="J103" s="25">
+      <c r="J103" s="23">
         <v>4.8600463769386199E-3</v>
       </c>
-      <c r="K103" s="24">
+      <c r="K103" s="14">
         <v>0.35431744476627097</v>
       </c>
       <c r="L103" s="15">
@@ -5967,37 +5955,37 @@
       </c>
     </row>
     <row r="104" spans="1:12">
-      <c r="A104" s="22" t="s">
+      <c r="A104" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="B104" s="22" t="s">
+      <c r="B104" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C104" s="23">
+      <c r="C104" s="22">
         <v>6.7334933484307102</v>
       </c>
-      <c r="D104" s="23">
+      <c r="D104" s="22">
         <v>0.22245943219883901</v>
       </c>
-      <c r="E104" s="24">
+      <c r="E104" s="14">
         <v>0.15124961361066599</v>
       </c>
-      <c r="F104" s="24">
+      <c r="F104" s="14">
         <v>4.6882223786793003E-3</v>
       </c>
-      <c r="G104" s="24">
+      <c r="G104" s="14">
         <v>1.55618578917104</v>
       </c>
-      <c r="H104" s="24">
+      <c r="H104" s="14">
         <v>8.5713775100795003E-2</v>
       </c>
-      <c r="I104" s="25">
+      <c r="I104" s="23">
         <v>7.6338822102329895E-2</v>
       </c>
-      <c r="J104" s="25">
+      <c r="J104" s="23">
         <v>4.4090899776074296E-3</v>
       </c>
-      <c r="K104" s="24">
+      <c r="K104" s="14">
         <v>0.22218882946978699</v>
       </c>
       <c r="L104" s="15">
@@ -6005,37 +5993,37 @@
       </c>
     </row>
     <row r="105" spans="1:12">
-      <c r="A105" s="22" t="s">
+      <c r="A105" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="B105" s="22" t="s">
+      <c r="B105" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C105" s="23">
+      <c r="C105" s="22">
         <v>6.8970477868571196</v>
       </c>
-      <c r="D105" s="23">
+      <c r="D105" s="22">
         <v>0.28191120849585499</v>
       </c>
-      <c r="E105" s="24">
+      <c r="E105" s="14">
         <v>0.14657735351722601</v>
       </c>
-      <c r="F105" s="24">
+      <c r="F105" s="14">
         <v>5.4832854133789596E-3</v>
       </c>
-      <c r="G105" s="24">
+      <c r="G105" s="14">
         <v>1.5433809758699399</v>
       </c>
-      <c r="H105" s="24">
+      <c r="H105" s="14">
         <v>0.10383464910222499</v>
       </c>
-      <c r="I105" s="25">
+      <c r="I105" s="23">
         <v>7.5654392399372203E-2</v>
       </c>
-      <c r="J105" s="25">
+      <c r="J105" s="23">
         <v>4.9378443768086401E-3</v>
       </c>
-      <c r="K105" s="24">
+      <c r="K105" s="14">
         <v>0.40201678397956497</v>
       </c>
       <c r="L105" s="15">
@@ -6043,37 +6031,37 @@
       </c>
     </row>
     <row r="106" spans="1:12">
-      <c r="A106" s="22" t="s">
+      <c r="A106" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="B106" s="22" t="s">
+      <c r="B106" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C106" s="23">
+      <c r="C106" s="22">
         <v>6.8038203413937302</v>
       </c>
-      <c r="D106" s="23">
+      <c r="D106" s="22">
         <v>0.32055348389581301</v>
       </c>
-      <c r="E106" s="24">
+      <c r="E106" s="14">
         <v>0.148580938493101</v>
       </c>
-      <c r="F106" s="24">
+      <c r="F106" s="14">
         <v>5.6494380623842702E-3</v>
       </c>
-      <c r="G106" s="24">
+      <c r="G106" s="14">
         <v>1.4911555139214301</v>
       </c>
-      <c r="H106" s="24">
+      <c r="H106" s="14">
         <v>0.117164350519634</v>
       </c>
-      <c r="I106" s="25">
+      <c r="I106" s="23">
         <v>7.1860651427691602E-2</v>
       </c>
-      <c r="J106" s="25">
+      <c r="J106" s="23">
         <v>6.3079525995808697E-3</v>
       </c>
-      <c r="K106" s="24">
+      <c r="K106" s="14">
         <v>0.12132651463782999</v>
       </c>
       <c r="L106" s="15">
@@ -6081,37 +6069,37 @@
       </c>
     </row>
     <row r="107" spans="1:12">
-      <c r="A107" s="22" t="s">
+      <c r="A107" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="B107" s="22" t="s">
+      <c r="B107" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C107" s="23">
+      <c r="C107" s="22">
         <v>7.1629083586653</v>
       </c>
-      <c r="D107" s="23">
+      <c r="D107" s="22">
         <v>0.33328733304147501</v>
       </c>
-      <c r="E107" s="24">
+      <c r="E107" s="14">
         <v>0.14329542429959799</v>
       </c>
-      <c r="F107" s="24">
+      <c r="F107" s="14">
         <v>5.4604341803247197E-3</v>
       </c>
-      <c r="G107" s="24">
+      <c r="G107" s="14">
         <v>1.6051705427971601</v>
       </c>
-      <c r="H107" s="24">
+      <c r="H107" s="14">
         <v>0.10301455370863</v>
       </c>
-      <c r="I107" s="25">
+      <c r="I107" s="23">
         <v>8.1521683811864198E-2</v>
       </c>
-      <c r="J107" s="25">
+      <c r="J107" s="23">
         <v>5.1829535009683602E-3</v>
       </c>
-      <c r="K107" s="24">
+      <c r="K107" s="14">
         <v>0.42391466584830301</v>
       </c>
       <c r="L107" s="15">
@@ -6119,37 +6107,37 @@
       </c>
     </row>
     <row r="108" spans="1:12">
-      <c r="A108" s="22" t="s">
+      <c r="A108" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="B108" s="22" t="s">
+      <c r="B108" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C108" s="23">
+      <c r="C108" s="22">
         <v>7.05799559878567</v>
       </c>
-      <c r="D108" s="23">
+      <c r="D108" s="22">
         <v>0.31250118042830999</v>
       </c>
-      <c r="E108" s="24">
+      <c r="E108" s="14">
         <v>0.14578001568938401</v>
       </c>
-      <c r="F108" s="24">
+      <c r="F108" s="14">
         <v>5.2800239168396398E-3</v>
       </c>
-      <c r="G108" s="24">
+      <c r="G108" s="14">
         <v>1.5081373678051899</v>
       </c>
-      <c r="H108" s="24">
+      <c r="H108" s="14">
         <v>0.105096747686011</v>
       </c>
-      <c r="I108" s="25">
+      <c r="I108" s="23">
         <v>7.3422091340499193E-2</v>
       </c>
-      <c r="J108" s="25">
+      <c r="J108" s="23">
         <v>4.9421954556481303E-3</v>
       </c>
-      <c r="K108" s="24">
+      <c r="K108" s="14">
         <v>0.39486839307714999</v>
       </c>
       <c r="L108" s="15">
@@ -6157,37 +6145,37 @@
       </c>
     </row>
     <row r="109" spans="1:12">
-      <c r="A109" s="22" t="s">
+      <c r="A109" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="B109" s="22" t="s">
+      <c r="B109" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C109" s="23">
+      <c r="C109" s="22">
         <v>8.0740780073671203</v>
       </c>
-      <c r="D109" s="23">
+      <c r="D109" s="22">
         <v>0.342876789122671</v>
       </c>
-      <c r="E109" s="24">
+      <c r="E109" s="14">
         <v>0.130512191653401</v>
       </c>
-      <c r="F109" s="24">
+      <c r="F109" s="14">
         <v>5.05572085197167E-3</v>
       </c>
-      <c r="G109" s="24">
+      <c r="G109" s="14">
         <v>1.36906130127351</v>
       </c>
-      <c r="H109" s="24">
+      <c r="H109" s="14">
         <v>9.3189514096570905E-2</v>
       </c>
-      <c r="I109" s="25">
+      <c r="I109" s="23">
         <v>7.4918737362231105E-2</v>
       </c>
-      <c r="J109" s="25">
+      <c r="J109" s="23">
         <v>5.0385968208752603E-3</v>
       </c>
-      <c r="K109" s="24">
+      <c r="K109" s="14">
         <v>0.26851987986694997</v>
       </c>
       <c r="L109" s="15">
@@ -6195,37 +6183,37 @@
       </c>
     </row>
     <row r="110" spans="1:12">
-      <c r="A110" s="22" t="s">
+      <c r="A110" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="B110" s="22" t="s">
+      <c r="B110" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C110" s="23">
+      <c r="C110" s="22">
         <v>7.8994000370066901</v>
       </c>
-      <c r="D110" s="23">
+      <c r="D110" s="22">
         <v>0.33830544617744002</v>
       </c>
-      <c r="E110" s="24">
+      <c r="E110" s="14">
         <v>0.13288817214452101</v>
       </c>
-      <c r="F110" s="24">
+      <c r="F110" s="14">
         <v>5.1267310021031699E-3</v>
       </c>
-      <c r="G110" s="24">
+      <c r="G110" s="14">
         <v>1.34797038021028</v>
       </c>
-      <c r="H110" s="24">
+      <c r="H110" s="14">
         <v>0.11287891483991699</v>
       </c>
-      <c r="I110" s="25">
+      <c r="I110" s="23">
         <v>7.1278899497503198E-2</v>
       </c>
-      <c r="J110" s="25">
+      <c r="J110" s="23">
         <v>5.6395332213672496E-3</v>
       </c>
-      <c r="K110" s="24">
+      <c r="K110" s="14">
         <v>0.35602778134092999</v>
       </c>
       <c r="L110" s="15">
@@ -6233,37 +6221,37 @@
       </c>
     </row>
     <row r="111" spans="1:12">
-      <c r="A111" s="22" t="s">
+      <c r="A111" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="B111" s="22" t="s">
+      <c r="B111" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C111" s="23">
+      <c r="C111" s="22">
         <v>7.6470368303547502</v>
       </c>
-      <c r="D111" s="23">
+      <c r="D111" s="22">
         <v>0.37057852089862098</v>
       </c>
-      <c r="E111" s="24">
+      <c r="E111" s="14">
         <v>0.13536164675919701</v>
       </c>
-      <c r="F111" s="24">
+      <c r="F111" s="14">
         <v>5.6173371757510804E-3</v>
       </c>
-      <c r="G111" s="24">
+      <c r="G111" s="14">
         <v>1.4102443908662701</v>
       </c>
-      <c r="H111" s="24">
+      <c r="H111" s="14">
         <v>0.104336192558346</v>
       </c>
-      <c r="I111" s="25">
+      <c r="I111" s="23">
         <v>7.4770293545313393E-2</v>
       </c>
-      <c r="J111" s="25">
+      <c r="J111" s="23">
         <v>5.86911866602597E-3</v>
       </c>
-      <c r="K111" s="24">
+      <c r="K111" s="14">
         <v>0.31384686452035199</v>
       </c>
       <c r="L111" s="15">
@@ -6271,37 +6259,37 @@
       </c>
     </row>
     <row r="112" spans="1:12">
-      <c r="A112" s="22" t="s">
+      <c r="A112" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="B112" s="22" t="s">
+      <c r="B112" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C112" s="23">
+      <c r="C112" s="22">
         <v>7.6611176070965001</v>
       </c>
-      <c r="D112" s="23">
+      <c r="D112" s="22">
         <v>0.36092203270369999</v>
       </c>
-      <c r="E112" s="24">
+      <c r="E112" s="14">
         <v>0.13656589689524901</v>
       </c>
-      <c r="F112" s="24">
+      <c r="F112" s="14">
         <v>5.4676305747243603E-3</v>
       </c>
-      <c r="G112" s="24">
+      <c r="G112" s="14">
         <v>1.42971119804596</v>
       </c>
-      <c r="H112" s="24">
+      <c r="H112" s="14">
         <v>0.116737158454051</v>
       </c>
-      <c r="I112" s="25">
+      <c r="I112" s="23">
         <v>7.3897567517689E-2</v>
       </c>
-      <c r="J112" s="25">
+      <c r="J112" s="23">
         <v>6.1470789160013098E-3</v>
       </c>
-      <c r="K112" s="24">
+      <c r="K112" s="14">
         <v>0.43766522097985899</v>
       </c>
       <c r="L112" s="15">
@@ -6309,37 +6297,37 @@
       </c>
     </row>
     <row r="113" spans="1:12">
-      <c r="A113" s="22" t="s">
+      <c r="A113" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="B113" s="22" t="s">
+      <c r="B113" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C113" s="23">
+      <c r="C113" s="22">
         <v>6.7435461718969698</v>
       </c>
-      <c r="D113" s="23">
+      <c r="D113" s="22">
         <v>0.23669139245357601</v>
       </c>
-      <c r="E113" s="24">
+      <c r="E113" s="14">
         <v>0.149122875354397</v>
       </c>
-      <c r="F113" s="24">
+      <c r="F113" s="14">
         <v>4.9237104932553103E-3</v>
       </c>
-      <c r="G113" s="24">
+      <c r="G113" s="14">
         <v>1.3485911535580499</v>
       </c>
-      <c r="H113" s="24">
+      <c r="H113" s="14">
         <v>0.114173516352737</v>
       </c>
-      <c r="I113" s="25">
+      <c r="I113" s="23">
         <v>6.3775022799817394E-2</v>
       </c>
-      <c r="J113" s="25">
+      <c r="J113" s="23">
         <v>5.1121964887020799E-3</v>
       </c>
-      <c r="K113" s="24">
+      <c r="K113" s="14">
         <v>0.34665647698975399</v>
       </c>
       <c r="L113" s="15">
@@ -6347,37 +6335,37 @@
       </c>
     </row>
     <row r="114" spans="1:12">
-      <c r="A114" s="22" t="s">
+      <c r="A114" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="B114" s="22" t="s">
+      <c r="B114" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C114" s="23">
+      <c r="C114" s="22">
         <v>7.1105960626779696</v>
       </c>
-      <c r="D114" s="23">
+      <c r="D114" s="22">
         <v>0.33694101665217202</v>
       </c>
-      <c r="E114" s="24">
+      <c r="E114" s="14">
         <v>0.144310949953326</v>
       </c>
-      <c r="F114" s="24">
+      <c r="F114" s="14">
         <v>5.9136103653360797E-3</v>
       </c>
-      <c r="G114" s="24">
+      <c r="G114" s="14">
         <v>1.5924940918853701</v>
       </c>
-      <c r="H114" s="24">
+      <c r="H114" s="14">
         <v>0.113989292874417</v>
       </c>
-      <c r="I114" s="25">
+      <c r="I114" s="23">
         <v>7.9714665155939696E-2</v>
       </c>
-      <c r="J114" s="25">
+      <c r="J114" s="23">
         <v>6.3412329323659202E-3</v>
       </c>
-      <c r="K114" s="24">
+      <c r="K114" s="14">
         <v>0.27475301175675299</v>
       </c>
       <c r="L114" s="15">
@@ -6385,37 +6373,37 @@
       </c>
     </row>
     <row r="115" spans="1:12">
-      <c r="A115" s="22" t="s">
+      <c r="A115" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="B115" s="22" t="s">
+      <c r="B115" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C115" s="23">
+      <c r="C115" s="22">
         <v>7.0223097896236499</v>
       </c>
-      <c r="D115" s="23">
+      <c r="D115" s="22">
         <v>0.28993551769474601</v>
       </c>
-      <c r="E115" s="24">
+      <c r="E115" s="14">
         <v>0.148004481896131</v>
       </c>
-      <c r="F115" s="24">
+      <c r="F115" s="14">
         <v>5.4881581086688204E-3</v>
       </c>
-      <c r="G115" s="24">
+      <c r="G115" s="14">
         <v>1.58499938424681</v>
       </c>
-      <c r="H115" s="24">
+      <c r="H115" s="14">
         <v>0.12593629030677</v>
       </c>
-      <c r="I115" s="25">
+      <c r="I115" s="23">
         <v>7.6801920006095897E-2</v>
       </c>
-      <c r="J115" s="25">
+      <c r="J115" s="23">
         <v>6.3515097200765201E-3</v>
       </c>
-      <c r="K115" s="24">
+      <c r="K115" s="14">
         <v>0.21061237575687899</v>
       </c>
       <c r="L115" s="15">
@@ -6423,37 +6411,37 @@
       </c>
     </row>
     <row r="116" spans="1:12">
-      <c r="A116" s="22" t="s">
+      <c r="A116" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="B116" s="22" t="s">
+      <c r="B116" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C116" s="23">
+      <c r="C116" s="22">
         <v>7.2169184931556298</v>
       </c>
-      <c r="D116" s="23">
+      <c r="D116" s="22">
         <v>0.335115465114739</v>
       </c>
-      <c r="E116" s="24">
+      <c r="E116" s="14">
         <v>0.14558899951599999</v>
       </c>
-      <c r="F116" s="24">
+      <c r="F116" s="14">
         <v>5.7537309532333502E-3</v>
       </c>
-      <c r="G116" s="24">
+      <c r="G116" s="14">
         <v>1.4041219511565399</v>
       </c>
-      <c r="H116" s="24">
+      <c r="H116" s="14">
         <v>0.124867570445735</v>
       </c>
-      <c r="I116" s="25">
+      <c r="I116" s="23">
         <v>6.7960105254238207E-2</v>
       </c>
-      <c r="J116" s="25">
+      <c r="J116" s="23">
         <v>5.65905798090974E-3</v>
       </c>
-      <c r="K116" s="24">
+      <c r="K116" s="14">
         <v>0.37289070564348997</v>
       </c>
       <c r="L116" s="15">
@@ -6461,37 +6449,37 @@
       </c>
     </row>
     <row r="117" spans="1:12">
-      <c r="A117" s="22" t="s">
+      <c r="A117" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="B117" s="22" t="s">
+      <c r="B117" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C117" s="23">
+      <c r="C117" s="22">
         <v>6.8203048615534199</v>
       </c>
-      <c r="D117" s="23">
+      <c r="D117" s="22">
         <v>0.23819512784449101</v>
       </c>
-      <c r="E117" s="24">
+      <c r="E117" s="14">
         <v>0.14649871190674199</v>
       </c>
-      <c r="F117" s="24">
+      <c r="F117" s="14">
         <v>4.7721146854088903E-3</v>
       </c>
-      <c r="G117" s="24">
+      <c r="G117" s="14">
         <v>1.5557160897000499</v>
       </c>
-      <c r="H117" s="24">
+      <c r="H117" s="14">
         <v>0.11328435690810899</v>
       </c>
-      <c r="I117" s="25">
+      <c r="I117" s="23">
         <v>7.6490279243060802E-2</v>
       </c>
-      <c r="J117" s="25">
+      <c r="J117" s="23">
         <v>5.6170973831842098E-3</v>
       </c>
-      <c r="K117" s="24">
+      <c r="K117" s="14">
         <v>0.40770700059390402</v>
       </c>
       <c r="L117" s="15">
@@ -6499,37 +6487,37 @@
       </c>
     </row>
     <row r="118" spans="1:12">
-      <c r="A118" s="22" t="s">
+      <c r="A118" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="B118" s="22" t="s">
+      <c r="B118" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C118" s="23">
+      <c r="C118" s="22">
         <v>7.0129521124329797</v>
       </c>
-      <c r="D118" s="23">
+      <c r="D118" s="22">
         <v>0.35661732131393398</v>
       </c>
-      <c r="E118" s="24">
+      <c r="E118" s="14">
         <v>0.14768913343846099</v>
       </c>
-      <c r="F118" s="24">
+      <c r="F118" s="14">
         <v>6.1034466466038497E-3</v>
       </c>
-      <c r="G118" s="24">
+      <c r="G118" s="14">
         <v>1.5363015521268799</v>
       </c>
-      <c r="H118" s="24">
+      <c r="H118" s="14">
         <v>0.12045857617526599</v>
       </c>
-      <c r="I118" s="25">
+      <c r="I118" s="23">
         <v>7.4952582599410705E-2</v>
       </c>
-      <c r="J118" s="25">
+      <c r="J118" s="23">
         <v>5.8862691354111601E-3</v>
       </c>
-      <c r="K118" s="24">
+      <c r="K118" s="14">
         <v>0.39000092545564602</v>
       </c>
       <c r="L118" s="15">
@@ -6537,37 +6525,37 @@
       </c>
     </row>
     <row r="119" spans="1:12">
-      <c r="A119" s="22" t="s">
+      <c r="A119" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="B119" s="22" t="s">
+      <c r="B119" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C119" s="23">
+      <c r="C119" s="22">
         <v>7.48946599113592</v>
       </c>
-      <c r="D119" s="23">
+      <c r="D119" s="22">
         <v>0.33096210936353798</v>
       </c>
-      <c r="E119" s="24">
+      <c r="E119" s="14">
         <v>0.13879866678344399</v>
       </c>
-      <c r="F119" s="24">
+      <c r="F119" s="14">
         <v>5.6863099921405204E-3</v>
       </c>
-      <c r="G119" s="24">
+      <c r="G119" s="14">
         <v>1.3357770481434901</v>
       </c>
-      <c r="H119" s="24">
+      <c r="H119" s="14">
         <v>0.11852051509067001</v>
       </c>
-      <c r="I119" s="25">
+      <c r="I119" s="23">
         <v>6.9863668741382098E-2</v>
       </c>
-      <c r="J119" s="25">
+      <c r="J119" s="23">
         <v>6.9839409888671202E-3</v>
       </c>
-      <c r="K119" s="24">
+      <c r="K119" s="14">
         <v>0.29333189867216602</v>
       </c>
       <c r="L119" s="15">
@@ -6575,37 +6563,37 @@
       </c>
     </row>
     <row r="120" spans="1:12">
-      <c r="A120" s="22" t="s">
+      <c r="A120" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="B120" s="22" t="s">
+      <c r="B120" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C120" s="23">
+      <c r="C120" s="22">
         <v>7.2354360380182996</v>
       </c>
-      <c r="D120" s="23">
+      <c r="D120" s="22">
         <v>0.222268778457439</v>
       </c>
-      <c r="E120" s="24">
+      <c r="E120" s="14">
         <v>0.139783806908966</v>
       </c>
-      <c r="F120" s="24">
+      <c r="F120" s="14">
         <v>4.2183500714130101E-3</v>
       </c>
-      <c r="G120" s="24">
+      <c r="G120" s="14">
         <v>1.4280515024903899</v>
       </c>
-      <c r="H120" s="24">
+      <c r="H120" s="14">
         <v>0.10600893913399199</v>
       </c>
-      <c r="I120" s="25">
+      <c r="I120" s="23">
         <v>7.3555862011009401E-2</v>
       </c>
-      <c r="J120" s="25">
+      <c r="J120" s="23">
         <v>5.4241499394569797E-3</v>
       </c>
-      <c r="K120" s="24">
+      <c r="K120" s="14">
         <v>0.30793397089816898</v>
       </c>
       <c r="L120" s="15">
@@ -6613,37 +6601,37 @@
       </c>
     </row>
     <row r="121" spans="1:12">
-      <c r="A121" s="22" t="s">
+      <c r="A121" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="B121" s="22" t="s">
+      <c r="B121" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C121" s="23">
+      <c r="C121" s="22">
         <v>8.0352178084539698</v>
       </c>
-      <c r="D121" s="23">
+      <c r="D121" s="22">
         <v>0.29762081801991702</v>
       </c>
-      <c r="E121" s="24">
+      <c r="E121" s="14">
         <v>0.12734605299978299</v>
       </c>
-      <c r="F121" s="24">
+      <c r="F121" s="14">
         <v>4.5355265288434098E-3</v>
       </c>
-      <c r="G121" s="24">
+      <c r="G121" s="14">
         <v>1.24864109420488</v>
       </c>
-      <c r="H121" s="24">
+      <c r="H121" s="14">
         <v>9.4959556662007699E-2</v>
       </c>
-      <c r="I121" s="25">
+      <c r="I121" s="23">
         <v>7.2273225955992795E-2</v>
       </c>
-      <c r="J121" s="25">
+      <c r="J121" s="23">
         <v>5.4149695734202596E-3</v>
       </c>
-      <c r="K121" s="24">
+      <c r="K121" s="14">
         <v>0.34724530156287697</v>
       </c>
       <c r="L121" s="15">
@@ -6651,37 +6639,37 @@
       </c>
     </row>
     <row r="122" spans="1:12">
-      <c r="A122" s="22" t="s">
+      <c r="A122" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="B122" s="22" t="s">
+      <c r="B122" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C122" s="23">
+      <c r="C122" s="22">
         <v>8.4766399713369704</v>
       </c>
-      <c r="D122" s="23">
+      <c r="D122" s="22">
         <v>0.44008848574708598</v>
       </c>
-      <c r="E122" s="24">
+      <c r="E122" s="14">
         <v>0.124992342844969</v>
       </c>
-      <c r="F122" s="24">
+      <c r="F122" s="14">
         <v>5.7985134691181904E-3</v>
       </c>
-      <c r="G122" s="24">
+      <c r="G122" s="14">
         <v>1.25587009534764</v>
       </c>
-      <c r="H122" s="24">
+      <c r="H122" s="14">
         <v>0.110170219600183</v>
       </c>
-      <c r="I122" s="25">
+      <c r="I122" s="23">
         <v>7.2481444489414196E-2</v>
       </c>
-      <c r="J122" s="25">
+      <c r="J122" s="23">
         <v>6.5606155470168603E-3</v>
       </c>
-      <c r="K122" s="24">
+      <c r="K122" s="14">
         <v>0.41425955914214402</v>
       </c>
       <c r="L122" s="15">
@@ -6689,37 +6677,37 @@
       </c>
     </row>
     <row r="123" spans="1:12">
-      <c r="A123" s="22" t="s">
+      <c r="A123" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="B123" s="22" t="s">
+      <c r="B123" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C123" s="23">
+      <c r="C123" s="22">
         <v>7.8476844108630699</v>
       </c>
-      <c r="D123" s="23">
+      <c r="D123" s="22">
         <v>0.31048359893026101</v>
       </c>
-      <c r="E123" s="24">
+      <c r="E123" s="14">
         <v>0.131214347241252</v>
       </c>
-      <c r="F123" s="24">
+      <c r="F123" s="14">
         <v>4.7102199988970301E-3</v>
       </c>
-      <c r="G123" s="24">
+      <c r="G123" s="14">
         <v>1.3976180444411599</v>
       </c>
-      <c r="H123" s="24">
+      <c r="H123" s="14">
         <v>0.10971419748111801</v>
       </c>
-      <c r="I123" s="25">
+      <c r="I123" s="23">
         <v>7.8565401643065996E-2</v>
       </c>
-      <c r="J123" s="25">
+      <c r="J123" s="23">
         <v>6.4437431390303602E-3</v>
       </c>
-      <c r="K123" s="24">
+      <c r="K123" s="14">
         <v>0.20299246930777801</v>
       </c>
       <c r="L123" s="15">
@@ -6727,37 +6715,37 @@
       </c>
     </row>
     <row r="124" spans="1:12">
-      <c r="A124" s="22" t="s">
+      <c r="A124" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="B124" s="22" t="s">
+      <c r="B124" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C124" s="23">
+      <c r="C124" s="22">
         <v>8.2428598398819002</v>
       </c>
-      <c r="D124" s="23">
+      <c r="D124" s="22">
         <v>0.47977440893359702</v>
       </c>
-      <c r="E124" s="24">
+      <c r="E124" s="14">
         <v>0.12934063423268699</v>
       </c>
-      <c r="F124" s="24">
+      <c r="F124" s="14">
         <v>6.0934169575949902E-3</v>
       </c>
-      <c r="G124" s="24">
+      <c r="G124" s="14">
         <v>1.23386696791896</v>
       </c>
-      <c r="H124" s="24">
+      <c r="H124" s="14">
         <v>0.12599548534044899</v>
       </c>
-      <c r="I124" s="25">
+      <c r="I124" s="23">
         <v>6.7787278061260794E-2</v>
       </c>
-      <c r="J124" s="25">
+      <c r="J124" s="23">
         <v>7.3050647594953E-3</v>
       </c>
-      <c r="K124" s="24">
+      <c r="K124" s="14">
         <v>0.40238400643148597</v>
       </c>
       <c r="L124" s="15">
@@ -6765,37 +6753,37 @@
       </c>
     </row>
     <row r="125" spans="1:12">
-      <c r="A125" s="22" t="s">
+      <c r="A125" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="B125" s="22" t="s">
+      <c r="B125" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C125" s="23">
+      <c r="C125" s="22">
         <v>8.7801010995132298</v>
       </c>
-      <c r="D125" s="23">
+      <c r="D125" s="22">
         <v>0.703837280058076</v>
       </c>
-      <c r="E125" s="24">
+      <c r="E125" s="14">
         <v>0.130048040631384</v>
       </c>
-      <c r="F125" s="24">
+      <c r="F125" s="14">
         <v>7.3107546587188096E-3</v>
       </c>
-      <c r="G125" s="24">
+      <c r="G125" s="14">
         <v>1.4856439645370301</v>
       </c>
-      <c r="H125" s="24">
+      <c r="H125" s="14">
         <v>0.12897516695119601</v>
       </c>
-      <c r="I125" s="25">
+      <c r="I125" s="23">
         <v>8.3998345847869194E-2</v>
       </c>
-      <c r="J125" s="25">
+      <c r="J125" s="23">
         <v>8.6906241328943493E-3</v>
       </c>
-      <c r="K125" s="24">
+      <c r="K125" s="14">
         <v>0.399895799504149</v>
       </c>
       <c r="L125" s="15">
@@ -6803,37 +6791,37 @@
       </c>
     </row>
     <row r="126" spans="1:12">
-      <c r="A126" s="22" t="s">
+      <c r="A126" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="B126" s="22" t="s">
+      <c r="B126" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C126" s="23">
+      <c r="C126" s="22">
         <v>8.4168143127732797</v>
       </c>
-      <c r="D126" s="23">
+      <c r="D126" s="22">
         <v>0.52876985267842902</v>
       </c>
-      <c r="E126" s="24">
+      <c r="E126" s="14">
         <v>0.130218184751765</v>
       </c>
-      <c r="F126" s="24">
+      <c r="F126" s="14">
         <v>6.1080006884965798E-3</v>
       </c>
-      <c r="G126" s="24">
+      <c r="G126" s="14">
         <v>1.41711903458388</v>
       </c>
-      <c r="H126" s="24">
+      <c r="H126" s="14">
         <v>0.12138798885716399</v>
       </c>
-      <c r="I126" s="25">
+      <c r="I126" s="23">
         <v>7.9600816730821797E-2</v>
       </c>
-      <c r="J126" s="25">
+      <c r="J126" s="23">
         <v>7.4146774781893299E-3</v>
       </c>
-      <c r="K126" s="24">
+      <c r="K126" s="14">
         <v>0.30759179147019999</v>
       </c>
       <c r="L126" s="15">
@@ -6841,44 +6829,44 @@
       </c>
     </row>
     <row r="127" spans="1:12">
-      <c r="A127" s="22" t="s">
+      <c r="A127" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="B127" s="22" t="s">
+      <c r="B127" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C127" s="23">
+      <c r="C127" s="22">
         <v>7.2333064163672498</v>
       </c>
-      <c r="D127" s="23">
+      <c r="D127" s="22">
         <v>0.30540885987741201</v>
       </c>
-      <c r="E127" s="24">
+      <c r="E127" s="14">
         <v>0.14097557871435301</v>
       </c>
-      <c r="F127" s="24">
+      <c r="F127" s="14">
         <v>5.5701923174270402E-3</v>
       </c>
-      <c r="G127" s="24">
+      <c r="G127" s="14">
         <v>1.5553122232407901</v>
       </c>
-      <c r="H127" s="24">
+      <c r="H127" s="14">
         <v>0.13214843008308999</v>
       </c>
-      <c r="I127" s="25">
+      <c r="I127" s="23">
         <v>7.6198837103467004E-2</v>
       </c>
-      <c r="J127" s="25">
+      <c r="J127" s="23">
         <v>6.9179938898318999E-3</v>
       </c>
-      <c r="K127" s="24">
+      <c r="K127" s="14">
         <v>0.30006170300031598</v>
       </c>
       <c r="L127" s="15">
         <v>0.106525484140246</v>
       </c>
     </row>
-    <row r="128" spans="1:12" s="28" customFormat="1">
+    <row r="128" spans="1:12">
       <c r="A128" s="19" t="s">
         <v>150</v>
       </c>
@@ -6920,50 +6908,50 @@
       <c r="A129" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B129" s="26"/>
-      <c r="C129" s="27"/>
-      <c r="D129" s="27"/>
-      <c r="E129" s="27"/>
-      <c r="F129" s="27"/>
-      <c r="G129" s="27"/>
-      <c r="H129" s="27"/>
-      <c r="I129" s="27"/>
-      <c r="J129" s="27"/>
-      <c r="K129" s="27"/>
+      <c r="B129" s="13"/>
+      <c r="C129" s="7"/>
+      <c r="D129" s="7"/>
+      <c r="E129" s="7"/>
+      <c r="F129" s="7"/>
+      <c r="G129" s="7"/>
+      <c r="H129" s="7"/>
+      <c r="I129" s="7"/>
+      <c r="J129" s="7"/>
+      <c r="K129" s="7"/>
       <c r="L129" s="8"/>
     </row>
     <row r="130" spans="1:12">
-      <c r="A130" s="22" t="s">
+      <c r="A130" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="B130" s="22" t="s">
+      <c r="B130" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C130" s="24">
+      <c r="C130" s="14">
         <v>6.3298163949999999</v>
       </c>
-      <c r="D130" s="24">
+      <c r="D130" s="14">
         <v>0.14557653600000001</v>
       </c>
-      <c r="E130" s="24">
+      <c r="E130" s="14">
         <v>0.15700777972947899</v>
       </c>
-      <c r="F130" s="24">
+      <c r="F130" s="14">
         <v>3.7948519527287701E-3</v>
       </c>
-      <c r="G130" s="24">
+      <c r="G130" s="14">
         <v>19.8235050598011</v>
       </c>
-      <c r="H130" s="24">
+      <c r="H130" s="14">
         <v>0.36946595225297901</v>
       </c>
-      <c r="I130" s="25">
+      <c r="I130" s="23">
         <v>0.91821928399999997</v>
       </c>
-      <c r="J130" s="25">
+      <c r="J130" s="23">
         <v>1.180313E-2</v>
       </c>
-      <c r="K130" s="24">
+      <c r="K130" s="14">
         <v>0.38174102399999998</v>
       </c>
       <c r="L130" s="15">
@@ -6971,37 +6959,37 @@
       </c>
     </row>
     <row r="131" spans="1:12">
-      <c r="A131" s="22" t="s">
+      <c r="A131" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="B131" s="22" t="s">
+      <c r="B131" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C131" s="24">
+      <c r="C131" s="14">
         <v>6.5217738120000002</v>
       </c>
-      <c r="D131" s="24">
+      <c r="D131" s="14">
         <v>0.16590663999999999</v>
       </c>
-      <c r="E131" s="24">
+      <c r="E131" s="14">
         <v>0.15360807742216001</v>
       </c>
-      <c r="F131" s="24">
+      <c r="F131" s="14">
         <v>3.99357939874801E-3</v>
       </c>
-      <c r="G131" s="24">
+      <c r="G131" s="14">
         <v>19.199408763544501</v>
       </c>
-      <c r="H131" s="24">
+      <c r="H131" s="14">
         <v>0.37466631408831502</v>
       </c>
-      <c r="I131" s="25">
+      <c r="I131" s="23">
         <v>0.90946470700000004</v>
       </c>
-      <c r="J131" s="25">
+      <c r="J131" s="23">
         <v>1.4325905E-2</v>
       </c>
-      <c r="K131" s="24">
+      <c r="K131" s="14">
         <v>0.49174786199999998</v>
       </c>
       <c r="L131" s="15">
@@ -7009,37 +6997,37 @@
       </c>
     </row>
     <row r="132" spans="1:12">
-      <c r="A132" s="22" t="s">
+      <c r="A132" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="B132" s="22" t="s">
+      <c r="B132" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C132" s="24">
+      <c r="C132" s="14">
         <v>6.4438622690000003</v>
       </c>
-      <c r="D132" s="24">
+      <c r="D132" s="14">
         <v>0.181489657</v>
       </c>
-      <c r="E132" s="24">
+      <c r="E132" s="14">
         <v>0.15959888430768701</v>
       </c>
-      <c r="F132" s="24">
+      <c r="F132" s="14">
         <v>4.6852918652070504E-3</v>
       </c>
-      <c r="G132" s="24">
+      <c r="G132" s="14">
         <v>19.990330612151801</v>
       </c>
-      <c r="H132" s="24">
+      <c r="H132" s="14">
         <v>0.39518865067709102</v>
       </c>
-      <c r="I132" s="25">
+      <c r="I132" s="23">
         <v>0.92480568799999996</v>
       </c>
-      <c r="J132" s="25">
+      <c r="J132" s="23">
         <v>1.4249532000000001E-2</v>
       </c>
-      <c r="K132" s="24">
+      <c r="K132" s="14">
         <v>0.58812741800000001</v>
       </c>
       <c r="L132" s="15">
@@ -7047,37 +7035,37 @@
       </c>
     </row>
     <row r="133" spans="1:12">
-      <c r="A133" s="22" t="s">
+      <c r="A133" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="B133" s="22" t="s">
+      <c r="B133" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C133" s="24">
+      <c r="C133" s="14">
         <v>6.3424107379999999</v>
       </c>
-      <c r="D133" s="24">
+      <c r="D133" s="14">
         <v>0.14771427100000001</v>
       </c>
-      <c r="E133" s="24">
+      <c r="E133" s="14">
         <v>0.15972216181750301</v>
       </c>
-      <c r="F133" s="24">
+      <c r="F133" s="14">
         <v>3.8374218147892202E-3</v>
       </c>
-      <c r="G133" s="24">
+      <c r="G133" s="14">
         <v>19.9775086065954</v>
       </c>
-      <c r="H133" s="24">
+      <c r="H133" s="14">
         <v>0.37941701436807701</v>
       </c>
-      <c r="I133" s="25">
+      <c r="I133" s="23">
         <v>0.91430466799999999</v>
       </c>
-      <c r="J133" s="25">
+      <c r="J133" s="23">
         <v>1.1297652E-2</v>
       </c>
-      <c r="K133" s="24">
+      <c r="K133" s="14">
         <v>0.38772537499999998</v>
       </c>
       <c r="L133" s="15">
@@ -7085,37 +7073,37 @@
       </c>
     </row>
     <row r="134" spans="1:12">
-      <c r="A134" s="22" t="s">
+      <c r="A134" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="B134" s="22" t="s">
+      <c r="B134" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C134" s="24">
+      <c r="C134" s="14">
         <v>5.8391629949999997</v>
       </c>
-      <c r="D134" s="24">
+      <c r="D134" s="14">
         <v>0.14266177799999999</v>
       </c>
-      <c r="E134" s="24">
+      <c r="E134" s="14">
         <v>0.174172790462326</v>
       </c>
-      <c r="F134" s="24">
+      <c r="F134" s="14">
         <v>4.4461984341801703E-3</v>
       </c>
-      <c r="G134" s="24">
+      <c r="G134" s="14">
         <v>21.427962880986101</v>
       </c>
-      <c r="H134" s="24">
+      <c r="H134" s="14">
         <v>0.39614645982038699</v>
       </c>
-      <c r="I134" s="25">
+      <c r="I134" s="23">
         <v>0.90688678700000003</v>
       </c>
-      <c r="J134" s="25">
+      <c r="J134" s="23">
         <v>1.273495E-2</v>
       </c>
-      <c r="K134" s="24">
+      <c r="K134" s="14">
         <v>0.45111948499999999</v>
       </c>
       <c r="L134" s="15">
@@ -7123,37 +7111,37 @@
       </c>
     </row>
     <row r="135" spans="1:12">
-      <c r="A135" s="22" t="s">
+      <c r="A135" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="B135" s="22" t="s">
+      <c r="B135" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C135" s="24">
+      <c r="C135" s="14">
         <v>5.9810989609999998</v>
       </c>
-      <c r="D135" s="24">
+      <c r="D135" s="14">
         <v>0.164504127</v>
       </c>
-      <c r="E135" s="24">
+      <c r="E135" s="14">
         <v>0.171025881918489</v>
       </c>
-      <c r="F135" s="24">
+      <c r="F135" s="14">
         <v>4.9131555240562799E-3</v>
       </c>
-      <c r="G135" s="24">
+      <c r="G135" s="14">
         <v>21.402665292823901</v>
       </c>
-      <c r="H135" s="24">
+      <c r="H135" s="14">
         <v>0.40937271620586202</v>
       </c>
-      <c r="I135" s="25">
+      <c r="I135" s="23">
         <v>0.91942860999999998</v>
       </c>
-      <c r="J135" s="25">
+      <c r="J135" s="23">
         <v>1.6824262E-2</v>
       </c>
-      <c r="K135" s="24">
+      <c r="K135" s="14">
         <v>0.60103450700000005</v>
       </c>
       <c r="L135" s="15">
@@ -7161,37 +7149,37 @@
       </c>
     </row>
     <row r="136" spans="1:12">
-      <c r="A136" s="22" t="s">
+      <c r="A136" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="B136" s="22" t="s">
+      <c r="B136" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C136" s="24">
+      <c r="C136" s="14">
         <v>6.2929802910000001</v>
       </c>
-      <c r="D136" s="24">
+      <c r="D136" s="14">
         <v>0.175201669</v>
       </c>
-      <c r="E136" s="24">
+      <c r="E136" s="14">
         <v>0.15822391625565599</v>
       </c>
-      <c r="F136" s="24">
+      <c r="F136" s="14">
         <v>4.3163856315502598E-3</v>
       </c>
-      <c r="G136" s="24">
+      <c r="G136" s="14">
         <v>19.6949709610867</v>
       </c>
-      <c r="H136" s="24">
+      <c r="H136" s="14">
         <v>0.39152955763078201</v>
       </c>
-      <c r="I136" s="25">
+      <c r="I136" s="23">
         <v>0.90855618900000001</v>
       </c>
-      <c r="J136" s="25">
+      <c r="J136" s="23">
         <v>1.4718267E-2</v>
       </c>
-      <c r="K136" s="24">
+      <c r="K136" s="14">
         <v>0.56874997299999996</v>
       </c>
       <c r="L136" s="15">
@@ -7199,37 +7187,37 @@
       </c>
     </row>
     <row r="137" spans="1:12">
-      <c r="A137" s="22" t="s">
+      <c r="A137" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="B137" s="22" t="s">
+      <c r="B137" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C137" s="24">
+      <c r="C137" s="14">
         <v>6.1641441410000004</v>
       </c>
-      <c r="D137" s="24">
+      <c r="D137" s="14">
         <v>0.17857735199999999</v>
       </c>
-      <c r="E137" s="24">
+      <c r="E137" s="14">
         <v>0.16584309573474901</v>
       </c>
-      <c r="F137" s="24">
+      <c r="F137" s="14">
         <v>4.9202977276585798E-3</v>
       </c>
-      <c r="G137" s="24">
+      <c r="G137" s="14">
         <v>20.535801591800599</v>
       </c>
-      <c r="H137" s="24">
+      <c r="H137" s="14">
         <v>0.41147026061534803</v>
       </c>
-      <c r="I137" s="25">
+      <c r="I137" s="23">
         <v>0.91165470100000001</v>
       </c>
-      <c r="J137" s="25">
+      <c r="J137" s="23">
         <v>1.8840091999999999E-2</v>
       </c>
-      <c r="K137" s="24">
+      <c r="K137" s="14">
         <v>0.64819179800000004</v>
       </c>
       <c r="L137" s="15">
@@ -7237,37 +7225,37 @@
       </c>
     </row>
     <row r="138" spans="1:12">
-      <c r="A138" s="22" t="s">
+      <c r="A138" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="B138" s="22" t="s">
+      <c r="B138" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C138" s="24">
+      <c r="C138" s="14">
         <v>5.5449699260000003</v>
       </c>
-      <c r="D138" s="24">
+      <c r="D138" s="14">
         <v>0.153585473</v>
       </c>
-      <c r="E138" s="24">
+      <c r="E138" s="14">
         <v>0.18105682264464901</v>
       </c>
-      <c r="F138" s="24">
+      <c r="F138" s="14">
         <v>4.9121934802793003E-3</v>
       </c>
-      <c r="G138" s="24">
+      <c r="G138" s="14">
         <v>22.536929890300598</v>
       </c>
-      <c r="H138" s="24">
+      <c r="H138" s="14">
         <v>0.43430164809699201</v>
       </c>
-      <c r="I138" s="25">
+      <c r="I138" s="23">
         <v>0.90852234700000001</v>
       </c>
-      <c r="J138" s="25">
+      <c r="J138" s="23">
         <v>1.6861592000000002E-2</v>
       </c>
-      <c r="K138" s="24">
+      <c r="K138" s="14">
         <v>0.58833849999999999</v>
       </c>
       <c r="L138" s="15">
@@ -7275,37 +7263,37 @@
       </c>
     </row>
     <row r="139" spans="1:12">
-      <c r="A139" s="22" t="s">
+      <c r="A139" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="B139" s="22" t="s">
+      <c r="B139" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C139" s="24">
+      <c r="C139" s="14">
         <v>6.017814006</v>
       </c>
-      <c r="D139" s="24">
+      <c r="D139" s="14">
         <v>0.169812822</v>
       </c>
-      <c r="E139" s="24">
+      <c r="E139" s="14">
         <v>0.169454769721851</v>
       </c>
-      <c r="F139" s="24">
+      <c r="F139" s="14">
         <v>4.7330154768201703E-3</v>
       </c>
-      <c r="G139" s="24">
+      <c r="G139" s="14">
         <v>21.331752527049201</v>
       </c>
-      <c r="H139" s="24">
+      <c r="H139" s="14">
         <v>0.40140226985517602</v>
       </c>
-      <c r="I139" s="25">
+      <c r="I139" s="23">
         <v>0.92496986299999995</v>
       </c>
-      <c r="J139" s="25">
+      <c r="J139" s="23">
         <v>1.6840114999999999E-2</v>
       </c>
-      <c r="K139" s="24">
+      <c r="K139" s="14">
         <v>0.62593702600000001</v>
       </c>
       <c r="L139" s="15">
@@ -7313,37 +7301,37 @@
       </c>
     </row>
     <row r="140" spans="1:12">
-      <c r="A140" s="22" t="s">
+      <c r="A140" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="B140" s="22" t="s">
+      <c r="B140" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C140" s="24">
+      <c r="C140" s="14">
         <v>6.7591174939999998</v>
       </c>
-      <c r="D140" s="24">
+      <c r="D140" s="14">
         <v>0.17366257199999999</v>
       </c>
-      <c r="E140" s="24">
+      <c r="E140" s="14">
         <v>0.148130089721312</v>
       </c>
-      <c r="F140" s="24">
+      <c r="F140" s="14">
         <v>3.96193922284418E-3</v>
       </c>
-      <c r="G140" s="24">
+      <c r="G140" s="14">
         <v>18.642969601628099</v>
       </c>
-      <c r="H140" s="24">
+      <c r="H140" s="14">
         <v>0.33622623910234201</v>
       </c>
-      <c r="I140" s="25">
+      <c r="I140" s="23">
         <v>0.92623064600000005</v>
       </c>
-      <c r="J140" s="25">
+      <c r="J140" s="23">
         <v>1.5994436000000001E-2</v>
       </c>
-      <c r="K140" s="24">
+      <c r="K140" s="14">
         <v>0.57978835699999998</v>
       </c>
       <c r="L140" s="15">
@@ -7351,37 +7339,37 @@
       </c>
     </row>
     <row r="141" spans="1:12">
-      <c r="A141" s="22" t="s">
+      <c r="A141" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="B141" s="22" t="s">
+      <c r="B141" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C141" s="24">
+      <c r="C141" s="14">
         <v>5.7110123809999997</v>
       </c>
-      <c r="D141" s="24">
+      <c r="D141" s="14">
         <v>0.16131188299999999</v>
       </c>
-      <c r="E141" s="24">
+      <c r="E141" s="14">
         <v>0.173817328101529</v>
       </c>
-      <c r="F141" s="24">
+      <c r="F141" s="14">
         <v>4.92757193057869E-3</v>
       </c>
-      <c r="G141" s="24">
+      <c r="G141" s="14">
         <v>21.817923034040899</v>
       </c>
-      <c r="H141" s="24">
+      <c r="H141" s="14">
         <v>0.44351203906536302</v>
       </c>
-      <c r="I141" s="25">
+      <c r="I141" s="23">
         <v>0.90360881800000004</v>
       </c>
-      <c r="J141" s="25">
+      <c r="J141" s="23">
         <v>1.4470703E-2</v>
       </c>
-      <c r="K141" s="24">
+      <c r="K141" s="14">
         <v>0.60244334300000002</v>
       </c>
       <c r="L141" s="15">
@@ -7389,37 +7377,37 @@
       </c>
     </row>
     <row r="142" spans="1:12">
-      <c r="A142" s="22" t="s">
+      <c r="A142" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="B142" s="22" t="s">
+      <c r="B142" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C142" s="24">
+      <c r="C142" s="14">
         <v>5.9058362889999998</v>
       </c>
-      <c r="D142" s="24">
+      <c r="D142" s="14">
         <v>0.17625711599999999</v>
       </c>
-      <c r="E142" s="24">
+      <c r="E142" s="14">
         <v>0.17097673987304199</v>
       </c>
-      <c r="F142" s="24">
+      <c r="F142" s="14">
         <v>5.1650298338698801E-3</v>
       </c>
-      <c r="G142" s="24">
+      <c r="G142" s="14">
         <v>21.484940328728801</v>
       </c>
-      <c r="H142" s="24">
+      <c r="H142" s="14">
         <v>0.46056471639632102</v>
       </c>
-      <c r="I142" s="25">
+      <c r="I142" s="23">
         <v>0.92078461300000003</v>
       </c>
-      <c r="J142" s="25">
+      <c r="J142" s="23">
         <v>1.9106699000000001E-2</v>
       </c>
-      <c r="K142" s="24">
+      <c r="K142" s="14">
         <v>0.57818401100000005</v>
       </c>
       <c r="L142" s="15">
@@ -7427,37 +7415,37 @@
       </c>
     </row>
     <row r="143" spans="1:12">
-      <c r="A143" s="22" t="s">
+      <c r="A143" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="B143" s="22" t="s">
+      <c r="B143" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C143" s="24">
+      <c r="C143" s="14">
         <v>5.7875499149999996</v>
       </c>
-      <c r="D143" s="24">
+      <c r="D143" s="14">
         <v>0.14761761000000001</v>
       </c>
-      <c r="E143" s="24">
+      <c r="E143" s="14">
         <v>0.17243299057765199</v>
       </c>
-      <c r="F143" s="24">
+      <c r="F143" s="14">
         <v>4.36762289273478E-3</v>
       </c>
-      <c r="G143" s="24">
+      <c r="G143" s="14">
         <v>21.645921448587799</v>
       </c>
-      <c r="H143" s="24">
+      <c r="H143" s="14">
         <v>0.413433331009814</v>
       </c>
-      <c r="I143" s="25">
+      <c r="I143" s="23">
         <v>0.91435843699999997</v>
       </c>
-      <c r="J143" s="25">
+      <c r="J143" s="23">
         <v>1.5376772E-2</v>
       </c>
-      <c r="K143" s="24">
+      <c r="K143" s="14">
         <v>0.50557870100000002</v>
       </c>
       <c r="L143" s="15">
@@ -7465,37 +7453,37 @@
       </c>
     </row>
     <row r="144" spans="1:12">
-      <c r="A144" s="22" t="s">
+      <c r="A144" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="B144" s="22" t="s">
+      <c r="B144" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C144" s="24">
+      <c r="C144" s="14">
         <v>6.4138355909999998</v>
       </c>
-      <c r="D144" s="24">
+      <c r="D144" s="14">
         <v>0.16814795299999999</v>
       </c>
-      <c r="E144" s="24">
+      <c r="E144" s="14">
         <v>0.160016261055523</v>
       </c>
-      <c r="F144" s="24">
+      <c r="F144" s="14">
         <v>4.4830704000538499E-3</v>
       </c>
-      <c r="G144" s="24">
+      <c r="G144" s="14">
         <v>19.787761132159201</v>
       </c>
-      <c r="H144" s="24">
+      <c r="H144" s="14">
         <v>0.38264441949331801</v>
       </c>
-      <c r="I144" s="25">
+      <c r="I144" s="23">
         <v>0.91111993300000005</v>
       </c>
-      <c r="J144" s="25">
+      <c r="J144" s="23">
         <v>1.4329356E-2</v>
       </c>
-      <c r="K144" s="24">
+      <c r="K144" s="14">
         <v>0.55807356500000005</v>
       </c>
       <c r="L144" s="15">
@@ -7503,37 +7491,37 @@
       </c>
     </row>
     <row r="145" spans="1:12">
-      <c r="A145" s="22" t="s">
+      <c r="A145" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="B145" s="22" t="s">
+      <c r="B145" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C145" s="24">
+      <c r="C145" s="14">
         <v>6.2994188150000001</v>
       </c>
-      <c r="D145" s="24">
+      <c r="D145" s="14">
         <v>0.15342167400000001</v>
       </c>
-      <c r="E145" s="24">
+      <c r="E145" s="14">
         <v>0.161101229504894</v>
       </c>
-      <c r="F145" s="24">
+      <c r="F145" s="14">
         <v>3.9158927355547601E-3</v>
       </c>
-      <c r="G145" s="24">
+      <c r="G145" s="14">
         <v>20.102054772783902</v>
       </c>
-      <c r="H145" s="24">
+      <c r="H145" s="14">
         <v>0.35880442236813398</v>
       </c>
-      <c r="I145" s="25">
+      <c r="I145" s="23">
         <v>0.91025799600000001</v>
       </c>
-      <c r="J145" s="25">
+      <c r="J145" s="23">
         <v>1.3832176E-2</v>
       </c>
-      <c r="K145" s="24">
+      <c r="K145" s="14">
         <v>0.53744708799999996</v>
       </c>
       <c r="L145" s="15">
@@ -7541,37 +7529,37 @@
       </c>
     </row>
     <row r="146" spans="1:12">
-      <c r="A146" s="22" t="s">
+      <c r="A146" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="B146" s="22" t="s">
+      <c r="B146" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C146" s="24">
+      <c r="C146" s="14">
         <v>6.1778617069999999</v>
       </c>
-      <c r="D146" s="24">
+      <c r="D146" s="14">
         <v>0.168864236</v>
       </c>
-      <c r="E146" s="24">
+      <c r="E146" s="14">
         <v>0.16511366419127901</v>
       </c>
-      <c r="F146" s="24">
+      <c r="F146" s="14">
         <v>4.6610869823423403E-3</v>
       </c>
-      <c r="G146" s="24">
+      <c r="G146" s="14">
         <v>20.338012951446299</v>
       </c>
-      <c r="H146" s="24">
+      <c r="H146" s="14">
         <v>0.38850255337650702</v>
       </c>
-      <c r="I146" s="25">
+      <c r="I146" s="23">
         <v>0.89821585599999998</v>
       </c>
-      <c r="J146" s="25">
+      <c r="J146" s="23">
         <v>1.4506216000000001E-2</v>
       </c>
-      <c r="K146" s="24">
+      <c r="K146" s="14">
         <v>0.58497260500000003</v>
       </c>
       <c r="L146" s="15">
@@ -7579,37 +7567,37 @@
       </c>
     </row>
     <row r="147" spans="1:12">
-      <c r="A147" s="22" t="s">
+      <c r="A147" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B147" s="22" t="s">
+      <c r="B147" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C147" s="24">
+      <c r="C147" s="14">
         <v>5.6672114569999996</v>
       </c>
-      <c r="D147" s="24">
+      <c r="D147" s="14">
         <v>0.144873205</v>
       </c>
-      <c r="E147" s="24">
+      <c r="E147" s="14">
         <v>0.17615898773255301</v>
       </c>
-      <c r="F147" s="24">
+      <c r="F147" s="14">
         <v>4.4600669946356199E-3</v>
       </c>
-      <c r="G147" s="24">
+      <c r="G147" s="14">
         <v>22.1350195212868</v>
       </c>
-      <c r="H147" s="24">
+      <c r="H147" s="14">
         <v>0.41912937739148898</v>
       </c>
-      <c r="I147" s="25">
+      <c r="I147" s="23">
         <v>0.902395905</v>
       </c>
-      <c r="J147" s="25">
+      <c r="J147" s="23">
         <v>1.5911636E-2</v>
       </c>
-      <c r="K147" s="24">
+      <c r="K147" s="14">
         <v>0.54069485699999997</v>
       </c>
       <c r="L147" s="15">
@@ -7617,37 +7605,37 @@
       </c>
     </row>
     <row r="148" spans="1:12">
-      <c r="A148" s="22" t="s">
+      <c r="A148" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="B148" s="22" t="s">
+      <c r="B148" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C148" s="24">
+      <c r="C148" s="14">
         <v>5.6059928120000002</v>
       </c>
-      <c r="D148" s="24">
+      <c r="D148" s="14">
         <v>0.13212817199999999</v>
       </c>
-      <c r="E148" s="24">
+      <c r="E148" s="14">
         <v>0.18016621797465199</v>
       </c>
-      <c r="F148" s="24">
+      <c r="F148" s="14">
         <v>4.4369512470230502E-3</v>
       </c>
-      <c r="G148" s="24">
+      <c r="G148" s="14">
         <v>22.476155370989702</v>
       </c>
-      <c r="H148" s="24">
+      <c r="H148" s="14">
         <v>0.438407002550741</v>
       </c>
-      <c r="I148" s="25">
+      <c r="I148" s="23">
         <v>0.91250376099999997</v>
       </c>
-      <c r="J148" s="25">
+      <c r="J148" s="23">
         <v>1.3768519999999999E-2</v>
       </c>
-      <c r="K148" s="24">
+      <c r="K148" s="14">
         <v>0.47270136600000001</v>
       </c>
       <c r="L148" s="15">
@@ -7655,37 +7643,37 @@
       </c>
     </row>
     <row r="149" spans="1:12">
-      <c r="A149" s="22" t="s">
+      <c r="A149" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="B149" s="22" t="s">
+      <c r="B149" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C149" s="24">
+      <c r="C149" s="14">
         <v>5.4013507409999999</v>
       </c>
-      <c r="D149" s="24">
+      <c r="D149" s="14">
         <v>0.142327379</v>
       </c>
-      <c r="E149" s="24">
+      <c r="E149" s="14">
         <v>0.182615217442024</v>
       </c>
-      <c r="F149" s="24">
+      <c r="F149" s="14">
         <v>4.9434489229017303E-3</v>
       </c>
-      <c r="G149" s="24">
+      <c r="G149" s="14">
         <v>22.781094827515599</v>
       </c>
-      <c r="H149" s="24">
+      <c r="H149" s="14">
         <v>0.51733957789256502</v>
       </c>
-      <c r="I149" s="25">
+      <c r="I149" s="23">
         <v>0.91026348199999996</v>
       </c>
-      <c r="J149" s="25">
+      <c r="J149" s="23">
         <v>1.5243596999999999E-2</v>
       </c>
-      <c r="K149" s="24">
+      <c r="K149" s="14">
         <v>0.47567710800000002</v>
       </c>
       <c r="L149" s="15">
@@ -7693,37 +7681,37 @@
       </c>
     </row>
     <row r="150" spans="1:12">
-      <c r="A150" s="22" t="s">
+      <c r="A150" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="B150" s="22" t="s">
+      <c r="B150" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C150" s="24">
+      <c r="C150" s="14">
         <v>6.0550669580000003</v>
       </c>
-      <c r="D150" s="24">
+      <c r="D150" s="14">
         <v>0.16367294600000001</v>
       </c>
-      <c r="E150" s="24">
+      <c r="E150" s="14">
         <v>0.16805447400436399</v>
       </c>
-      <c r="F150" s="24">
+      <c r="F150" s="14">
         <v>4.7078106075379997E-3</v>
       </c>
-      <c r="G150" s="24">
+      <c r="G150" s="14">
         <v>20.792663248707701</v>
       </c>
-      <c r="H150" s="24">
+      <c r="H150" s="14">
         <v>0.39316046501549901</v>
       </c>
-      <c r="I150" s="25">
+      <c r="I150" s="23">
         <v>0.91853715499999999</v>
       </c>
-      <c r="J150" s="25">
+      <c r="J150" s="23">
         <v>1.7680675E-2</v>
       </c>
-      <c r="K150" s="24">
+      <c r="K150" s="14">
         <v>0.63239387599999997</v>
       </c>
       <c r="L150" s="15">
@@ -7731,37 +7719,37 @@
       </c>
     </row>
     <row r="151" spans="1:12">
-      <c r="A151" s="22" t="s">
+      <c r="A151" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="B151" s="22" t="s">
+      <c r="B151" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C151" s="24">
+      <c r="C151" s="14">
         <v>6.6439189020000002</v>
       </c>
-      <c r="D151" s="24">
+      <c r="D151" s="14">
         <v>0.204186584</v>
       </c>
-      <c r="E151" s="24">
+      <c r="E151" s="14">
         <v>0.153977336191467</v>
       </c>
-      <c r="F151" s="24">
+      <c r="F151" s="14">
         <v>4.6634274085396903E-3</v>
       </c>
-      <c r="G151" s="24">
+      <c r="G151" s="14">
         <v>19.101421611134501</v>
       </c>
-      <c r="H151" s="24">
+      <c r="H151" s="14">
         <v>0.483954737877337</v>
       </c>
-      <c r="I151" s="25">
+      <c r="I151" s="23">
         <v>0.91428005000000001</v>
       </c>
-      <c r="J151" s="25">
+      <c r="J151" s="23">
         <v>1.5670973000000001E-2</v>
       </c>
-      <c r="K151" s="24">
+      <c r="K151" s="14">
         <v>0.45074490299999997</v>
       </c>
       <c r="L151" s="15">
@@ -7769,37 +7757,37 @@
       </c>
     </row>
     <row r="152" spans="1:12">
-      <c r="A152" s="22" t="s">
+      <c r="A152" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="B152" s="22" t="s">
+      <c r="B152" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C152" s="24">
+      <c r="C152" s="14">
         <v>6.5151959550000003</v>
       </c>
-      <c r="D152" s="24">
+      <c r="D152" s="14">
         <v>0.195994796</v>
       </c>
-      <c r="E152" s="24">
+      <c r="E152" s="14">
         <v>0.15650218953853201</v>
       </c>
-      <c r="F152" s="24">
+      <c r="F152" s="14">
         <v>4.8289625519440703E-3</v>
       </c>
-      <c r="G152" s="24">
+      <c r="G152" s="14">
         <v>19.221139013267699</v>
       </c>
-      <c r="H152" s="24">
+      <c r="H152" s="14">
         <v>0.54154389862730901</v>
       </c>
-      <c r="I152" s="25">
+      <c r="I152" s="23">
         <v>0.90001319000000002</v>
       </c>
-      <c r="J152" s="25">
+      <c r="J152" s="23">
         <v>1.3885305000000001E-2</v>
       </c>
-      <c r="K152" s="24">
+      <c r="K152" s="14">
         <v>0.23740915400000001</v>
       </c>
       <c r="L152" s="15">
@@ -7807,37 +7795,37 @@
       </c>
     </row>
     <row r="153" spans="1:12">
-      <c r="A153" s="22" t="s">
+      <c r="A153" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="B153" s="22" t="s">
+      <c r="B153" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C153" s="24">
+      <c r="C153" s="14">
         <v>5.8826438740000002</v>
       </c>
-      <c r="D153" s="24">
+      <c r="D153" s="14">
         <v>0.185298886</v>
       </c>
-      <c r="E153" s="24">
+      <c r="E153" s="14">
         <v>0.17345670123309001</v>
       </c>
-      <c r="F153" s="24">
+      <c r="F153" s="14">
         <v>5.5827391940642497E-3</v>
       </c>
-      <c r="G153" s="24">
+      <c r="G153" s="14">
         <v>21.851342784174701</v>
       </c>
-      <c r="H153" s="24">
+      <c r="H153" s="14">
         <v>0.61074958916600197</v>
       </c>
-      <c r="I153" s="25">
+      <c r="I153" s="23">
         <v>0.90676927100000004</v>
       </c>
-      <c r="J153" s="25">
+      <c r="J153" s="23">
         <v>1.4489854E-2</v>
       </c>
-      <c r="K153" s="24">
+      <c r="K153" s="14">
         <v>0.33077997999999997</v>
       </c>
       <c r="L153" s="15">
@@ -11888,7 +11876,7 @@
         <v>0.83560542500000001</v>
       </c>
     </row>
-    <row r="261" spans="1:12" s="28" customFormat="1">
+    <row r="261" spans="1:12">
       <c r="A261" s="19" t="s">
         <v>269</v>
       </c>
@@ -11926,3097 +11914,2665 @@
         <v>0.88352719099999999</v>
       </c>
     </row>
-    <row r="262" spans="1:12" s="28" customFormat="1">
-      <c r="C262" s="23"/>
-      <c r="D262" s="23"/>
-      <c r="E262" s="23"/>
-      <c r="F262" s="23"/>
-      <c r="G262" s="23"/>
-      <c r="H262" s="23"/>
-      <c r="I262" s="23"/>
-      <c r="J262" s="23"/>
-      <c r="K262" s="23"/>
-      <c r="L262" s="23"/>
+    <row r="262" spans="1:12">
+      <c r="C262" s="22"/>
+      <c r="D262" s="22"/>
+      <c r="E262" s="22"/>
+      <c r="F262" s="22"/>
+      <c r="G262" s="22"/>
+      <c r="H262" s="22"/>
+      <c r="I262" s="22"/>
+      <c r="J262" s="22"/>
+      <c r="K262" s="22"/>
+      <c r="L262" s="22"/>
     </row>
     <row r="263" spans="1:12">
-      <c r="A263" s="28"/>
-      <c r="B263" s="28"/>
-      <c r="C263" s="23"/>
-      <c r="D263" s="23"/>
-      <c r="E263" s="23"/>
-      <c r="F263" s="23"/>
-      <c r="G263" s="23"/>
-      <c r="H263" s="23"/>
-      <c r="I263" s="23"/>
-      <c r="J263" s="23"/>
-      <c r="K263" s="23"/>
-      <c r="L263" s="23"/>
+      <c r="C263" s="22"/>
+      <c r="D263" s="22"/>
+      <c r="E263" s="22"/>
+      <c r="F263" s="22"/>
+      <c r="G263" s="22"/>
+      <c r="H263" s="22"/>
+      <c r="I263" s="22"/>
+      <c r="J263" s="22"/>
+      <c r="K263" s="22"/>
+      <c r="L263" s="22"/>
     </row>
     <row r="264" spans="1:12">
-      <c r="A264" s="28"/>
-      <c r="B264" s="28"/>
-      <c r="C264" s="23"/>
-      <c r="D264" s="23"/>
-      <c r="E264" s="23"/>
-      <c r="F264" s="23"/>
-      <c r="G264" s="23"/>
-      <c r="H264" s="23"/>
-      <c r="I264" s="23"/>
-      <c r="J264" s="23"/>
-      <c r="K264" s="23"/>
-      <c r="L264" s="23"/>
+      <c r="C264" s="22"/>
+      <c r="D264" s="22"/>
+      <c r="E264" s="22"/>
+      <c r="F264" s="22"/>
+      <c r="G264" s="22"/>
+      <c r="H264" s="22"/>
+      <c r="I264" s="22"/>
+      <c r="J264" s="22"/>
+      <c r="K264" s="22"/>
+      <c r="L264" s="22"/>
     </row>
     <row r="265" spans="1:12">
-      <c r="A265" s="26"/>
-      <c r="B265" s="26"/>
-      <c r="C265" s="27"/>
-      <c r="D265" s="27"/>
-      <c r="E265" s="27"/>
-      <c r="F265" s="27"/>
-      <c r="G265" s="27"/>
-      <c r="H265" s="27"/>
-      <c r="I265" s="27"/>
-      <c r="J265" s="27"/>
-      <c r="K265" s="27"/>
-      <c r="L265" s="27"/>
+      <c r="A265" s="13"/>
+      <c r="B265" s="13"/>
+      <c r="C265" s="7"/>
+      <c r="D265" s="7"/>
+      <c r="E265" s="7"/>
+      <c r="F265" s="7"/>
+      <c r="G265" s="7"/>
+      <c r="H265" s="7"/>
+      <c r="I265" s="7"/>
+      <c r="J265" s="7"/>
+      <c r="K265" s="7"/>
+      <c r="L265" s="7"/>
     </row>
     <row r="266" spans="1:12">
-      <c r="A266" s="28"/>
-      <c r="B266" s="28"/>
-      <c r="C266" s="24"/>
-      <c r="D266" s="24"/>
-      <c r="E266" s="24"/>
-      <c r="F266" s="24"/>
-      <c r="G266" s="24"/>
-      <c r="H266" s="24"/>
-      <c r="I266" s="24"/>
-      <c r="J266" s="24"/>
-      <c r="K266" s="24"/>
-      <c r="L266" s="24"/>
+      <c r="C266" s="14"/>
+      <c r="D266" s="14"/>
+      <c r="E266" s="14"/>
+      <c r="F266" s="14"/>
+      <c r="G266" s="14"/>
+      <c r="H266" s="14"/>
+      <c r="I266" s="14"/>
+      <c r="J266" s="14"/>
+      <c r="K266" s="14"/>
+      <c r="L266" s="14"/>
     </row>
     <row r="267" spans="1:12">
-      <c r="A267" s="28"/>
-      <c r="B267" s="28"/>
-      <c r="C267" s="24"/>
-      <c r="D267" s="24"/>
-      <c r="E267" s="24"/>
-      <c r="F267" s="24"/>
-      <c r="G267" s="24"/>
-      <c r="H267" s="24"/>
-      <c r="I267" s="24"/>
-      <c r="J267" s="24"/>
-      <c r="K267" s="24"/>
-      <c r="L267" s="24"/>
+      <c r="C267" s="14"/>
+      <c r="D267" s="14"/>
+      <c r="E267" s="14"/>
+      <c r="F267" s="14"/>
+      <c r="G267" s="14"/>
+      <c r="H267" s="14"/>
+      <c r="I267" s="14"/>
+      <c r="J267" s="14"/>
+      <c r="K267" s="14"/>
+      <c r="L267" s="14"/>
     </row>
     <row r="268" spans="1:12">
-      <c r="A268" s="28"/>
-      <c r="B268" s="28"/>
-      <c r="C268" s="24"/>
-      <c r="D268" s="24"/>
-      <c r="E268" s="24"/>
-      <c r="F268" s="24"/>
-      <c r="G268" s="24"/>
-      <c r="H268" s="24"/>
-      <c r="I268" s="24"/>
-      <c r="J268" s="24"/>
-      <c r="K268" s="24"/>
-      <c r="L268" s="24"/>
+      <c r="C268" s="14"/>
+      <c r="D268" s="14"/>
+      <c r="E268" s="14"/>
+      <c r="F268" s="14"/>
+      <c r="G268" s="14"/>
+      <c r="H268" s="14"/>
+      <c r="I268" s="14"/>
+      <c r="J268" s="14"/>
+      <c r="K268" s="14"/>
+      <c r="L268" s="14"/>
     </row>
     <row r="269" spans="1:12">
-      <c r="A269" s="28"/>
-      <c r="B269" s="28"/>
-      <c r="C269" s="24"/>
-      <c r="D269" s="24"/>
-      <c r="E269" s="24"/>
-      <c r="F269" s="24"/>
-      <c r="G269" s="24"/>
-      <c r="H269" s="24"/>
-      <c r="I269" s="24"/>
-      <c r="J269" s="24"/>
-      <c r="K269" s="24"/>
-      <c r="L269" s="24"/>
+      <c r="C269" s="14"/>
+      <c r="D269" s="14"/>
+      <c r="E269" s="14"/>
+      <c r="F269" s="14"/>
+      <c r="G269" s="14"/>
+      <c r="H269" s="14"/>
+      <c r="I269" s="14"/>
+      <c r="J269" s="14"/>
+      <c r="K269" s="14"/>
+      <c r="L269" s="14"/>
     </row>
     <row r="270" spans="1:12">
-      <c r="A270" s="28"/>
-      <c r="B270" s="28"/>
-      <c r="C270" s="24"/>
-      <c r="D270" s="24"/>
-      <c r="E270" s="24"/>
-      <c r="F270" s="24"/>
-      <c r="G270" s="24"/>
-      <c r="H270" s="24"/>
-      <c r="I270" s="24"/>
-      <c r="J270" s="24"/>
-      <c r="K270" s="24"/>
-      <c r="L270" s="24"/>
+      <c r="C270" s="14"/>
+      <c r="D270" s="14"/>
+      <c r="E270" s="14"/>
+      <c r="F270" s="14"/>
+      <c r="G270" s="14"/>
+      <c r="H270" s="14"/>
+      <c r="I270" s="14"/>
+      <c r="J270" s="14"/>
+      <c r="K270" s="14"/>
+      <c r="L270" s="14"/>
     </row>
     <row r="271" spans="1:12">
-      <c r="A271" s="28"/>
-      <c r="B271" s="28"/>
-      <c r="C271" s="24"/>
-      <c r="D271" s="24"/>
-      <c r="E271" s="24"/>
-      <c r="F271" s="24"/>
-      <c r="G271" s="24"/>
-      <c r="H271" s="24"/>
-      <c r="I271" s="24"/>
-      <c r="J271" s="24"/>
-      <c r="K271" s="24"/>
-      <c r="L271" s="24"/>
+      <c r="C271" s="14"/>
+      <c r="D271" s="14"/>
+      <c r="E271" s="14"/>
+      <c r="F271" s="14"/>
+      <c r="G271" s="14"/>
+      <c r="H271" s="14"/>
+      <c r="I271" s="14"/>
+      <c r="J271" s="14"/>
+      <c r="K271" s="14"/>
+      <c r="L271" s="14"/>
     </row>
     <row r="272" spans="1:12">
-      <c r="A272" s="28"/>
-      <c r="B272" s="28"/>
-      <c r="C272" s="24"/>
-      <c r="D272" s="24"/>
-      <c r="E272" s="24"/>
-      <c r="F272" s="24"/>
-      <c r="G272" s="24"/>
-      <c r="H272" s="24"/>
-      <c r="I272" s="24"/>
-      <c r="J272" s="24"/>
-      <c r="K272" s="24"/>
-      <c r="L272" s="24"/>
-    </row>
-    <row r="273" spans="1:12">
-      <c r="A273" s="28"/>
-      <c r="B273" s="28"/>
-      <c r="C273" s="24"/>
-      <c r="D273" s="24"/>
-      <c r="E273" s="24"/>
-      <c r="F273" s="24"/>
-      <c r="G273" s="24"/>
-      <c r="H273" s="24"/>
-      <c r="I273" s="24"/>
-      <c r="J273" s="24"/>
-      <c r="K273" s="24"/>
-      <c r="L273" s="24"/>
-    </row>
-    <row r="274" spans="1:12">
-      <c r="A274" s="28"/>
-      <c r="B274" s="28"/>
-      <c r="C274" s="24"/>
-      <c r="D274" s="24"/>
-      <c r="E274" s="24"/>
-      <c r="F274" s="24"/>
-      <c r="G274" s="24"/>
-      <c r="H274" s="24"/>
-      <c r="I274" s="24"/>
-      <c r="J274" s="24"/>
-      <c r="K274" s="24"/>
-      <c r="L274" s="24"/>
-    </row>
-    <row r="275" spans="1:12">
-      <c r="A275" s="28"/>
-      <c r="B275" s="28"/>
-      <c r="C275" s="24"/>
-      <c r="D275" s="24"/>
-      <c r="E275" s="24"/>
-      <c r="F275" s="24"/>
-      <c r="G275" s="24"/>
-      <c r="H275" s="24"/>
-      <c r="I275" s="24"/>
-      <c r="J275" s="24"/>
-      <c r="K275" s="24"/>
-      <c r="L275" s="24"/>
-    </row>
-    <row r="276" spans="1:12">
-      <c r="A276" s="28"/>
-      <c r="B276" s="28"/>
-      <c r="C276" s="24"/>
-      <c r="D276" s="24"/>
-      <c r="E276" s="24"/>
-      <c r="F276" s="24"/>
-      <c r="G276" s="24"/>
-      <c r="H276" s="24"/>
-      <c r="I276" s="24"/>
-      <c r="J276" s="24"/>
-      <c r="K276" s="24"/>
-      <c r="L276" s="24"/>
-    </row>
-    <row r="277" spans="1:12">
-      <c r="A277" s="28"/>
-      <c r="B277" s="28"/>
-      <c r="C277" s="24"/>
-      <c r="D277" s="24"/>
-      <c r="E277" s="24"/>
-      <c r="F277" s="24"/>
-      <c r="G277" s="24"/>
-      <c r="H277" s="24"/>
-      <c r="I277" s="24"/>
-      <c r="J277" s="24"/>
-      <c r="K277" s="24"/>
-      <c r="L277" s="24"/>
-    </row>
-    <row r="278" spans="1:12">
-      <c r="A278" s="28"/>
-      <c r="B278" s="28"/>
-      <c r="C278" s="24"/>
-      <c r="D278" s="24"/>
-      <c r="E278" s="24"/>
-      <c r="F278" s="24"/>
-      <c r="G278" s="24"/>
-      <c r="H278" s="24"/>
-      <c r="I278" s="24"/>
-      <c r="J278" s="24"/>
-      <c r="K278" s="24"/>
-      <c r="L278" s="24"/>
-    </row>
-    <row r="279" spans="1:12">
-      <c r="A279" s="28"/>
-      <c r="B279" s="28"/>
-      <c r="C279" s="24"/>
-      <c r="D279" s="24"/>
-      <c r="E279" s="24"/>
-      <c r="F279" s="24"/>
-      <c r="G279" s="24"/>
-      <c r="H279" s="24"/>
-      <c r="I279" s="24"/>
-      <c r="J279" s="24"/>
-      <c r="K279" s="24"/>
-      <c r="L279" s="24"/>
-    </row>
-    <row r="280" spans="1:12">
-      <c r="A280" s="28"/>
-      <c r="B280" s="28"/>
-      <c r="C280" s="24"/>
-      <c r="D280" s="24"/>
-      <c r="E280" s="24"/>
-      <c r="F280" s="24"/>
-      <c r="G280" s="24"/>
-      <c r="H280" s="24"/>
-      <c r="I280" s="24"/>
-      <c r="J280" s="24"/>
-      <c r="K280" s="24"/>
-      <c r="L280" s="24"/>
-    </row>
-    <row r="281" spans="1:12">
-      <c r="A281" s="28"/>
-      <c r="B281" s="28"/>
-      <c r="C281" s="24"/>
-      <c r="D281" s="24"/>
-      <c r="E281" s="24"/>
-      <c r="F281" s="24"/>
-      <c r="G281" s="24"/>
-      <c r="H281" s="24"/>
-      <c r="I281" s="24"/>
-      <c r="J281" s="24"/>
-      <c r="K281" s="24"/>
-      <c r="L281" s="24"/>
-    </row>
-    <row r="282" spans="1:12">
-      <c r="A282" s="28"/>
-      <c r="B282" s="28"/>
-      <c r="C282" s="24"/>
-      <c r="D282" s="24"/>
-      <c r="E282" s="24"/>
-      <c r="F282" s="24"/>
-      <c r="G282" s="24"/>
-      <c r="H282" s="24"/>
-      <c r="I282" s="24"/>
-      <c r="J282" s="24"/>
-      <c r="K282" s="24"/>
-      <c r="L282" s="24"/>
-    </row>
-    <row r="283" spans="1:12">
-      <c r="A283" s="28"/>
-      <c r="B283" s="28"/>
-      <c r="C283" s="24"/>
-      <c r="D283" s="24"/>
-      <c r="E283" s="24"/>
-      <c r="F283" s="24"/>
-      <c r="G283" s="24"/>
-      <c r="H283" s="24"/>
-      <c r="I283" s="24"/>
-      <c r="J283" s="24"/>
-      <c r="K283" s="24"/>
-      <c r="L283" s="24"/>
-    </row>
-    <row r="284" spans="1:12">
-      <c r="A284" s="28"/>
-      <c r="B284" s="28"/>
-      <c r="C284" s="24"/>
-      <c r="D284" s="24"/>
-      <c r="E284" s="24"/>
-      <c r="F284" s="24"/>
-      <c r="G284" s="24"/>
-      <c r="H284" s="24"/>
-      <c r="I284" s="24"/>
-      <c r="J284" s="24"/>
-      <c r="K284" s="24"/>
-      <c r="L284" s="24"/>
-    </row>
-    <row r="285" spans="1:12">
-      <c r="A285" s="28"/>
-      <c r="B285" s="28"/>
-      <c r="C285" s="24"/>
-      <c r="D285" s="24"/>
-      <c r="E285" s="24"/>
-      <c r="F285" s="24"/>
-      <c r="G285" s="24"/>
-      <c r="H285" s="24"/>
-      <c r="I285" s="24"/>
-      <c r="J285" s="24"/>
-      <c r="K285" s="24"/>
-      <c r="L285" s="24"/>
-    </row>
-    <row r="286" spans="1:12">
-      <c r="A286" s="28"/>
-      <c r="B286" s="28"/>
-      <c r="C286" s="24"/>
-      <c r="D286" s="24"/>
-      <c r="E286" s="24"/>
-      <c r="F286" s="24"/>
-      <c r="G286" s="24"/>
-      <c r="H286" s="24"/>
-      <c r="I286" s="24"/>
-      <c r="J286" s="24"/>
-      <c r="K286" s="24"/>
-      <c r="L286" s="24"/>
-    </row>
-    <row r="287" spans="1:12">
-      <c r="A287" s="28"/>
-      <c r="B287" s="28"/>
-      <c r="C287" s="24"/>
-      <c r="D287" s="24"/>
-      <c r="E287" s="24"/>
-      <c r="F287" s="24"/>
-      <c r="G287" s="24"/>
-      <c r="H287" s="24"/>
-      <c r="I287" s="24"/>
-      <c r="J287" s="24"/>
-      <c r="K287" s="24"/>
-      <c r="L287" s="24"/>
-    </row>
-    <row r="288" spans="1:12">
-      <c r="A288" s="28"/>
-      <c r="B288" s="28"/>
-      <c r="C288" s="24"/>
-      <c r="D288" s="24"/>
-      <c r="E288" s="24"/>
-      <c r="F288" s="24"/>
-      <c r="G288" s="24"/>
-      <c r="H288" s="24"/>
-      <c r="I288" s="24"/>
-      <c r="J288" s="24"/>
-      <c r="K288" s="24"/>
-      <c r="L288" s="24"/>
-    </row>
-    <row r="289" spans="1:12">
-      <c r="A289" s="28"/>
-      <c r="B289" s="28"/>
-      <c r="C289" s="24"/>
-      <c r="D289" s="24"/>
-      <c r="E289" s="24"/>
-      <c r="F289" s="24"/>
-      <c r="G289" s="24"/>
-      <c r="H289" s="24"/>
-      <c r="I289" s="24"/>
-      <c r="J289" s="24"/>
-      <c r="K289" s="24"/>
-      <c r="L289" s="24"/>
-    </row>
-    <row r="290" spans="1:12">
-      <c r="A290" s="28"/>
-      <c r="B290" s="28"/>
-      <c r="C290" s="24"/>
-      <c r="D290" s="24"/>
-      <c r="E290" s="24"/>
-      <c r="F290" s="24"/>
-      <c r="G290" s="24"/>
-      <c r="H290" s="24"/>
-      <c r="I290" s="24"/>
-      <c r="J290" s="24"/>
-      <c r="K290" s="24"/>
-      <c r="L290" s="24"/>
-    </row>
-    <row r="291" spans="1:12">
-      <c r="A291" s="28"/>
-      <c r="B291" s="28"/>
-      <c r="C291" s="24"/>
-      <c r="D291" s="24"/>
-      <c r="E291" s="24"/>
-      <c r="F291" s="24"/>
-      <c r="G291" s="24"/>
-      <c r="H291" s="24"/>
-      <c r="I291" s="24"/>
-      <c r="J291" s="24"/>
-      <c r="K291" s="24"/>
-      <c r="L291" s="24"/>
-    </row>
-    <row r="292" spans="1:12">
-      <c r="A292" s="28"/>
-      <c r="B292" s="28"/>
-      <c r="C292" s="24"/>
-      <c r="D292" s="24"/>
-      <c r="E292" s="24"/>
-      <c r="F292" s="24"/>
-      <c r="G292" s="24"/>
-      <c r="H292" s="24"/>
-      <c r="I292" s="24"/>
-      <c r="J292" s="24"/>
-      <c r="K292" s="24"/>
-      <c r="L292" s="24"/>
-    </row>
-    <row r="293" spans="1:12">
-      <c r="A293" s="28"/>
-      <c r="B293" s="28"/>
-      <c r="C293" s="24"/>
-      <c r="D293" s="24"/>
-      <c r="E293" s="24"/>
-      <c r="F293" s="24"/>
-      <c r="G293" s="24"/>
-      <c r="H293" s="24"/>
-      <c r="I293" s="24"/>
-      <c r="J293" s="24"/>
-      <c r="K293" s="24"/>
-      <c r="L293" s="24"/>
-    </row>
-    <row r="294" spans="1:12">
-      <c r="A294" s="28"/>
-      <c r="B294" s="28"/>
-      <c r="C294" s="24"/>
-      <c r="D294" s="24"/>
-      <c r="E294" s="24"/>
-      <c r="F294" s="24"/>
-      <c r="G294" s="24"/>
-      <c r="H294" s="24"/>
-      <c r="I294" s="24"/>
-      <c r="J294" s="24"/>
-      <c r="K294" s="24"/>
-      <c r="L294" s="24"/>
-    </row>
-    <row r="295" spans="1:12">
-      <c r="A295" s="28"/>
-      <c r="B295" s="28"/>
-      <c r="C295" s="24"/>
-      <c r="D295" s="24"/>
-      <c r="E295" s="24"/>
-      <c r="F295" s="24"/>
-      <c r="G295" s="24"/>
-      <c r="H295" s="24"/>
-      <c r="I295" s="24"/>
-      <c r="J295" s="24"/>
-      <c r="K295" s="24"/>
-      <c r="L295" s="24"/>
-    </row>
-    <row r="296" spans="1:12">
-      <c r="A296" s="28"/>
-      <c r="B296" s="28"/>
-      <c r="C296" s="24"/>
-      <c r="D296" s="24"/>
-      <c r="E296" s="24"/>
-      <c r="F296" s="24"/>
-      <c r="G296" s="24"/>
-      <c r="H296" s="24"/>
-      <c r="I296" s="24"/>
-      <c r="J296" s="24"/>
-      <c r="K296" s="24"/>
-      <c r="L296" s="24"/>
-    </row>
-    <row r="297" spans="1:12">
-      <c r="A297" s="28"/>
-      <c r="B297" s="28"/>
-      <c r="C297" s="24"/>
-      <c r="D297" s="24"/>
-      <c r="E297" s="24"/>
-      <c r="F297" s="24"/>
-      <c r="G297" s="24"/>
-      <c r="H297" s="24"/>
-      <c r="I297" s="24"/>
-      <c r="J297" s="24"/>
-      <c r="K297" s="24"/>
-      <c r="L297" s="24"/>
-    </row>
-    <row r="298" spans="1:12">
-      <c r="A298" s="28"/>
-      <c r="B298" s="28"/>
-      <c r="C298" s="24"/>
-      <c r="D298" s="24"/>
-      <c r="E298" s="24"/>
-      <c r="F298" s="24"/>
-      <c r="G298" s="24"/>
-      <c r="H298" s="24"/>
-      <c r="I298" s="24"/>
-      <c r="J298" s="24"/>
-      <c r="K298" s="24"/>
-      <c r="L298" s="24"/>
-    </row>
-    <row r="299" spans="1:12">
-      <c r="A299" s="28"/>
-      <c r="B299" s="28"/>
-      <c r="C299" s="24"/>
-      <c r="D299" s="24"/>
-      <c r="E299" s="24"/>
-      <c r="F299" s="24"/>
-      <c r="G299" s="24"/>
-      <c r="H299" s="24"/>
-      <c r="I299" s="24"/>
-      <c r="J299" s="24"/>
-      <c r="K299" s="24"/>
-      <c r="L299" s="24"/>
-    </row>
-    <row r="300" spans="1:12">
-      <c r="A300" s="28"/>
-      <c r="B300" s="28"/>
-      <c r="C300" s="24"/>
-      <c r="D300" s="24"/>
-      <c r="E300" s="24"/>
-      <c r="F300" s="24"/>
-      <c r="G300" s="24"/>
-      <c r="H300" s="24"/>
-      <c r="I300" s="24"/>
-      <c r="J300" s="24"/>
-      <c r="K300" s="24"/>
-      <c r="L300" s="24"/>
-    </row>
-    <row r="301" spans="1:12">
-      <c r="A301" s="28"/>
-      <c r="B301" s="28"/>
-      <c r="C301" s="24"/>
-      <c r="D301" s="24"/>
-      <c r="E301" s="24"/>
-      <c r="F301" s="24"/>
-      <c r="G301" s="24"/>
-      <c r="H301" s="24"/>
-      <c r="I301" s="24"/>
-      <c r="J301" s="24"/>
-      <c r="K301" s="24"/>
-      <c r="L301" s="24"/>
-    </row>
-    <row r="302" spans="1:12">
-      <c r="A302" s="28"/>
-      <c r="B302" s="28"/>
-      <c r="C302" s="24"/>
-      <c r="D302" s="24"/>
-      <c r="E302" s="24"/>
-      <c r="F302" s="24"/>
-      <c r="G302" s="24"/>
-      <c r="H302" s="24"/>
-      <c r="I302" s="24"/>
-      <c r="J302" s="24"/>
-      <c r="K302" s="24"/>
-      <c r="L302" s="24"/>
-    </row>
-    <row r="303" spans="1:12">
-      <c r="A303" s="28"/>
-      <c r="B303" s="28"/>
-      <c r="C303" s="24"/>
-      <c r="D303" s="24"/>
-      <c r="E303" s="24"/>
-      <c r="F303" s="24"/>
-      <c r="G303" s="24"/>
-      <c r="H303" s="24"/>
-      <c r="I303" s="24"/>
-      <c r="J303" s="24"/>
-      <c r="K303" s="24"/>
-      <c r="L303" s="24"/>
-    </row>
-    <row r="304" spans="1:12">
-      <c r="A304" s="28"/>
-      <c r="B304" s="28"/>
-      <c r="C304" s="24"/>
-      <c r="D304" s="24"/>
-      <c r="E304" s="24"/>
-      <c r="F304" s="24"/>
-      <c r="G304" s="24"/>
-      <c r="H304" s="24"/>
-      <c r="I304" s="24"/>
-      <c r="J304" s="24"/>
-      <c r="K304" s="24"/>
-      <c r="L304" s="24"/>
+      <c r="C272" s="14"/>
+      <c r="D272" s="14"/>
+      <c r="E272" s="14"/>
+      <c r="F272" s="14"/>
+      <c r="G272" s="14"/>
+      <c r="H272" s="14"/>
+      <c r="I272" s="14"/>
+      <c r="J272" s="14"/>
+      <c r="K272" s="14"/>
+      <c r="L272" s="14"/>
+    </row>
+    <row r="273" spans="3:12">
+      <c r="C273" s="14"/>
+      <c r="D273" s="14"/>
+      <c r="E273" s="14"/>
+      <c r="F273" s="14"/>
+      <c r="G273" s="14"/>
+      <c r="H273" s="14"/>
+      <c r="I273" s="14"/>
+      <c r="J273" s="14"/>
+      <c r="K273" s="14"/>
+      <c r="L273" s="14"/>
+    </row>
+    <row r="274" spans="3:12">
+      <c r="C274" s="14"/>
+      <c r="D274" s="14"/>
+      <c r="E274" s="14"/>
+      <c r="F274" s="14"/>
+      <c r="G274" s="14"/>
+      <c r="H274" s="14"/>
+      <c r="I274" s="14"/>
+      <c r="J274" s="14"/>
+      <c r="K274" s="14"/>
+      <c r="L274" s="14"/>
+    </row>
+    <row r="275" spans="3:12">
+      <c r="C275" s="14"/>
+      <c r="D275" s="14"/>
+      <c r="E275" s="14"/>
+      <c r="F275" s="14"/>
+      <c r="G275" s="14"/>
+      <c r="H275" s="14"/>
+      <c r="I275" s="14"/>
+      <c r="J275" s="14"/>
+      <c r="K275" s="14"/>
+      <c r="L275" s="14"/>
+    </row>
+    <row r="276" spans="3:12">
+      <c r="C276" s="14"/>
+      <c r="D276" s="14"/>
+      <c r="E276" s="14"/>
+      <c r="F276" s="14"/>
+      <c r="G276" s="14"/>
+      <c r="H276" s="14"/>
+      <c r="I276" s="14"/>
+      <c r="J276" s="14"/>
+      <c r="K276" s="14"/>
+      <c r="L276" s="14"/>
+    </row>
+    <row r="277" spans="3:12">
+      <c r="C277" s="14"/>
+      <c r="D277" s="14"/>
+      <c r="E277" s="14"/>
+      <c r="F277" s="14"/>
+      <c r="G277" s="14"/>
+      <c r="H277" s="14"/>
+      <c r="I277" s="14"/>
+      <c r="J277" s="14"/>
+      <c r="K277" s="14"/>
+      <c r="L277" s="14"/>
+    </row>
+    <row r="278" spans="3:12">
+      <c r="C278" s="14"/>
+      <c r="D278" s="14"/>
+      <c r="E278" s="14"/>
+      <c r="F278" s="14"/>
+      <c r="G278" s="14"/>
+      <c r="H278" s="14"/>
+      <c r="I278" s="14"/>
+      <c r="J278" s="14"/>
+      <c r="K278" s="14"/>
+      <c r="L278" s="14"/>
+    </row>
+    <row r="279" spans="3:12">
+      <c r="C279" s="14"/>
+      <c r="D279" s="14"/>
+      <c r="E279" s="14"/>
+      <c r="F279" s="14"/>
+      <c r="G279" s="14"/>
+      <c r="H279" s="14"/>
+      <c r="I279" s="14"/>
+      <c r="J279" s="14"/>
+      <c r="K279" s="14"/>
+      <c r="L279" s="14"/>
+    </row>
+    <row r="280" spans="3:12">
+      <c r="C280" s="14"/>
+      <c r="D280" s="14"/>
+      <c r="E280" s="14"/>
+      <c r="F280" s="14"/>
+      <c r="G280" s="14"/>
+      <c r="H280" s="14"/>
+      <c r="I280" s="14"/>
+      <c r="J280" s="14"/>
+      <c r="K280" s="14"/>
+      <c r="L280" s="14"/>
+    </row>
+    <row r="281" spans="3:12">
+      <c r="C281" s="14"/>
+      <c r="D281" s="14"/>
+      <c r="E281" s="14"/>
+      <c r="F281" s="14"/>
+      <c r="G281" s="14"/>
+      <c r="H281" s="14"/>
+      <c r="I281" s="14"/>
+      <c r="J281" s="14"/>
+      <c r="K281" s="14"/>
+      <c r="L281" s="14"/>
+    </row>
+    <row r="282" spans="3:12">
+      <c r="C282" s="14"/>
+      <c r="D282" s="14"/>
+      <c r="E282" s="14"/>
+      <c r="F282" s="14"/>
+      <c r="G282" s="14"/>
+      <c r="H282" s="14"/>
+      <c r="I282" s="14"/>
+      <c r="J282" s="14"/>
+      <c r="K282" s="14"/>
+      <c r="L282" s="14"/>
+    </row>
+    <row r="283" spans="3:12">
+      <c r="C283" s="14"/>
+      <c r="D283" s="14"/>
+      <c r="E283" s="14"/>
+      <c r="F283" s="14"/>
+      <c r="G283" s="14"/>
+      <c r="H283" s="14"/>
+      <c r="I283" s="14"/>
+      <c r="J283" s="14"/>
+      <c r="K283" s="14"/>
+      <c r="L283" s="14"/>
+    </row>
+    <row r="284" spans="3:12">
+      <c r="C284" s="14"/>
+      <c r="D284" s="14"/>
+      <c r="E284" s="14"/>
+      <c r="F284" s="14"/>
+      <c r="G284" s="14"/>
+      <c r="H284" s="14"/>
+      <c r="I284" s="14"/>
+      <c r="J284" s="14"/>
+      <c r="K284" s="14"/>
+      <c r="L284" s="14"/>
+    </row>
+    <row r="285" spans="3:12">
+      <c r="C285" s="14"/>
+      <c r="D285" s="14"/>
+      <c r="E285" s="14"/>
+      <c r="F285" s="14"/>
+      <c r="G285" s="14"/>
+      <c r="H285" s="14"/>
+      <c r="I285" s="14"/>
+      <c r="J285" s="14"/>
+      <c r="K285" s="14"/>
+      <c r="L285" s="14"/>
+    </row>
+    <row r="286" spans="3:12">
+      <c r="C286" s="14"/>
+      <c r="D286" s="14"/>
+      <c r="E286" s="14"/>
+      <c r="F286" s="14"/>
+      <c r="G286" s="14"/>
+      <c r="H286" s="14"/>
+      <c r="I286" s="14"/>
+      <c r="J286" s="14"/>
+      <c r="K286" s="14"/>
+      <c r="L286" s="14"/>
+    </row>
+    <row r="287" spans="3:12">
+      <c r="C287" s="14"/>
+      <c r="D287" s="14"/>
+      <c r="E287" s="14"/>
+      <c r="F287" s="14"/>
+      <c r="G287" s="14"/>
+      <c r="H287" s="14"/>
+      <c r="I287" s="14"/>
+      <c r="J287" s="14"/>
+      <c r="K287" s="14"/>
+      <c r="L287" s="14"/>
+    </row>
+    <row r="288" spans="3:12">
+      <c r="C288" s="14"/>
+      <c r="D288" s="14"/>
+      <c r="E288" s="14"/>
+      <c r="F288" s="14"/>
+      <c r="G288" s="14"/>
+      <c r="H288" s="14"/>
+      <c r="I288" s="14"/>
+      <c r="J288" s="14"/>
+      <c r="K288" s="14"/>
+      <c r="L288" s="14"/>
+    </row>
+    <row r="289" spans="3:12">
+      <c r="C289" s="14"/>
+      <c r="D289" s="14"/>
+      <c r="E289" s="14"/>
+      <c r="F289" s="14"/>
+      <c r="G289" s="14"/>
+      <c r="H289" s="14"/>
+      <c r="I289" s="14"/>
+      <c r="J289" s="14"/>
+      <c r="K289" s="14"/>
+      <c r="L289" s="14"/>
+    </row>
+    <row r="290" spans="3:12">
+      <c r="C290" s="14"/>
+      <c r="D290" s="14"/>
+      <c r="E290" s="14"/>
+      <c r="F290" s="14"/>
+      <c r="G290" s="14"/>
+      <c r="H290" s="14"/>
+      <c r="I290" s="14"/>
+      <c r="J290" s="14"/>
+      <c r="K290" s="14"/>
+      <c r="L290" s="14"/>
+    </row>
+    <row r="291" spans="3:12">
+      <c r="C291" s="14"/>
+      <c r="D291" s="14"/>
+      <c r="E291" s="14"/>
+      <c r="F291" s="14"/>
+      <c r="G291" s="14"/>
+      <c r="H291" s="14"/>
+      <c r="I291" s="14"/>
+      <c r="J291" s="14"/>
+      <c r="K291" s="14"/>
+      <c r="L291" s="14"/>
+    </row>
+    <row r="292" spans="3:12">
+      <c r="C292" s="14"/>
+      <c r="D292" s="14"/>
+      <c r="E292" s="14"/>
+      <c r="F292" s="14"/>
+      <c r="G292" s="14"/>
+      <c r="H292" s="14"/>
+      <c r="I292" s="14"/>
+      <c r="J292" s="14"/>
+      <c r="K292" s="14"/>
+      <c r="L292" s="14"/>
+    </row>
+    <row r="293" spans="3:12">
+      <c r="C293" s="14"/>
+      <c r="D293" s="14"/>
+      <c r="E293" s="14"/>
+      <c r="F293" s="14"/>
+      <c r="G293" s="14"/>
+      <c r="H293" s="14"/>
+      <c r="I293" s="14"/>
+      <c r="J293" s="14"/>
+      <c r="K293" s="14"/>
+      <c r="L293" s="14"/>
+    </row>
+    <row r="294" spans="3:12">
+      <c r="C294" s="14"/>
+      <c r="D294" s="14"/>
+      <c r="E294" s="14"/>
+      <c r="F294" s="14"/>
+      <c r="G294" s="14"/>
+      <c r="H294" s="14"/>
+      <c r="I294" s="14"/>
+      <c r="J294" s="14"/>
+      <c r="K294" s="14"/>
+      <c r="L294" s="14"/>
+    </row>
+    <row r="295" spans="3:12">
+      <c r="C295" s="14"/>
+      <c r="D295" s="14"/>
+      <c r="E295" s="14"/>
+      <c r="F295" s="14"/>
+      <c r="G295" s="14"/>
+      <c r="H295" s="14"/>
+      <c r="I295" s="14"/>
+      <c r="J295" s="14"/>
+      <c r="K295" s="14"/>
+      <c r="L295" s="14"/>
+    </row>
+    <row r="296" spans="3:12">
+      <c r="C296" s="14"/>
+      <c r="D296" s="14"/>
+      <c r="E296" s="14"/>
+      <c r="F296" s="14"/>
+      <c r="G296" s="14"/>
+      <c r="H296" s="14"/>
+      <c r="I296" s="14"/>
+      <c r="J296" s="14"/>
+      <c r="K296" s="14"/>
+      <c r="L296" s="14"/>
+    </row>
+    <row r="297" spans="3:12">
+      <c r="C297" s="14"/>
+      <c r="D297" s="14"/>
+      <c r="E297" s="14"/>
+      <c r="F297" s="14"/>
+      <c r="G297" s="14"/>
+      <c r="H297" s="14"/>
+      <c r="I297" s="14"/>
+      <c r="J297" s="14"/>
+      <c r="K297" s="14"/>
+      <c r="L297" s="14"/>
+    </row>
+    <row r="298" spans="3:12">
+      <c r="C298" s="14"/>
+      <c r="D298" s="14"/>
+      <c r="E298" s="14"/>
+      <c r="F298" s="14"/>
+      <c r="G298" s="14"/>
+      <c r="H298" s="14"/>
+      <c r="I298" s="14"/>
+      <c r="J298" s="14"/>
+      <c r="K298" s="14"/>
+      <c r="L298" s="14"/>
+    </row>
+    <row r="299" spans="3:12">
+      <c r="C299" s="14"/>
+      <c r="D299" s="14"/>
+      <c r="E299" s="14"/>
+      <c r="F299" s="14"/>
+      <c r="G299" s="14"/>
+      <c r="H299" s="14"/>
+      <c r="I299" s="14"/>
+      <c r="J299" s="14"/>
+      <c r="K299" s="14"/>
+      <c r="L299" s="14"/>
+    </row>
+    <row r="300" spans="3:12">
+      <c r="C300" s="14"/>
+      <c r="D300" s="14"/>
+      <c r="E300" s="14"/>
+      <c r="F300" s="14"/>
+      <c r="G300" s="14"/>
+      <c r="H300" s="14"/>
+      <c r="I300" s="14"/>
+      <c r="J300" s="14"/>
+      <c r="K300" s="14"/>
+      <c r="L300" s="14"/>
+    </row>
+    <row r="301" spans="3:12">
+      <c r="C301" s="14"/>
+      <c r="D301" s="14"/>
+      <c r="E301" s="14"/>
+      <c r="F301" s="14"/>
+      <c r="G301" s="14"/>
+      <c r="H301" s="14"/>
+      <c r="I301" s="14"/>
+      <c r="J301" s="14"/>
+      <c r="K301" s="14"/>
+      <c r="L301" s="14"/>
+    </row>
+    <row r="302" spans="3:12">
+      <c r="C302" s="14"/>
+      <c r="D302" s="14"/>
+      <c r="E302" s="14"/>
+      <c r="F302" s="14"/>
+      <c r="G302" s="14"/>
+      <c r="H302" s="14"/>
+      <c r="I302" s="14"/>
+      <c r="J302" s="14"/>
+      <c r="K302" s="14"/>
+      <c r="L302" s="14"/>
+    </row>
+    <row r="303" spans="3:12">
+      <c r="C303" s="14"/>
+      <c r="D303" s="14"/>
+      <c r="E303" s="14"/>
+      <c r="F303" s="14"/>
+      <c r="G303" s="14"/>
+      <c r="H303" s="14"/>
+      <c r="I303" s="14"/>
+      <c r="J303" s="14"/>
+      <c r="K303" s="14"/>
+      <c r="L303" s="14"/>
+    </row>
+    <row r="304" spans="3:12">
+      <c r="C304" s="14"/>
+      <c r="D304" s="14"/>
+      <c r="E304" s="14"/>
+      <c r="F304" s="14"/>
+      <c r="G304" s="14"/>
+      <c r="H304" s="14"/>
+      <c r="I304" s="14"/>
+      <c r="J304" s="14"/>
+      <c r="K304" s="14"/>
+      <c r="L304" s="14"/>
     </row>
     <row r="305" spans="1:12">
-      <c r="A305" s="28"/>
-      <c r="B305" s="28"/>
-      <c r="C305" s="24"/>
-      <c r="D305" s="24"/>
-      <c r="E305" s="24"/>
-      <c r="F305" s="24"/>
-      <c r="G305" s="24"/>
-      <c r="H305" s="24"/>
-      <c r="I305" s="24"/>
-      <c r="J305" s="24"/>
-      <c r="K305" s="24"/>
-      <c r="L305" s="24"/>
+      <c r="C305" s="14"/>
+      <c r="D305" s="14"/>
+      <c r="E305" s="14"/>
+      <c r="F305" s="14"/>
+      <c r="G305" s="14"/>
+      <c r="H305" s="14"/>
+      <c r="I305" s="14"/>
+      <c r="J305" s="14"/>
+      <c r="K305" s="14"/>
+      <c r="L305" s="14"/>
     </row>
     <row r="306" spans="1:12">
-      <c r="A306" s="28"/>
-      <c r="B306" s="28"/>
-      <c r="C306" s="24"/>
-      <c r="D306" s="24"/>
-      <c r="E306" s="24"/>
-      <c r="F306" s="24"/>
-      <c r="G306" s="24"/>
-      <c r="H306" s="24"/>
-      <c r="I306" s="24"/>
-      <c r="J306" s="24"/>
-      <c r="K306" s="24"/>
-      <c r="L306" s="24"/>
+      <c r="C306" s="14"/>
+      <c r="D306" s="14"/>
+      <c r="E306" s="14"/>
+      <c r="F306" s="14"/>
+      <c r="G306" s="14"/>
+      <c r="H306" s="14"/>
+      <c r="I306" s="14"/>
+      <c r="J306" s="14"/>
+      <c r="K306" s="14"/>
+      <c r="L306" s="14"/>
     </row>
     <row r="307" spans="1:12">
-      <c r="A307" s="28"/>
-      <c r="B307" s="28"/>
-      <c r="C307" s="24"/>
-      <c r="D307" s="24"/>
-      <c r="E307" s="24"/>
-      <c r="F307" s="24"/>
-      <c r="G307" s="24"/>
-      <c r="H307" s="24"/>
-      <c r="I307" s="24"/>
-      <c r="J307" s="24"/>
-      <c r="K307" s="24"/>
-      <c r="L307" s="24"/>
+      <c r="C307" s="14"/>
+      <c r="D307" s="14"/>
+      <c r="E307" s="14"/>
+      <c r="F307" s="14"/>
+      <c r="G307" s="14"/>
+      <c r="H307" s="14"/>
+      <c r="I307" s="14"/>
+      <c r="J307" s="14"/>
+      <c r="K307" s="14"/>
+      <c r="L307" s="14"/>
     </row>
     <row r="308" spans="1:12">
-      <c r="A308" s="28"/>
-      <c r="B308" s="28"/>
-      <c r="C308" s="24"/>
-      <c r="D308" s="24"/>
-      <c r="E308" s="24"/>
-      <c r="F308" s="24"/>
-      <c r="G308" s="24"/>
-      <c r="H308" s="24"/>
-      <c r="I308" s="24"/>
-      <c r="J308" s="24"/>
-      <c r="K308" s="24"/>
-      <c r="L308" s="24"/>
+      <c r="C308" s="14"/>
+      <c r="D308" s="14"/>
+      <c r="E308" s="14"/>
+      <c r="F308" s="14"/>
+      <c r="G308" s="14"/>
+      <c r="H308" s="14"/>
+      <c r="I308" s="14"/>
+      <c r="J308" s="14"/>
+      <c r="K308" s="14"/>
+      <c r="L308" s="14"/>
     </row>
     <row r="309" spans="1:12">
-      <c r="A309" s="28"/>
-      <c r="B309" s="28"/>
-      <c r="C309" s="24"/>
-      <c r="D309" s="24"/>
-      <c r="E309" s="24"/>
-      <c r="F309" s="24"/>
-      <c r="G309" s="24"/>
-      <c r="H309" s="24"/>
-      <c r="I309" s="24"/>
-      <c r="J309" s="24"/>
-      <c r="K309" s="24"/>
-      <c r="L309" s="24"/>
+      <c r="C309" s="14"/>
+      <c r="D309" s="14"/>
+      <c r="E309" s="14"/>
+      <c r="F309" s="14"/>
+      <c r="G309" s="14"/>
+      <c r="H309" s="14"/>
+      <c r="I309" s="14"/>
+      <c r="J309" s="14"/>
+      <c r="K309" s="14"/>
+      <c r="L309" s="14"/>
     </row>
     <row r="310" spans="1:12">
-      <c r="A310" s="28"/>
-      <c r="B310" s="28"/>
-      <c r="C310" s="24"/>
-      <c r="D310" s="24"/>
-      <c r="E310" s="24"/>
-      <c r="F310" s="24"/>
-      <c r="G310" s="24"/>
-      <c r="H310" s="24"/>
-      <c r="I310" s="24"/>
-      <c r="J310" s="24"/>
-      <c r="K310" s="24"/>
-      <c r="L310" s="24"/>
+      <c r="C310" s="14"/>
+      <c r="D310" s="14"/>
+      <c r="E310" s="14"/>
+      <c r="F310" s="14"/>
+      <c r="G310" s="14"/>
+      <c r="H310" s="14"/>
+      <c r="I310" s="14"/>
+      <c r="J310" s="14"/>
+      <c r="K310" s="14"/>
+      <c r="L310" s="14"/>
     </row>
     <row r="311" spans="1:12">
-      <c r="A311" s="26"/>
-      <c r="B311" s="26"/>
-      <c r="C311" s="27"/>
-      <c r="D311" s="27"/>
-      <c r="E311" s="27"/>
-      <c r="F311" s="27"/>
-      <c r="G311" s="27"/>
-      <c r="H311" s="27"/>
-      <c r="I311" s="27"/>
-      <c r="J311" s="27"/>
-      <c r="K311" s="27"/>
-      <c r="L311" s="27"/>
+      <c r="A311" s="13"/>
+      <c r="B311" s="13"/>
+      <c r="C311" s="7"/>
+      <c r="D311" s="7"/>
+      <c r="E311" s="7"/>
+      <c r="F311" s="7"/>
+      <c r="G311" s="7"/>
+      <c r="H311" s="7"/>
+      <c r="I311" s="7"/>
+      <c r="J311" s="7"/>
+      <c r="K311" s="7"/>
+      <c r="L311" s="7"/>
     </row>
     <row r="312" spans="1:12">
-      <c r="A312" s="28"/>
-      <c r="B312" s="28"/>
-      <c r="C312" s="24"/>
-      <c r="D312" s="24"/>
-      <c r="E312" s="24"/>
-      <c r="F312" s="24"/>
-      <c r="G312" s="24"/>
-      <c r="H312" s="24"/>
-      <c r="I312" s="24"/>
-      <c r="J312" s="24"/>
-      <c r="K312" s="24"/>
-      <c r="L312" s="24"/>
+      <c r="C312" s="14"/>
+      <c r="D312" s="14"/>
+      <c r="E312" s="14"/>
+      <c r="F312" s="14"/>
+      <c r="G312" s="14"/>
+      <c r="H312" s="14"/>
+      <c r="I312" s="14"/>
+      <c r="J312" s="14"/>
+      <c r="K312" s="14"/>
+      <c r="L312" s="14"/>
     </row>
     <row r="313" spans="1:12">
-      <c r="A313" s="28"/>
-      <c r="B313" s="28"/>
-      <c r="C313" s="24"/>
-      <c r="D313" s="24"/>
-      <c r="E313" s="24"/>
-      <c r="F313" s="24"/>
-      <c r="G313" s="24"/>
-      <c r="H313" s="24"/>
-      <c r="I313" s="24"/>
-      <c r="J313" s="24"/>
-      <c r="K313" s="24"/>
-      <c r="L313" s="24"/>
+      <c r="C313" s="14"/>
+      <c r="D313" s="14"/>
+      <c r="E313" s="14"/>
+      <c r="F313" s="14"/>
+      <c r="G313" s="14"/>
+      <c r="H313" s="14"/>
+      <c r="I313" s="14"/>
+      <c r="J313" s="14"/>
+      <c r="K313" s="14"/>
+      <c r="L313" s="14"/>
     </row>
     <row r="314" spans="1:12">
-      <c r="A314" s="28"/>
-      <c r="B314" s="28"/>
-      <c r="C314" s="24"/>
-      <c r="D314" s="24"/>
-      <c r="E314" s="24"/>
-      <c r="F314" s="24"/>
-      <c r="G314" s="24"/>
-      <c r="H314" s="24"/>
-      <c r="I314" s="24"/>
-      <c r="J314" s="24"/>
-      <c r="K314" s="24"/>
-      <c r="L314" s="24"/>
+      <c r="C314" s="14"/>
+      <c r="D314" s="14"/>
+      <c r="E314" s="14"/>
+      <c r="F314" s="14"/>
+      <c r="G314" s="14"/>
+      <c r="H314" s="14"/>
+      <c r="I314" s="14"/>
+      <c r="J314" s="14"/>
+      <c r="K314" s="14"/>
+      <c r="L314" s="14"/>
     </row>
     <row r="315" spans="1:12">
-      <c r="A315" s="28"/>
-      <c r="B315" s="28"/>
-      <c r="C315" s="24"/>
-      <c r="D315" s="24"/>
-      <c r="E315" s="24"/>
-      <c r="F315" s="24"/>
-      <c r="G315" s="24"/>
-      <c r="H315" s="24"/>
-      <c r="I315" s="24"/>
-      <c r="J315" s="24"/>
-      <c r="K315" s="24"/>
-      <c r="L315" s="24"/>
+      <c r="C315" s="14"/>
+      <c r="D315" s="14"/>
+      <c r="E315" s="14"/>
+      <c r="F315" s="14"/>
+      <c r="G315" s="14"/>
+      <c r="H315" s="14"/>
+      <c r="I315" s="14"/>
+      <c r="J315" s="14"/>
+      <c r="K315" s="14"/>
+      <c r="L315" s="14"/>
     </row>
     <row r="316" spans="1:12">
-      <c r="A316" s="28"/>
-      <c r="B316" s="28"/>
-      <c r="C316" s="24"/>
-      <c r="D316" s="24"/>
-      <c r="E316" s="24"/>
-      <c r="F316" s="24"/>
-      <c r="G316" s="24"/>
-      <c r="H316" s="24"/>
-      <c r="I316" s="24"/>
-      <c r="J316" s="24"/>
-      <c r="K316" s="24"/>
-      <c r="L316" s="24"/>
+      <c r="C316" s="14"/>
+      <c r="D316" s="14"/>
+      <c r="E316" s="14"/>
+      <c r="F316" s="14"/>
+      <c r="G316" s="14"/>
+      <c r="H316" s="14"/>
+      <c r="I316" s="14"/>
+      <c r="J316" s="14"/>
+      <c r="K316" s="14"/>
+      <c r="L316" s="14"/>
     </row>
     <row r="317" spans="1:12">
-      <c r="A317" s="28"/>
-      <c r="B317" s="28"/>
-      <c r="C317" s="24"/>
-      <c r="D317" s="24"/>
-      <c r="E317" s="24"/>
-      <c r="F317" s="24"/>
-      <c r="G317" s="24"/>
-      <c r="H317" s="24"/>
-      <c r="I317" s="24"/>
-      <c r="J317" s="24"/>
-      <c r="K317" s="24"/>
-      <c r="L317" s="24"/>
+      <c r="C317" s="14"/>
+      <c r="D317" s="14"/>
+      <c r="E317" s="14"/>
+      <c r="F317" s="14"/>
+      <c r="G317" s="14"/>
+      <c r="H317" s="14"/>
+      <c r="I317" s="14"/>
+      <c r="J317" s="14"/>
+      <c r="K317" s="14"/>
+      <c r="L317" s="14"/>
     </row>
     <row r="318" spans="1:12">
-      <c r="A318" s="28"/>
-      <c r="B318" s="28"/>
-      <c r="C318" s="24"/>
-      <c r="D318" s="24"/>
-      <c r="E318" s="24"/>
-      <c r="F318" s="24"/>
-      <c r="G318" s="24"/>
-      <c r="H318" s="24"/>
-      <c r="I318" s="24"/>
-      <c r="J318" s="24"/>
-      <c r="K318" s="24"/>
-      <c r="L318" s="24"/>
+      <c r="C318" s="14"/>
+      <c r="D318" s="14"/>
+      <c r="E318" s="14"/>
+      <c r="F318" s="14"/>
+      <c r="G318" s="14"/>
+      <c r="H318" s="14"/>
+      <c r="I318" s="14"/>
+      <c r="J318" s="14"/>
+      <c r="K318" s="14"/>
+      <c r="L318" s="14"/>
     </row>
     <row r="319" spans="1:12">
-      <c r="A319" s="28"/>
-      <c r="B319" s="28"/>
-      <c r="C319" s="24"/>
-      <c r="D319" s="24"/>
-      <c r="E319" s="24"/>
-      <c r="F319" s="24"/>
-      <c r="G319" s="24"/>
-      <c r="H319" s="24"/>
-      <c r="I319" s="24"/>
-      <c r="J319" s="24"/>
-      <c r="K319" s="24"/>
-      <c r="L319" s="24"/>
+      <c r="C319" s="14"/>
+      <c r="D319" s="14"/>
+      <c r="E319" s="14"/>
+      <c r="F319" s="14"/>
+      <c r="G319" s="14"/>
+      <c r="H319" s="14"/>
+      <c r="I319" s="14"/>
+      <c r="J319" s="14"/>
+      <c r="K319" s="14"/>
+      <c r="L319" s="14"/>
     </row>
     <row r="320" spans="1:12">
-      <c r="A320" s="28"/>
-      <c r="B320" s="28"/>
-      <c r="C320" s="24"/>
-      <c r="D320" s="24"/>
-      <c r="E320" s="24"/>
-      <c r="F320" s="24"/>
-      <c r="G320" s="24"/>
-      <c r="H320" s="24"/>
-      <c r="I320" s="24"/>
-      <c r="J320" s="24"/>
-      <c r="K320" s="24"/>
-      <c r="L320" s="24"/>
-    </row>
-    <row r="321" spans="1:12">
-      <c r="A321" s="28"/>
-      <c r="B321" s="28"/>
-      <c r="C321" s="24"/>
-      <c r="D321" s="24"/>
-      <c r="E321" s="24"/>
-      <c r="F321" s="24"/>
-      <c r="G321" s="24"/>
-      <c r="H321" s="24"/>
-      <c r="I321" s="24"/>
-      <c r="J321" s="24"/>
-      <c r="K321" s="24"/>
-      <c r="L321" s="24"/>
-    </row>
-    <row r="322" spans="1:12">
-      <c r="A322" s="28"/>
-      <c r="B322" s="28"/>
-      <c r="C322" s="24"/>
-      <c r="D322" s="24"/>
-      <c r="E322" s="24"/>
-      <c r="F322" s="24"/>
-      <c r="G322" s="24"/>
-      <c r="H322" s="24"/>
-      <c r="I322" s="24"/>
-      <c r="J322" s="24"/>
-      <c r="K322" s="24"/>
-      <c r="L322" s="24"/>
-    </row>
-    <row r="323" spans="1:12">
-      <c r="A323" s="28"/>
-      <c r="B323" s="28"/>
-      <c r="C323" s="24"/>
-      <c r="D323" s="24"/>
-      <c r="E323" s="24"/>
-      <c r="F323" s="24"/>
-      <c r="G323" s="24"/>
-      <c r="H323" s="24"/>
-      <c r="I323" s="24"/>
-      <c r="J323" s="24"/>
-      <c r="K323" s="24"/>
-      <c r="L323" s="24"/>
-    </row>
-    <row r="324" spans="1:12">
-      <c r="A324" s="28"/>
-      <c r="B324" s="28"/>
-      <c r="C324" s="24"/>
-      <c r="D324" s="24"/>
-      <c r="E324" s="24"/>
-      <c r="F324" s="24"/>
-      <c r="G324" s="24"/>
-      <c r="H324" s="24"/>
-      <c r="I324" s="24"/>
-      <c r="J324" s="24"/>
-      <c r="K324" s="24"/>
-      <c r="L324" s="24"/>
-    </row>
-    <row r="325" spans="1:12">
-      <c r="A325" s="28"/>
-      <c r="B325" s="28"/>
-      <c r="C325" s="24"/>
-      <c r="D325" s="24"/>
-      <c r="E325" s="24"/>
-      <c r="F325" s="24"/>
-      <c r="G325" s="24"/>
-      <c r="H325" s="24"/>
-      <c r="I325" s="24"/>
-      <c r="J325" s="24"/>
-      <c r="K325" s="24"/>
-      <c r="L325" s="24"/>
-    </row>
-    <row r="326" spans="1:12">
-      <c r="A326" s="28"/>
-      <c r="B326" s="28"/>
-      <c r="C326" s="24"/>
-      <c r="D326" s="24"/>
-      <c r="E326" s="24"/>
-      <c r="F326" s="24"/>
-      <c r="G326" s="24"/>
-      <c r="H326" s="24"/>
-      <c r="I326" s="24"/>
-      <c r="J326" s="24"/>
-      <c r="K326" s="24"/>
-      <c r="L326" s="24"/>
-    </row>
-    <row r="327" spans="1:12">
-      <c r="A327" s="28"/>
-      <c r="B327" s="28"/>
-      <c r="C327" s="24"/>
-      <c r="D327" s="24"/>
-      <c r="E327" s="24"/>
-      <c r="F327" s="24"/>
-      <c r="G327" s="24"/>
-      <c r="H327" s="24"/>
-      <c r="I327" s="24"/>
-      <c r="J327" s="24"/>
-      <c r="K327" s="24"/>
-      <c r="L327" s="24"/>
-    </row>
-    <row r="328" spans="1:12">
-      <c r="A328" s="28"/>
-      <c r="B328" s="28"/>
-      <c r="C328" s="24"/>
-      <c r="D328" s="24"/>
-      <c r="E328" s="24"/>
-      <c r="F328" s="24"/>
-      <c r="G328" s="24"/>
-      <c r="H328" s="24"/>
-      <c r="I328" s="24"/>
-      <c r="J328" s="24"/>
-      <c r="K328" s="24"/>
-      <c r="L328" s="24"/>
-    </row>
-    <row r="329" spans="1:12">
-      <c r="A329" s="28"/>
-      <c r="B329" s="28"/>
-      <c r="C329" s="24"/>
-      <c r="D329" s="24"/>
-      <c r="E329" s="24"/>
-      <c r="F329" s="24"/>
-      <c r="G329" s="24"/>
-      <c r="H329" s="24"/>
-      <c r="I329" s="24"/>
-      <c r="J329" s="24"/>
-      <c r="K329" s="24"/>
-      <c r="L329" s="24"/>
-    </row>
-    <row r="330" spans="1:12">
-      <c r="A330" s="28"/>
-      <c r="B330" s="28"/>
-      <c r="C330" s="24"/>
-      <c r="D330" s="24"/>
-      <c r="E330" s="24"/>
-      <c r="F330" s="24"/>
-      <c r="G330" s="24"/>
-      <c r="H330" s="24"/>
-      <c r="I330" s="24"/>
-      <c r="J330" s="24"/>
-      <c r="K330" s="24"/>
-      <c r="L330" s="24"/>
-    </row>
-    <row r="331" spans="1:12">
-      <c r="A331" s="28"/>
-      <c r="B331" s="28"/>
-      <c r="C331" s="24"/>
-      <c r="D331" s="24"/>
-      <c r="E331" s="24"/>
-      <c r="F331" s="24"/>
-      <c r="G331" s="24"/>
-      <c r="H331" s="24"/>
-      <c r="I331" s="24"/>
-      <c r="J331" s="24"/>
-      <c r="K331" s="24"/>
-      <c r="L331" s="24"/>
-    </row>
-    <row r="332" spans="1:12">
-      <c r="A332" s="28"/>
-      <c r="B332" s="28"/>
-      <c r="C332" s="24"/>
-      <c r="D332" s="24"/>
-      <c r="E332" s="24"/>
-      <c r="F332" s="24"/>
-      <c r="G332" s="24"/>
-      <c r="H332" s="24"/>
-      <c r="I332" s="24"/>
-      <c r="J332" s="24"/>
-      <c r="K332" s="24"/>
-      <c r="L332" s="24"/>
-    </row>
-    <row r="333" spans="1:12">
-      <c r="A333" s="28"/>
-      <c r="B333" s="28"/>
-      <c r="C333" s="24"/>
-      <c r="D333" s="24"/>
-      <c r="E333" s="24"/>
-      <c r="F333" s="24"/>
-      <c r="G333" s="24"/>
-      <c r="H333" s="24"/>
-      <c r="I333" s="24"/>
-      <c r="J333" s="24"/>
-      <c r="K333" s="24"/>
-      <c r="L333" s="24"/>
-    </row>
-    <row r="334" spans="1:12">
-      <c r="A334" s="28"/>
-      <c r="B334" s="28"/>
-      <c r="C334" s="24"/>
-      <c r="D334" s="24"/>
-      <c r="E334" s="24"/>
-      <c r="F334" s="24"/>
-      <c r="G334" s="24"/>
-      <c r="H334" s="24"/>
-      <c r="I334" s="24"/>
-      <c r="J334" s="24"/>
-      <c r="K334" s="24"/>
-      <c r="L334" s="24"/>
-    </row>
-    <row r="335" spans="1:12">
-      <c r="A335" s="28"/>
-      <c r="B335" s="28"/>
-      <c r="C335" s="24"/>
-      <c r="D335" s="24"/>
-      <c r="E335" s="24"/>
-      <c r="F335" s="24"/>
-      <c r="G335" s="24"/>
-      <c r="H335" s="24"/>
-      <c r="I335" s="24"/>
-      <c r="J335" s="24"/>
-      <c r="K335" s="24"/>
-      <c r="L335" s="24"/>
-    </row>
-    <row r="336" spans="1:12">
-      <c r="A336" s="28"/>
-      <c r="B336" s="28"/>
-      <c r="C336" s="24"/>
-      <c r="D336" s="24"/>
-      <c r="E336" s="24"/>
-      <c r="F336" s="24"/>
-      <c r="G336" s="24"/>
-      <c r="H336" s="24"/>
-      <c r="I336" s="24"/>
-      <c r="J336" s="24"/>
-      <c r="K336" s="24"/>
-      <c r="L336" s="24"/>
-    </row>
-    <row r="337" spans="1:12">
-      <c r="A337" s="28"/>
-      <c r="B337" s="28"/>
-      <c r="C337" s="24"/>
-      <c r="D337" s="24"/>
-      <c r="E337" s="24"/>
-      <c r="F337" s="24"/>
-      <c r="G337" s="24"/>
-      <c r="H337" s="24"/>
-      <c r="I337" s="24"/>
-      <c r="J337" s="24"/>
-      <c r="K337" s="24"/>
-      <c r="L337" s="24"/>
-    </row>
-    <row r="338" spans="1:12">
-      <c r="A338" s="28"/>
-      <c r="B338" s="28"/>
-      <c r="C338" s="24"/>
-      <c r="D338" s="24"/>
-      <c r="E338" s="24"/>
-      <c r="F338" s="24"/>
-      <c r="G338" s="24"/>
-      <c r="H338" s="24"/>
-      <c r="I338" s="24"/>
-      <c r="J338" s="24"/>
-      <c r="K338" s="24"/>
-      <c r="L338" s="24"/>
-    </row>
-    <row r="339" spans="1:12">
-      <c r="A339" s="28"/>
-      <c r="B339" s="28"/>
-      <c r="C339" s="24"/>
-      <c r="D339" s="24"/>
-      <c r="E339" s="24"/>
-      <c r="F339" s="24"/>
-      <c r="G339" s="24"/>
-      <c r="H339" s="24"/>
-      <c r="I339" s="24"/>
-      <c r="J339" s="24"/>
-      <c r="K339" s="24"/>
-      <c r="L339" s="24"/>
-    </row>
-    <row r="340" spans="1:12">
-      <c r="A340" s="28"/>
-      <c r="B340" s="28"/>
-      <c r="C340" s="24"/>
-      <c r="D340" s="24"/>
-      <c r="E340" s="24"/>
-      <c r="F340" s="24"/>
-      <c r="G340" s="24"/>
-      <c r="H340" s="24"/>
-      <c r="I340" s="24"/>
-      <c r="J340" s="24"/>
-      <c r="K340" s="24"/>
-      <c r="L340" s="24"/>
-    </row>
-    <row r="341" spans="1:12">
-      <c r="A341" s="28"/>
-      <c r="B341" s="28"/>
-      <c r="C341" s="24"/>
-      <c r="D341" s="24"/>
-      <c r="E341" s="24"/>
-      <c r="F341" s="24"/>
-      <c r="G341" s="24"/>
-      <c r="H341" s="24"/>
-      <c r="I341" s="24"/>
-      <c r="J341" s="24"/>
-      <c r="K341" s="24"/>
-      <c r="L341" s="24"/>
-    </row>
-    <row r="342" spans="1:12">
-      <c r="A342" s="28"/>
-      <c r="B342" s="28"/>
-      <c r="C342" s="24"/>
-      <c r="D342" s="24"/>
-      <c r="E342" s="24"/>
-      <c r="F342" s="24"/>
-      <c r="G342" s="24"/>
-      <c r="H342" s="24"/>
-      <c r="I342" s="24"/>
-      <c r="J342" s="24"/>
-      <c r="K342" s="24"/>
-      <c r="L342" s="24"/>
-    </row>
-    <row r="343" spans="1:12">
-      <c r="A343" s="28"/>
-      <c r="B343" s="28"/>
-      <c r="C343" s="24"/>
-      <c r="D343" s="24"/>
-      <c r="E343" s="24"/>
-      <c r="F343" s="24"/>
-      <c r="G343" s="24"/>
-      <c r="H343" s="24"/>
-      <c r="I343" s="24"/>
-      <c r="J343" s="24"/>
-      <c r="K343" s="24"/>
-      <c r="L343" s="24"/>
-    </row>
-    <row r="344" spans="1:12">
-      <c r="A344" s="28"/>
-      <c r="B344" s="28"/>
-      <c r="C344" s="24"/>
-      <c r="D344" s="24"/>
-      <c r="E344" s="24"/>
-      <c r="F344" s="24"/>
-      <c r="G344" s="24"/>
-      <c r="H344" s="24"/>
-      <c r="I344" s="24"/>
-      <c r="J344" s="24"/>
-      <c r="K344" s="24"/>
-      <c r="L344" s="24"/>
-    </row>
-    <row r="345" spans="1:12">
-      <c r="A345" s="28"/>
-      <c r="B345" s="28"/>
-      <c r="C345" s="24"/>
-      <c r="D345" s="24"/>
-      <c r="E345" s="24"/>
-      <c r="F345" s="24"/>
-      <c r="G345" s="24"/>
-      <c r="H345" s="24"/>
-      <c r="I345" s="24"/>
-      <c r="J345" s="24"/>
-      <c r="K345" s="24"/>
-      <c r="L345" s="24"/>
-    </row>
-    <row r="346" spans="1:12">
-      <c r="A346" s="28"/>
-      <c r="B346" s="28"/>
-      <c r="C346" s="24"/>
-      <c r="D346" s="24"/>
-      <c r="E346" s="24"/>
-      <c r="F346" s="24"/>
-      <c r="G346" s="24"/>
-      <c r="H346" s="24"/>
-      <c r="I346" s="24"/>
-      <c r="J346" s="24"/>
-      <c r="K346" s="24"/>
-      <c r="L346" s="24"/>
-    </row>
-    <row r="347" spans="1:12">
-      <c r="A347" s="28"/>
-      <c r="B347" s="28"/>
-      <c r="C347" s="24"/>
-      <c r="D347" s="24"/>
-      <c r="E347" s="24"/>
-      <c r="F347" s="24"/>
-      <c r="G347" s="24"/>
-      <c r="H347" s="24"/>
-      <c r="I347" s="24"/>
-      <c r="J347" s="24"/>
-      <c r="K347" s="24"/>
-      <c r="L347" s="24"/>
-    </row>
-    <row r="348" spans="1:12">
-      <c r="A348" s="28"/>
-      <c r="B348" s="28"/>
-      <c r="C348" s="24"/>
-      <c r="D348" s="24"/>
-      <c r="E348" s="24"/>
-      <c r="F348" s="24"/>
-      <c r="G348" s="24"/>
-      <c r="H348" s="24"/>
-      <c r="I348" s="24"/>
-      <c r="J348" s="24"/>
-      <c r="K348" s="24"/>
-      <c r="L348" s="24"/>
-    </row>
-    <row r="349" spans="1:12">
-      <c r="A349" s="28"/>
-      <c r="B349" s="28"/>
-      <c r="C349" s="24"/>
-      <c r="D349" s="24"/>
-      <c r="E349" s="24"/>
-      <c r="F349" s="24"/>
-      <c r="G349" s="24"/>
-      <c r="H349" s="24"/>
-      <c r="I349" s="24"/>
-      <c r="J349" s="24"/>
-      <c r="K349" s="24"/>
-      <c r="L349" s="24"/>
-    </row>
-    <row r="350" spans="1:12">
-      <c r="A350" s="28"/>
-      <c r="B350" s="28"/>
-      <c r="C350" s="24"/>
-      <c r="D350" s="24"/>
-      <c r="E350" s="24"/>
-      <c r="F350" s="24"/>
-      <c r="G350" s="24"/>
-      <c r="H350" s="24"/>
-      <c r="I350" s="24"/>
-      <c r="J350" s="24"/>
-      <c r="K350" s="24"/>
-      <c r="L350" s="24"/>
-    </row>
-    <row r="351" spans="1:12">
-      <c r="A351" s="28"/>
-      <c r="B351" s="28"/>
-      <c r="C351" s="24"/>
-      <c r="D351" s="24"/>
-      <c r="E351" s="24"/>
-      <c r="F351" s="24"/>
-      <c r="G351" s="24"/>
-      <c r="H351" s="24"/>
-      <c r="I351" s="24"/>
-      <c r="J351" s="24"/>
-      <c r="K351" s="24"/>
-      <c r="L351" s="24"/>
-    </row>
-    <row r="352" spans="1:12">
-      <c r="A352" s="28"/>
-      <c r="B352" s="28"/>
-      <c r="C352" s="24"/>
-      <c r="D352" s="24"/>
-      <c r="E352" s="24"/>
-      <c r="F352" s="24"/>
-      <c r="G352" s="24"/>
-      <c r="H352" s="24"/>
-      <c r="I352" s="24"/>
-      <c r="J352" s="24"/>
-      <c r="K352" s="24"/>
-      <c r="L352" s="24"/>
-    </row>
-    <row r="353" spans="1:12">
-      <c r="A353" s="28"/>
-      <c r="B353" s="28"/>
-      <c r="C353" s="24"/>
-      <c r="D353" s="24"/>
-      <c r="E353" s="24"/>
-      <c r="F353" s="24"/>
-      <c r="G353" s="24"/>
-      <c r="H353" s="24"/>
-      <c r="I353" s="24"/>
-      <c r="J353" s="24"/>
-      <c r="K353" s="24"/>
-      <c r="L353" s="24"/>
-    </row>
-    <row r="354" spans="1:12">
-      <c r="A354" s="28"/>
-      <c r="B354" s="28"/>
-      <c r="C354" s="24"/>
-      <c r="D354" s="24"/>
-      <c r="E354" s="24"/>
-      <c r="F354" s="24"/>
-      <c r="G354" s="24"/>
-      <c r="H354" s="24"/>
-      <c r="I354" s="24"/>
-      <c r="J354" s="24"/>
-      <c r="K354" s="24"/>
-      <c r="L354" s="24"/>
-    </row>
-    <row r="355" spans="1:12">
-      <c r="A355" s="28"/>
-      <c r="B355" s="28"/>
-      <c r="C355" s="24"/>
-      <c r="D355" s="24"/>
-      <c r="E355" s="24"/>
-      <c r="F355" s="24"/>
-      <c r="G355" s="24"/>
-      <c r="H355" s="24"/>
-      <c r="I355" s="24"/>
-      <c r="J355" s="24"/>
-      <c r="K355" s="24"/>
-      <c r="L355" s="24"/>
-    </row>
-    <row r="356" spans="1:12">
-      <c r="A356" s="28"/>
-      <c r="B356" s="28"/>
-      <c r="C356" s="24"/>
-      <c r="D356" s="24"/>
-      <c r="E356" s="24"/>
-      <c r="F356" s="24"/>
-      <c r="G356" s="24"/>
-      <c r="H356" s="24"/>
-      <c r="I356" s="24"/>
-      <c r="J356" s="24"/>
-      <c r="K356" s="24"/>
-      <c r="L356" s="24"/>
-    </row>
-    <row r="357" spans="1:12">
-      <c r="A357" s="28"/>
-      <c r="B357" s="28"/>
-      <c r="C357" s="24"/>
-      <c r="D357" s="24"/>
-      <c r="E357" s="24"/>
-      <c r="F357" s="24"/>
-      <c r="G357" s="24"/>
-      <c r="H357" s="24"/>
-      <c r="I357" s="24"/>
-      <c r="J357" s="24"/>
-      <c r="K357" s="24"/>
-      <c r="L357" s="24"/>
-    </row>
-    <row r="358" spans="1:12">
-      <c r="A358" s="28"/>
-      <c r="B358" s="28"/>
-      <c r="C358" s="24"/>
-      <c r="D358" s="24"/>
-      <c r="E358" s="24"/>
-      <c r="F358" s="24"/>
-      <c r="G358" s="24"/>
-      <c r="H358" s="24"/>
-      <c r="I358" s="24"/>
-      <c r="J358" s="24"/>
-      <c r="K358" s="24"/>
-      <c r="L358" s="24"/>
-    </row>
-    <row r="359" spans="1:12">
-      <c r="A359" s="28"/>
-      <c r="B359" s="28"/>
-      <c r="C359" s="24"/>
-      <c r="D359" s="24"/>
-      <c r="E359" s="24"/>
-      <c r="F359" s="24"/>
-      <c r="G359" s="24"/>
-      <c r="H359" s="24"/>
-      <c r="I359" s="24"/>
-      <c r="J359" s="24"/>
-      <c r="K359" s="24"/>
-      <c r="L359" s="24"/>
-    </row>
-    <row r="360" spans="1:12">
-      <c r="A360" s="28"/>
-      <c r="B360" s="28"/>
-      <c r="C360" s="24"/>
-      <c r="D360" s="24"/>
-      <c r="E360" s="24"/>
-      <c r="F360" s="24"/>
-      <c r="G360" s="24"/>
-      <c r="H360" s="24"/>
-      <c r="I360" s="24"/>
-      <c r="J360" s="24"/>
-      <c r="K360" s="24"/>
-      <c r="L360" s="24"/>
-    </row>
-    <row r="361" spans="1:12">
-      <c r="A361" s="28"/>
-      <c r="B361" s="28"/>
-      <c r="C361" s="24"/>
-      <c r="D361" s="24"/>
-      <c r="E361" s="24"/>
-      <c r="F361" s="24"/>
-      <c r="G361" s="24"/>
-      <c r="H361" s="24"/>
-      <c r="I361" s="24"/>
-      <c r="J361" s="24"/>
-      <c r="K361" s="24"/>
-      <c r="L361" s="24"/>
-    </row>
-    <row r="362" spans="1:12">
-      <c r="A362" s="28"/>
-      <c r="B362" s="28"/>
-      <c r="C362" s="24"/>
-      <c r="D362" s="24"/>
-      <c r="E362" s="24"/>
-      <c r="F362" s="24"/>
-      <c r="G362" s="24"/>
-      <c r="H362" s="24"/>
-      <c r="I362" s="24"/>
-      <c r="J362" s="24"/>
-      <c r="K362" s="24"/>
-      <c r="L362" s="24"/>
-    </row>
-    <row r="363" spans="1:12">
-      <c r="A363" s="28"/>
-      <c r="B363" s="28"/>
-      <c r="C363" s="24"/>
-      <c r="D363" s="24"/>
-      <c r="E363" s="24"/>
-      <c r="F363" s="24"/>
-      <c r="G363" s="24"/>
-      <c r="H363" s="24"/>
-      <c r="I363" s="24"/>
-      <c r="J363" s="24"/>
-      <c r="K363" s="24"/>
-      <c r="L363" s="24"/>
-    </row>
-    <row r="364" spans="1:12">
-      <c r="A364" s="28"/>
-      <c r="B364" s="28"/>
-      <c r="C364" s="24"/>
-      <c r="D364" s="24"/>
-      <c r="E364" s="24"/>
-      <c r="F364" s="24"/>
-      <c r="G364" s="24"/>
-      <c r="H364" s="24"/>
-      <c r="I364" s="24"/>
-      <c r="J364" s="24"/>
-      <c r="K364" s="24"/>
-      <c r="L364" s="24"/>
-    </row>
-    <row r="365" spans="1:12">
-      <c r="A365" s="28"/>
-      <c r="B365" s="28"/>
-      <c r="C365" s="24"/>
-      <c r="D365" s="24"/>
-      <c r="E365" s="24"/>
-      <c r="F365" s="24"/>
-      <c r="G365" s="24"/>
-      <c r="H365" s="24"/>
-      <c r="I365" s="24"/>
-      <c r="J365" s="24"/>
-      <c r="K365" s="24"/>
-      <c r="L365" s="24"/>
-    </row>
-    <row r="366" spans="1:12">
-      <c r="A366" s="28"/>
-      <c r="B366" s="28"/>
-      <c r="C366" s="24"/>
-      <c r="D366" s="24"/>
-      <c r="E366" s="24"/>
-      <c r="F366" s="24"/>
-      <c r="G366" s="24"/>
-      <c r="H366" s="24"/>
-      <c r="I366" s="24"/>
-      <c r="J366" s="24"/>
-      <c r="K366" s="24"/>
-      <c r="L366" s="24"/>
-    </row>
-    <row r="367" spans="1:12">
-      <c r="A367" s="28"/>
-      <c r="B367" s="28"/>
-      <c r="C367" s="24"/>
-      <c r="D367" s="24"/>
-      <c r="E367" s="24"/>
-      <c r="F367" s="24"/>
-      <c r="G367" s="24"/>
-      <c r="H367" s="24"/>
-      <c r="I367" s="24"/>
-      <c r="J367" s="24"/>
-      <c r="K367" s="24"/>
-      <c r="L367" s="24"/>
-    </row>
-    <row r="368" spans="1:12">
-      <c r="A368" s="28"/>
-      <c r="B368" s="28"/>
-      <c r="C368" s="24"/>
-      <c r="D368" s="24"/>
-      <c r="E368" s="24"/>
-      <c r="F368" s="24"/>
-      <c r="G368" s="24"/>
-      <c r="H368" s="24"/>
-      <c r="I368" s="24"/>
-      <c r="J368" s="24"/>
-      <c r="K368" s="24"/>
-      <c r="L368" s="24"/>
+      <c r="C320" s="14"/>
+      <c r="D320" s="14"/>
+      <c r="E320" s="14"/>
+      <c r="F320" s="14"/>
+      <c r="G320" s="14"/>
+      <c r="H320" s="14"/>
+      <c r="I320" s="14"/>
+      <c r="J320" s="14"/>
+      <c r="K320" s="14"/>
+      <c r="L320" s="14"/>
+    </row>
+    <row r="321" spans="3:12">
+      <c r="C321" s="14"/>
+      <c r="D321" s="14"/>
+      <c r="E321" s="14"/>
+      <c r="F321" s="14"/>
+      <c r="G321" s="14"/>
+      <c r="H321" s="14"/>
+      <c r="I321" s="14"/>
+      <c r="J321" s="14"/>
+      <c r="K321" s="14"/>
+      <c r="L321" s="14"/>
+    </row>
+    <row r="322" spans="3:12">
+      <c r="C322" s="14"/>
+      <c r="D322" s="14"/>
+      <c r="E322" s="14"/>
+      <c r="F322" s="14"/>
+      <c r="G322" s="14"/>
+      <c r="H322" s="14"/>
+      <c r="I322" s="14"/>
+      <c r="J322" s="14"/>
+      <c r="K322" s="14"/>
+      <c r="L322" s="14"/>
+    </row>
+    <row r="323" spans="3:12">
+      <c r="C323" s="14"/>
+      <c r="D323" s="14"/>
+      <c r="E323" s="14"/>
+      <c r="F323" s="14"/>
+      <c r="G323" s="14"/>
+      <c r="H323" s="14"/>
+      <c r="I323" s="14"/>
+      <c r="J323" s="14"/>
+      <c r="K323" s="14"/>
+      <c r="L323" s="14"/>
+    </row>
+    <row r="324" spans="3:12">
+      <c r="C324" s="14"/>
+      <c r="D324" s="14"/>
+      <c r="E324" s="14"/>
+      <c r="F324" s="14"/>
+      <c r="G324" s="14"/>
+      <c r="H324" s="14"/>
+      <c r="I324" s="14"/>
+      <c r="J324" s="14"/>
+      <c r="K324" s="14"/>
+      <c r="L324" s="14"/>
+    </row>
+    <row r="325" spans="3:12">
+      <c r="C325" s="14"/>
+      <c r="D325" s="14"/>
+      <c r="E325" s="14"/>
+      <c r="F325" s="14"/>
+      <c r="G325" s="14"/>
+      <c r="H325" s="14"/>
+      <c r="I325" s="14"/>
+      <c r="J325" s="14"/>
+      <c r="K325" s="14"/>
+      <c r="L325" s="14"/>
+    </row>
+    <row r="326" spans="3:12">
+      <c r="C326" s="14"/>
+      <c r="D326" s="14"/>
+      <c r="E326" s="14"/>
+      <c r="F326" s="14"/>
+      <c r="G326" s="14"/>
+      <c r="H326" s="14"/>
+      <c r="I326" s="14"/>
+      <c r="J326" s="14"/>
+      <c r="K326" s="14"/>
+      <c r="L326" s="14"/>
+    </row>
+    <row r="327" spans="3:12">
+      <c r="C327" s="14"/>
+      <c r="D327" s="14"/>
+      <c r="E327" s="14"/>
+      <c r="F327" s="14"/>
+      <c r="G327" s="14"/>
+      <c r="H327" s="14"/>
+      <c r="I327" s="14"/>
+      <c r="J327" s="14"/>
+      <c r="K327" s="14"/>
+      <c r="L327" s="14"/>
+    </row>
+    <row r="328" spans="3:12">
+      <c r="C328" s="14"/>
+      <c r="D328" s="14"/>
+      <c r="E328" s="14"/>
+      <c r="F328" s="14"/>
+      <c r="G328" s="14"/>
+      <c r="H328" s="14"/>
+      <c r="I328" s="14"/>
+      <c r="J328" s="14"/>
+      <c r="K328" s="14"/>
+      <c r="L328" s="14"/>
+    </row>
+    <row r="329" spans="3:12">
+      <c r="C329" s="14"/>
+      <c r="D329" s="14"/>
+      <c r="E329" s="14"/>
+      <c r="F329" s="14"/>
+      <c r="G329" s="14"/>
+      <c r="H329" s="14"/>
+      <c r="I329" s="14"/>
+      <c r="J329" s="14"/>
+      <c r="K329" s="14"/>
+      <c r="L329" s="14"/>
+    </row>
+    <row r="330" spans="3:12">
+      <c r="C330" s="14"/>
+      <c r="D330" s="14"/>
+      <c r="E330" s="14"/>
+      <c r="F330" s="14"/>
+      <c r="G330" s="14"/>
+      <c r="H330" s="14"/>
+      <c r="I330" s="14"/>
+      <c r="J330" s="14"/>
+      <c r="K330" s="14"/>
+      <c r="L330" s="14"/>
+    </row>
+    <row r="331" spans="3:12">
+      <c r="C331" s="14"/>
+      <c r="D331" s="14"/>
+      <c r="E331" s="14"/>
+      <c r="F331" s="14"/>
+      <c r="G331" s="14"/>
+      <c r="H331" s="14"/>
+      <c r="I331" s="14"/>
+      <c r="J331" s="14"/>
+      <c r="K331" s="14"/>
+      <c r="L331" s="14"/>
+    </row>
+    <row r="332" spans="3:12">
+      <c r="C332" s="14"/>
+      <c r="D332" s="14"/>
+      <c r="E332" s="14"/>
+      <c r="F332" s="14"/>
+      <c r="G332" s="14"/>
+      <c r="H332" s="14"/>
+      <c r="I332" s="14"/>
+      <c r="J332" s="14"/>
+      <c r="K332" s="14"/>
+      <c r="L332" s="14"/>
+    </row>
+    <row r="333" spans="3:12">
+      <c r="C333" s="14"/>
+      <c r="D333" s="14"/>
+      <c r="E333" s="14"/>
+      <c r="F333" s="14"/>
+      <c r="G333" s="14"/>
+      <c r="H333" s="14"/>
+      <c r="I333" s="14"/>
+      <c r="J333" s="14"/>
+      <c r="K333" s="14"/>
+      <c r="L333" s="14"/>
+    </row>
+    <row r="334" spans="3:12">
+      <c r="C334" s="14"/>
+      <c r="D334" s="14"/>
+      <c r="E334" s="14"/>
+      <c r="F334" s="14"/>
+      <c r="G334" s="14"/>
+      <c r="H334" s="14"/>
+      <c r="I334" s="14"/>
+      <c r="J334" s="14"/>
+      <c r="K334" s="14"/>
+      <c r="L334" s="14"/>
+    </row>
+    <row r="335" spans="3:12">
+      <c r="C335" s="14"/>
+      <c r="D335" s="14"/>
+      <c r="E335" s="14"/>
+      <c r="F335" s="14"/>
+      <c r="G335" s="14"/>
+      <c r="H335" s="14"/>
+      <c r="I335" s="14"/>
+      <c r="J335" s="14"/>
+      <c r="K335" s="14"/>
+      <c r="L335" s="14"/>
+    </row>
+    <row r="336" spans="3:12">
+      <c r="C336" s="14"/>
+      <c r="D336" s="14"/>
+      <c r="E336" s="14"/>
+      <c r="F336" s="14"/>
+      <c r="G336" s="14"/>
+      <c r="H336" s="14"/>
+      <c r="I336" s="14"/>
+      <c r="J336" s="14"/>
+      <c r="K336" s="14"/>
+      <c r="L336" s="14"/>
+    </row>
+    <row r="337" spans="3:12">
+      <c r="C337" s="14"/>
+      <c r="D337" s="14"/>
+      <c r="E337" s="14"/>
+      <c r="F337" s="14"/>
+      <c r="G337" s="14"/>
+      <c r="H337" s="14"/>
+      <c r="I337" s="14"/>
+      <c r="J337" s="14"/>
+      <c r="K337" s="14"/>
+      <c r="L337" s="14"/>
+    </row>
+    <row r="338" spans="3:12">
+      <c r="C338" s="14"/>
+      <c r="D338" s="14"/>
+      <c r="E338" s="14"/>
+      <c r="F338" s="14"/>
+      <c r="G338" s="14"/>
+      <c r="H338" s="14"/>
+      <c r="I338" s="14"/>
+      <c r="J338" s="14"/>
+      <c r="K338" s="14"/>
+      <c r="L338" s="14"/>
+    </row>
+    <row r="339" spans="3:12">
+      <c r="C339" s="14"/>
+      <c r="D339" s="14"/>
+      <c r="E339" s="14"/>
+      <c r="F339" s="14"/>
+      <c r="G339" s="14"/>
+      <c r="H339" s="14"/>
+      <c r="I339" s="14"/>
+      <c r="J339" s="14"/>
+      <c r="K339" s="14"/>
+      <c r="L339" s="14"/>
+    </row>
+    <row r="340" spans="3:12">
+      <c r="C340" s="14"/>
+      <c r="D340" s="14"/>
+      <c r="E340" s="14"/>
+      <c r="F340" s="14"/>
+      <c r="G340" s="14"/>
+      <c r="H340" s="14"/>
+      <c r="I340" s="14"/>
+      <c r="J340" s="14"/>
+      <c r="K340" s="14"/>
+      <c r="L340" s="14"/>
+    </row>
+    <row r="341" spans="3:12">
+      <c r="C341" s="14"/>
+      <c r="D341" s="14"/>
+      <c r="E341" s="14"/>
+      <c r="F341" s="14"/>
+      <c r="G341" s="14"/>
+      <c r="H341" s="14"/>
+      <c r="I341" s="14"/>
+      <c r="J341" s="14"/>
+      <c r="K341" s="14"/>
+      <c r="L341" s="14"/>
+    </row>
+    <row r="342" spans="3:12">
+      <c r="C342" s="14"/>
+      <c r="D342" s="14"/>
+      <c r="E342" s="14"/>
+      <c r="F342" s="14"/>
+      <c r="G342" s="14"/>
+      <c r="H342" s="14"/>
+      <c r="I342" s="14"/>
+      <c r="J342" s="14"/>
+      <c r="K342" s="14"/>
+      <c r="L342" s="14"/>
+    </row>
+    <row r="343" spans="3:12">
+      <c r="C343" s="14"/>
+      <c r="D343" s="14"/>
+      <c r="E343" s="14"/>
+      <c r="F343" s="14"/>
+      <c r="G343" s="14"/>
+      <c r="H343" s="14"/>
+      <c r="I343" s="14"/>
+      <c r="J343" s="14"/>
+      <c r="K343" s="14"/>
+      <c r="L343" s="14"/>
+    </row>
+    <row r="344" spans="3:12">
+      <c r="C344" s="14"/>
+      <c r="D344" s="14"/>
+      <c r="E344" s="14"/>
+      <c r="F344" s="14"/>
+      <c r="G344" s="14"/>
+      <c r="H344" s="14"/>
+      <c r="I344" s="14"/>
+      <c r="J344" s="14"/>
+      <c r="K344" s="14"/>
+      <c r="L344" s="14"/>
+    </row>
+    <row r="345" spans="3:12">
+      <c r="C345" s="14"/>
+      <c r="D345" s="14"/>
+      <c r="E345" s="14"/>
+      <c r="F345" s="14"/>
+      <c r="G345" s="14"/>
+      <c r="H345" s="14"/>
+      <c r="I345" s="14"/>
+      <c r="J345" s="14"/>
+      <c r="K345" s="14"/>
+      <c r="L345" s="14"/>
+    </row>
+    <row r="346" spans="3:12">
+      <c r="C346" s="14"/>
+      <c r="D346" s="14"/>
+      <c r="E346" s="14"/>
+      <c r="F346" s="14"/>
+      <c r="G346" s="14"/>
+      <c r="H346" s="14"/>
+      <c r="I346" s="14"/>
+      <c r="J346" s="14"/>
+      <c r="K346" s="14"/>
+      <c r="L346" s="14"/>
+    </row>
+    <row r="347" spans="3:12">
+      <c r="C347" s="14"/>
+      <c r="D347" s="14"/>
+      <c r="E347" s="14"/>
+      <c r="F347" s="14"/>
+      <c r="G347" s="14"/>
+      <c r="H347" s="14"/>
+      <c r="I347" s="14"/>
+      <c r="J347" s="14"/>
+      <c r="K347" s="14"/>
+      <c r="L347" s="14"/>
+    </row>
+    <row r="348" spans="3:12">
+      <c r="C348" s="14"/>
+      <c r="D348" s="14"/>
+      <c r="E348" s="14"/>
+      <c r="F348" s="14"/>
+      <c r="G348" s="14"/>
+      <c r="H348" s="14"/>
+      <c r="I348" s="14"/>
+      <c r="J348" s="14"/>
+      <c r="K348" s="14"/>
+      <c r="L348" s="14"/>
+    </row>
+    <row r="349" spans="3:12">
+      <c r="C349" s="14"/>
+      <c r="D349" s="14"/>
+      <c r="E349" s="14"/>
+      <c r="F349" s="14"/>
+      <c r="G349" s="14"/>
+      <c r="H349" s="14"/>
+      <c r="I349" s="14"/>
+      <c r="J349" s="14"/>
+      <c r="K349" s="14"/>
+      <c r="L349" s="14"/>
+    </row>
+    <row r="350" spans="3:12">
+      <c r="C350" s="14"/>
+      <c r="D350" s="14"/>
+      <c r="E350" s="14"/>
+      <c r="F350" s="14"/>
+      <c r="G350" s="14"/>
+      <c r="H350" s="14"/>
+      <c r="I350" s="14"/>
+      <c r="J350" s="14"/>
+      <c r="K350" s="14"/>
+      <c r="L350" s="14"/>
+    </row>
+    <row r="351" spans="3:12">
+      <c r="C351" s="14"/>
+      <c r="D351" s="14"/>
+      <c r="E351" s="14"/>
+      <c r="F351" s="14"/>
+      <c r="G351" s="14"/>
+      <c r="H351" s="14"/>
+      <c r="I351" s="14"/>
+      <c r="J351" s="14"/>
+      <c r="K351" s="14"/>
+      <c r="L351" s="14"/>
+    </row>
+    <row r="352" spans="3:12">
+      <c r="C352" s="14"/>
+      <c r="D352" s="14"/>
+      <c r="E352" s="14"/>
+      <c r="F352" s="14"/>
+      <c r="G352" s="14"/>
+      <c r="H352" s="14"/>
+      <c r="I352" s="14"/>
+      <c r="J352" s="14"/>
+      <c r="K352" s="14"/>
+      <c r="L352" s="14"/>
+    </row>
+    <row r="353" spans="3:12">
+      <c r="C353" s="14"/>
+      <c r="D353" s="14"/>
+      <c r="E353" s="14"/>
+      <c r="F353" s="14"/>
+      <c r="G353" s="14"/>
+      <c r="H353" s="14"/>
+      <c r="I353" s="14"/>
+      <c r="J353" s="14"/>
+      <c r="K353" s="14"/>
+      <c r="L353" s="14"/>
+    </row>
+    <row r="354" spans="3:12">
+      <c r="C354" s="14"/>
+      <c r="D354" s="14"/>
+      <c r="E354" s="14"/>
+      <c r="F354" s="14"/>
+      <c r="G354" s="14"/>
+      <c r="H354" s="14"/>
+      <c r="I354" s="14"/>
+      <c r="J354" s="14"/>
+      <c r="K354" s="14"/>
+      <c r="L354" s="14"/>
+    </row>
+    <row r="355" spans="3:12">
+      <c r="C355" s="14"/>
+      <c r="D355" s="14"/>
+      <c r="E355" s="14"/>
+      <c r="F355" s="14"/>
+      <c r="G355" s="14"/>
+      <c r="H355" s="14"/>
+      <c r="I355" s="14"/>
+      <c r="J355" s="14"/>
+      <c r="K355" s="14"/>
+      <c r="L355" s="14"/>
+    </row>
+    <row r="356" spans="3:12">
+      <c r="C356" s="14"/>
+      <c r="D356" s="14"/>
+      <c r="E356" s="14"/>
+      <c r="F356" s="14"/>
+      <c r="G356" s="14"/>
+      <c r="H356" s="14"/>
+      <c r="I356" s="14"/>
+      <c r="J356" s="14"/>
+      <c r="K356" s="14"/>
+      <c r="L356" s="14"/>
+    </row>
+    <row r="357" spans="3:12">
+      <c r="C357" s="14"/>
+      <c r="D357" s="14"/>
+      <c r="E357" s="14"/>
+      <c r="F357" s="14"/>
+      <c r="G357" s="14"/>
+      <c r="H357" s="14"/>
+      <c r="I357" s="14"/>
+      <c r="J357" s="14"/>
+      <c r="K357" s="14"/>
+      <c r="L357" s="14"/>
+    </row>
+    <row r="358" spans="3:12">
+      <c r="C358" s="14"/>
+      <c r="D358" s="14"/>
+      <c r="E358" s="14"/>
+      <c r="F358" s="14"/>
+      <c r="G358" s="14"/>
+      <c r="H358" s="14"/>
+      <c r="I358" s="14"/>
+      <c r="J358" s="14"/>
+      <c r="K358" s="14"/>
+      <c r="L358" s="14"/>
+    </row>
+    <row r="359" spans="3:12">
+      <c r="C359" s="14"/>
+      <c r="D359" s="14"/>
+      <c r="E359" s="14"/>
+      <c r="F359" s="14"/>
+      <c r="G359" s="14"/>
+      <c r="H359" s="14"/>
+      <c r="I359" s="14"/>
+      <c r="J359" s="14"/>
+      <c r="K359" s="14"/>
+      <c r="L359" s="14"/>
+    </row>
+    <row r="360" spans="3:12">
+      <c r="C360" s="14"/>
+      <c r="D360" s="14"/>
+      <c r="E360" s="14"/>
+      <c r="F360" s="14"/>
+      <c r="G360" s="14"/>
+      <c r="H360" s="14"/>
+      <c r="I360" s="14"/>
+      <c r="J360" s="14"/>
+      <c r="K360" s="14"/>
+      <c r="L360" s="14"/>
+    </row>
+    <row r="361" spans="3:12">
+      <c r="C361" s="14"/>
+      <c r="D361" s="14"/>
+      <c r="E361" s="14"/>
+      <c r="F361" s="14"/>
+      <c r="G361" s="14"/>
+      <c r="H361" s="14"/>
+      <c r="I361" s="14"/>
+      <c r="J361" s="14"/>
+      <c r="K361" s="14"/>
+      <c r="L361" s="14"/>
+    </row>
+    <row r="362" spans="3:12">
+      <c r="C362" s="14"/>
+      <c r="D362" s="14"/>
+      <c r="E362" s="14"/>
+      <c r="F362" s="14"/>
+      <c r="G362" s="14"/>
+      <c r="H362" s="14"/>
+      <c r="I362" s="14"/>
+      <c r="J362" s="14"/>
+      <c r="K362" s="14"/>
+      <c r="L362" s="14"/>
+    </row>
+    <row r="363" spans="3:12">
+      <c r="C363" s="14"/>
+      <c r="D363" s="14"/>
+      <c r="E363" s="14"/>
+      <c r="F363" s="14"/>
+      <c r="G363" s="14"/>
+      <c r="H363" s="14"/>
+      <c r="I363" s="14"/>
+      <c r="J363" s="14"/>
+      <c r="K363" s="14"/>
+      <c r="L363" s="14"/>
+    </row>
+    <row r="364" spans="3:12">
+      <c r="C364" s="14"/>
+      <c r="D364" s="14"/>
+      <c r="E364" s="14"/>
+      <c r="F364" s="14"/>
+      <c r="G364" s="14"/>
+      <c r="H364" s="14"/>
+      <c r="I364" s="14"/>
+      <c r="J364" s="14"/>
+      <c r="K364" s="14"/>
+      <c r="L364" s="14"/>
+    </row>
+    <row r="365" spans="3:12">
+      <c r="C365" s="14"/>
+      <c r="D365" s="14"/>
+      <c r="E365" s="14"/>
+      <c r="F365" s="14"/>
+      <c r="G365" s="14"/>
+      <c r="H365" s="14"/>
+      <c r="I365" s="14"/>
+      <c r="J365" s="14"/>
+      <c r="K365" s="14"/>
+      <c r="L365" s="14"/>
+    </row>
+    <row r="366" spans="3:12">
+      <c r="C366" s="14"/>
+      <c r="D366" s="14"/>
+      <c r="E366" s="14"/>
+      <c r="F366" s="14"/>
+      <c r="G366" s="14"/>
+      <c r="H366" s="14"/>
+      <c r="I366" s="14"/>
+      <c r="J366" s="14"/>
+      <c r="K366" s="14"/>
+      <c r="L366" s="14"/>
+    </row>
+    <row r="367" spans="3:12">
+      <c r="C367" s="14"/>
+      <c r="D367" s="14"/>
+      <c r="E367" s="14"/>
+      <c r="F367" s="14"/>
+      <c r="G367" s="14"/>
+      <c r="H367" s="14"/>
+      <c r="I367" s="14"/>
+      <c r="J367" s="14"/>
+      <c r="K367" s="14"/>
+      <c r="L367" s="14"/>
+    </row>
+    <row r="368" spans="3:12">
+      <c r="C368" s="14"/>
+      <c r="D368" s="14"/>
+      <c r="E368" s="14"/>
+      <c r="F368" s="14"/>
+      <c r="G368" s="14"/>
+      <c r="H368" s="14"/>
+      <c r="I368" s="14"/>
+      <c r="J368" s="14"/>
+      <c r="K368" s="14"/>
+      <c r="L368" s="14"/>
     </row>
     <row r="369" spans="1:12">
-      <c r="A369" s="28"/>
-      <c r="B369" s="28"/>
-      <c r="C369" s="24"/>
-      <c r="D369" s="24"/>
-      <c r="E369" s="24"/>
-      <c r="F369" s="24"/>
-      <c r="G369" s="24"/>
-      <c r="H369" s="24"/>
-      <c r="I369" s="24"/>
-      <c r="J369" s="24"/>
-      <c r="K369" s="24"/>
-      <c r="L369" s="24"/>
+      <c r="C369" s="14"/>
+      <c r="D369" s="14"/>
+      <c r="E369" s="14"/>
+      <c r="F369" s="14"/>
+      <c r="G369" s="14"/>
+      <c r="H369" s="14"/>
+      <c r="I369" s="14"/>
+      <c r="J369" s="14"/>
+      <c r="K369" s="14"/>
+      <c r="L369" s="14"/>
     </row>
     <row r="370" spans="1:12">
-      <c r="A370" s="28"/>
-      <c r="B370" s="28"/>
-      <c r="C370" s="24"/>
-      <c r="D370" s="24"/>
-      <c r="E370" s="24"/>
-      <c r="F370" s="24"/>
-      <c r="G370" s="24"/>
-      <c r="H370" s="24"/>
-      <c r="I370" s="24"/>
-      <c r="J370" s="24"/>
-      <c r="K370" s="24"/>
-      <c r="L370" s="24"/>
+      <c r="C370" s="14"/>
+      <c r="D370" s="14"/>
+      <c r="E370" s="14"/>
+      <c r="F370" s="14"/>
+      <c r="G370" s="14"/>
+      <c r="H370" s="14"/>
+      <c r="I370" s="14"/>
+      <c r="J370" s="14"/>
+      <c r="K370" s="14"/>
+      <c r="L370" s="14"/>
     </row>
     <row r="371" spans="1:12">
-      <c r="A371" s="28"/>
-      <c r="B371" s="28"/>
-      <c r="C371" s="24"/>
-      <c r="D371" s="24"/>
-      <c r="E371" s="24"/>
-      <c r="F371" s="24"/>
-      <c r="G371" s="24"/>
-      <c r="H371" s="24"/>
-      <c r="I371" s="24"/>
-      <c r="J371" s="24"/>
-      <c r="K371" s="24"/>
-      <c r="L371" s="24"/>
+      <c r="C371" s="14"/>
+      <c r="D371" s="14"/>
+      <c r="E371" s="14"/>
+      <c r="F371" s="14"/>
+      <c r="G371" s="14"/>
+      <c r="H371" s="14"/>
+      <c r="I371" s="14"/>
+      <c r="J371" s="14"/>
+      <c r="K371" s="14"/>
+      <c r="L371" s="14"/>
     </row>
     <row r="372" spans="1:12">
-      <c r="A372" s="28"/>
-      <c r="B372" s="28"/>
-      <c r="C372" s="24"/>
-      <c r="D372" s="24"/>
-      <c r="E372" s="24"/>
-      <c r="F372" s="24"/>
-      <c r="G372" s="24"/>
-      <c r="H372" s="24"/>
-      <c r="I372" s="24"/>
-      <c r="J372" s="24"/>
-      <c r="K372" s="24"/>
-      <c r="L372" s="24"/>
+      <c r="C372" s="14"/>
+      <c r="D372" s="14"/>
+      <c r="E372" s="14"/>
+      <c r="F372" s="14"/>
+      <c r="G372" s="14"/>
+      <c r="H372" s="14"/>
+      <c r="I372" s="14"/>
+      <c r="J372" s="14"/>
+      <c r="K372" s="14"/>
+      <c r="L372" s="14"/>
     </row>
     <row r="373" spans="1:12">
-      <c r="A373" s="28"/>
-      <c r="B373" s="28"/>
-      <c r="C373" s="24"/>
-      <c r="D373" s="24"/>
-      <c r="E373" s="24"/>
-      <c r="F373" s="24"/>
-      <c r="G373" s="24"/>
-      <c r="H373" s="24"/>
-      <c r="I373" s="24"/>
-      <c r="J373" s="24"/>
-      <c r="K373" s="24"/>
-      <c r="L373" s="24"/>
+      <c r="C373" s="14"/>
+      <c r="D373" s="14"/>
+      <c r="E373" s="14"/>
+      <c r="F373" s="14"/>
+      <c r="G373" s="14"/>
+      <c r="H373" s="14"/>
+      <c r="I373" s="14"/>
+      <c r="J373" s="14"/>
+      <c r="K373" s="14"/>
+      <c r="L373" s="14"/>
     </row>
     <row r="374" spans="1:12">
-      <c r="A374" s="28"/>
-      <c r="B374" s="28"/>
-      <c r="C374" s="24"/>
-      <c r="D374" s="24"/>
-      <c r="E374" s="24"/>
-      <c r="F374" s="24"/>
-      <c r="G374" s="24"/>
-      <c r="H374" s="24"/>
-      <c r="I374" s="24"/>
-      <c r="J374" s="24"/>
-      <c r="K374" s="24"/>
-      <c r="L374" s="24"/>
+      <c r="C374" s="14"/>
+      <c r="D374" s="14"/>
+      <c r="E374" s="14"/>
+      <c r="F374" s="14"/>
+      <c r="G374" s="14"/>
+      <c r="H374" s="14"/>
+      <c r="I374" s="14"/>
+      <c r="J374" s="14"/>
+      <c r="K374" s="14"/>
+      <c r="L374" s="14"/>
     </row>
     <row r="375" spans="1:12">
-      <c r="A375" s="28"/>
-      <c r="B375" s="28"/>
-      <c r="C375" s="24"/>
-      <c r="D375" s="24"/>
-      <c r="E375" s="24"/>
-      <c r="F375" s="24"/>
-      <c r="G375" s="24"/>
-      <c r="H375" s="24"/>
-      <c r="I375" s="24"/>
-      <c r="J375" s="24"/>
-      <c r="K375" s="24"/>
-      <c r="L375" s="24"/>
+      <c r="C375" s="14"/>
+      <c r="D375" s="14"/>
+      <c r="E375" s="14"/>
+      <c r="F375" s="14"/>
+      <c r="G375" s="14"/>
+      <c r="H375" s="14"/>
+      <c r="I375" s="14"/>
+      <c r="J375" s="14"/>
+      <c r="K375" s="14"/>
+      <c r="L375" s="14"/>
     </row>
     <row r="376" spans="1:12">
-      <c r="A376" s="28"/>
-      <c r="B376" s="28"/>
-      <c r="C376" s="24"/>
-      <c r="D376" s="24"/>
-      <c r="E376" s="24"/>
-      <c r="F376" s="24"/>
-      <c r="G376" s="24"/>
-      <c r="H376" s="24"/>
-      <c r="I376" s="24"/>
-      <c r="J376" s="24"/>
-      <c r="K376" s="24"/>
-      <c r="L376" s="24"/>
+      <c r="C376" s="14"/>
+      <c r="D376" s="14"/>
+      <c r="E376" s="14"/>
+      <c r="F376" s="14"/>
+      <c r="G376" s="14"/>
+      <c r="H376" s="14"/>
+      <c r="I376" s="14"/>
+      <c r="J376" s="14"/>
+      <c r="K376" s="14"/>
+      <c r="L376" s="14"/>
     </row>
     <row r="377" spans="1:12">
-      <c r="A377" s="28"/>
-      <c r="B377" s="28"/>
-      <c r="C377" s="24"/>
-      <c r="D377" s="24"/>
-      <c r="E377" s="24"/>
-      <c r="F377" s="24"/>
-      <c r="G377" s="24"/>
-      <c r="H377" s="24"/>
-      <c r="I377" s="24"/>
-      <c r="J377" s="24"/>
-      <c r="K377" s="24"/>
-      <c r="L377" s="24"/>
+      <c r="C377" s="14"/>
+      <c r="D377" s="14"/>
+      <c r="E377" s="14"/>
+      <c r="F377" s="14"/>
+      <c r="G377" s="14"/>
+      <c r="H377" s="14"/>
+      <c r="I377" s="14"/>
+      <c r="J377" s="14"/>
+      <c r="K377" s="14"/>
+      <c r="L377" s="14"/>
     </row>
     <row r="378" spans="1:12">
-      <c r="A378" s="28"/>
-      <c r="B378" s="28"/>
-      <c r="C378" s="24"/>
-      <c r="D378" s="24"/>
-      <c r="E378" s="24"/>
-      <c r="F378" s="24"/>
-      <c r="G378" s="24"/>
-      <c r="H378" s="24"/>
-      <c r="I378" s="24"/>
-      <c r="J378" s="24"/>
-      <c r="K378" s="24"/>
-      <c r="L378" s="24"/>
+      <c r="C378" s="14"/>
+      <c r="D378" s="14"/>
+      <c r="E378" s="14"/>
+      <c r="F378" s="14"/>
+      <c r="G378" s="14"/>
+      <c r="H378" s="14"/>
+      <c r="I378" s="14"/>
+      <c r="J378" s="14"/>
+      <c r="K378" s="14"/>
+      <c r="L378" s="14"/>
     </row>
     <row r="379" spans="1:12">
-      <c r="A379" s="28"/>
-      <c r="B379" s="28"/>
-      <c r="C379" s="24"/>
-      <c r="D379" s="24"/>
-      <c r="E379" s="24"/>
-      <c r="F379" s="24"/>
-      <c r="G379" s="24"/>
-      <c r="H379" s="24"/>
-      <c r="I379" s="24"/>
-      <c r="J379" s="24"/>
-      <c r="K379" s="24"/>
-      <c r="L379" s="24"/>
+      <c r="C379" s="14"/>
+      <c r="D379" s="14"/>
+      <c r="E379" s="14"/>
+      <c r="F379" s="14"/>
+      <c r="G379" s="14"/>
+      <c r="H379" s="14"/>
+      <c r="I379" s="14"/>
+      <c r="J379" s="14"/>
+      <c r="K379" s="14"/>
+      <c r="L379" s="14"/>
     </row>
     <row r="380" spans="1:12">
-      <c r="A380" s="26"/>
-      <c r="B380" s="26"/>
-      <c r="C380" s="27"/>
-      <c r="D380" s="27"/>
-      <c r="E380" s="27"/>
-      <c r="F380" s="27"/>
-      <c r="G380" s="27"/>
-      <c r="H380" s="27"/>
-      <c r="I380" s="27"/>
-      <c r="J380" s="27"/>
-      <c r="K380" s="27"/>
-      <c r="L380" s="27"/>
+      <c r="A380" s="13"/>
+      <c r="B380" s="13"/>
+      <c r="C380" s="7"/>
+      <c r="D380" s="7"/>
+      <c r="E380" s="7"/>
+      <c r="F380" s="7"/>
+      <c r="G380" s="7"/>
+      <c r="H380" s="7"/>
+      <c r="I380" s="7"/>
+      <c r="J380" s="7"/>
+      <c r="K380" s="7"/>
+      <c r="L380" s="7"/>
     </row>
     <row r="381" spans="1:12">
-      <c r="A381" s="28"/>
-      <c r="B381" s="28"/>
-      <c r="C381" s="24"/>
-      <c r="D381" s="24"/>
-      <c r="E381" s="24"/>
-      <c r="F381" s="24"/>
-      <c r="G381" s="24"/>
-      <c r="H381" s="24"/>
-      <c r="I381" s="24"/>
-      <c r="J381" s="24"/>
-      <c r="K381" s="24"/>
-      <c r="L381" s="24"/>
+      <c r="C381" s="14"/>
+      <c r="D381" s="14"/>
+      <c r="E381" s="14"/>
+      <c r="F381" s="14"/>
+      <c r="G381" s="14"/>
+      <c r="H381" s="14"/>
+      <c r="I381" s="14"/>
+      <c r="J381" s="14"/>
+      <c r="K381" s="14"/>
+      <c r="L381" s="14"/>
     </row>
     <row r="382" spans="1:12">
-      <c r="A382" s="28"/>
-      <c r="B382" s="28"/>
-      <c r="C382" s="24"/>
-      <c r="D382" s="24"/>
-      <c r="E382" s="24"/>
-      <c r="F382" s="24"/>
-      <c r="G382" s="24"/>
-      <c r="H382" s="24"/>
-      <c r="I382" s="24"/>
-      <c r="J382" s="24"/>
-      <c r="K382" s="24"/>
-      <c r="L382" s="24"/>
+      <c r="C382" s="14"/>
+      <c r="D382" s="14"/>
+      <c r="E382" s="14"/>
+      <c r="F382" s="14"/>
+      <c r="G382" s="14"/>
+      <c r="H382" s="14"/>
+      <c r="I382" s="14"/>
+      <c r="J382" s="14"/>
+      <c r="K382" s="14"/>
+      <c r="L382" s="14"/>
     </row>
     <row r="383" spans="1:12">
-      <c r="A383" s="28"/>
-      <c r="B383" s="28"/>
-      <c r="C383" s="24"/>
-      <c r="D383" s="24"/>
-      <c r="E383" s="24"/>
-      <c r="F383" s="24"/>
-      <c r="G383" s="24"/>
-      <c r="H383" s="24"/>
-      <c r="I383" s="24"/>
-      <c r="J383" s="24"/>
-      <c r="K383" s="24"/>
-      <c r="L383" s="24"/>
+      <c r="C383" s="14"/>
+      <c r="D383" s="14"/>
+      <c r="E383" s="14"/>
+      <c r="F383" s="14"/>
+      <c r="G383" s="14"/>
+      <c r="H383" s="14"/>
+      <c r="I383" s="14"/>
+      <c r="J383" s="14"/>
+      <c r="K383" s="14"/>
+      <c r="L383" s="14"/>
     </row>
     <row r="384" spans="1:12">
-      <c r="A384" s="28"/>
-      <c r="B384" s="28"/>
-      <c r="C384" s="24"/>
-      <c r="D384" s="24"/>
-      <c r="E384" s="24"/>
-      <c r="F384" s="24"/>
-      <c r="G384" s="24"/>
-      <c r="H384" s="24"/>
-      <c r="I384" s="24"/>
-      <c r="J384" s="24"/>
-      <c r="K384" s="24"/>
-      <c r="L384" s="24"/>
-    </row>
-    <row r="385" spans="1:12">
-      <c r="A385" s="28"/>
-      <c r="B385" s="28"/>
-      <c r="C385" s="24"/>
-      <c r="D385" s="24"/>
-      <c r="E385" s="24"/>
-      <c r="F385" s="24"/>
-      <c r="G385" s="24"/>
-      <c r="H385" s="24"/>
-      <c r="I385" s="24"/>
-      <c r="J385" s="24"/>
-      <c r="K385" s="24"/>
-      <c r="L385" s="24"/>
-    </row>
-    <row r="386" spans="1:12">
-      <c r="A386" s="28"/>
-      <c r="B386" s="28"/>
-      <c r="C386" s="24"/>
-      <c r="D386" s="24"/>
-      <c r="E386" s="24"/>
-      <c r="F386" s="24"/>
-      <c r="G386" s="24"/>
-      <c r="H386" s="24"/>
-      <c r="I386" s="24"/>
-      <c r="J386" s="24"/>
-      <c r="K386" s="24"/>
-      <c r="L386" s="24"/>
-    </row>
-    <row r="387" spans="1:12">
-      <c r="A387" s="28"/>
-      <c r="B387" s="28"/>
-      <c r="C387" s="24"/>
-      <c r="D387" s="24"/>
-      <c r="E387" s="24"/>
-      <c r="F387" s="24"/>
-      <c r="G387" s="24"/>
-      <c r="H387" s="24"/>
-      <c r="I387" s="24"/>
-      <c r="J387" s="24"/>
-      <c r="K387" s="24"/>
-      <c r="L387" s="24"/>
-    </row>
-    <row r="388" spans="1:12">
-      <c r="A388" s="28"/>
-      <c r="B388" s="28"/>
-      <c r="C388" s="24"/>
-      <c r="D388" s="24"/>
-      <c r="E388" s="24"/>
-      <c r="F388" s="24"/>
-      <c r="G388" s="24"/>
-      <c r="H388" s="24"/>
-      <c r="I388" s="24"/>
-      <c r="J388" s="24"/>
-      <c r="K388" s="24"/>
-      <c r="L388" s="24"/>
-    </row>
-    <row r="389" spans="1:12">
-      <c r="A389" s="28"/>
-      <c r="B389" s="28"/>
-      <c r="C389" s="24"/>
-      <c r="D389" s="24"/>
-      <c r="E389" s="24"/>
-      <c r="F389" s="24"/>
-      <c r="G389" s="24"/>
-      <c r="H389" s="24"/>
-      <c r="I389" s="24"/>
-      <c r="J389" s="24"/>
-      <c r="K389" s="24"/>
-      <c r="L389" s="24"/>
-    </row>
-    <row r="390" spans="1:12">
-      <c r="A390" s="28"/>
-      <c r="B390" s="28"/>
-      <c r="C390" s="24"/>
-      <c r="D390" s="24"/>
-      <c r="E390" s="24"/>
-      <c r="F390" s="24"/>
-      <c r="G390" s="24"/>
-      <c r="H390" s="24"/>
-      <c r="I390" s="24"/>
-      <c r="J390" s="24"/>
-      <c r="K390" s="24"/>
-      <c r="L390" s="24"/>
-    </row>
-    <row r="391" spans="1:12">
-      <c r="A391" s="28"/>
-      <c r="B391" s="28"/>
-      <c r="C391" s="24"/>
-      <c r="D391" s="24"/>
-      <c r="E391" s="24"/>
-      <c r="F391" s="24"/>
-      <c r="G391" s="24"/>
-      <c r="H391" s="24"/>
-      <c r="I391" s="24"/>
-      <c r="J391" s="24"/>
-      <c r="K391" s="24"/>
-      <c r="L391" s="24"/>
-    </row>
-    <row r="392" spans="1:12">
-      <c r="A392" s="28"/>
-      <c r="B392" s="28"/>
-      <c r="C392" s="24"/>
-      <c r="D392" s="24"/>
-      <c r="E392" s="24"/>
-      <c r="F392" s="24"/>
-      <c r="G392" s="24"/>
-      <c r="H392" s="24"/>
-      <c r="I392" s="24"/>
-      <c r="J392" s="24"/>
-      <c r="K392" s="24"/>
-      <c r="L392" s="24"/>
-    </row>
-    <row r="393" spans="1:12">
-      <c r="A393" s="28"/>
-      <c r="B393" s="28"/>
-      <c r="C393" s="24"/>
-      <c r="D393" s="24"/>
-      <c r="E393" s="24"/>
-      <c r="F393" s="24"/>
-      <c r="G393" s="24"/>
-      <c r="H393" s="24"/>
-      <c r="I393" s="24"/>
-      <c r="J393" s="24"/>
-      <c r="K393" s="24"/>
-      <c r="L393" s="24"/>
-    </row>
-    <row r="394" spans="1:12">
-      <c r="A394" s="28"/>
-      <c r="B394" s="28"/>
-      <c r="C394" s="24"/>
-      <c r="D394" s="24"/>
-      <c r="E394" s="24"/>
-      <c r="F394" s="24"/>
-      <c r="G394" s="24"/>
-      <c r="H394" s="24"/>
-      <c r="I394" s="24"/>
-      <c r="J394" s="24"/>
-      <c r="K394" s="24"/>
-      <c r="L394" s="24"/>
-    </row>
-    <row r="395" spans="1:12">
-      <c r="A395" s="28"/>
-      <c r="B395" s="28"/>
-      <c r="C395" s="24"/>
-      <c r="D395" s="24"/>
-      <c r="E395" s="24"/>
-      <c r="F395" s="24"/>
-      <c r="G395" s="24"/>
-      <c r="H395" s="24"/>
-      <c r="I395" s="24"/>
-      <c r="J395" s="24"/>
-      <c r="K395" s="24"/>
-      <c r="L395" s="24"/>
-    </row>
-    <row r="396" spans="1:12">
-      <c r="A396" s="28"/>
-      <c r="B396" s="28"/>
-      <c r="C396" s="24"/>
-      <c r="D396" s="24"/>
-      <c r="E396" s="24"/>
-      <c r="F396" s="24"/>
-      <c r="G396" s="24"/>
-      <c r="H396" s="24"/>
-      <c r="I396" s="24"/>
-      <c r="J396" s="24"/>
-      <c r="K396" s="24"/>
-      <c r="L396" s="24"/>
-    </row>
-    <row r="397" spans="1:12">
-      <c r="A397" s="28"/>
-      <c r="B397" s="28"/>
-      <c r="C397" s="24"/>
-      <c r="D397" s="24"/>
-      <c r="E397" s="24"/>
-      <c r="F397" s="24"/>
-      <c r="G397" s="24"/>
-      <c r="H397" s="24"/>
-      <c r="I397" s="24"/>
-      <c r="J397" s="24"/>
-      <c r="K397" s="24"/>
-      <c r="L397" s="24"/>
-    </row>
-    <row r="398" spans="1:12">
-      <c r="A398" s="28"/>
-      <c r="B398" s="28"/>
-      <c r="C398" s="24"/>
-      <c r="D398" s="24"/>
-      <c r="E398" s="24"/>
-      <c r="F398" s="24"/>
-      <c r="G398" s="24"/>
-      <c r="H398" s="24"/>
-      <c r="I398" s="24"/>
-      <c r="J398" s="24"/>
-      <c r="K398" s="24"/>
-      <c r="L398" s="24"/>
-    </row>
-    <row r="399" spans="1:12">
-      <c r="A399" s="28"/>
-      <c r="B399" s="28"/>
-      <c r="C399" s="24"/>
-      <c r="D399" s="24"/>
-      <c r="E399" s="24"/>
-      <c r="F399" s="24"/>
-      <c r="G399" s="24"/>
-      <c r="H399" s="24"/>
-      <c r="I399" s="24"/>
-      <c r="J399" s="24"/>
-      <c r="K399" s="24"/>
-      <c r="L399" s="24"/>
-    </row>
-    <row r="400" spans="1:12">
-      <c r="A400" s="28"/>
-      <c r="B400" s="28"/>
-      <c r="C400" s="24"/>
-      <c r="D400" s="24"/>
-      <c r="E400" s="24"/>
-      <c r="F400" s="24"/>
-      <c r="G400" s="24"/>
-      <c r="H400" s="24"/>
-      <c r="I400" s="24"/>
-      <c r="J400" s="24"/>
-      <c r="K400" s="24"/>
-      <c r="L400" s="24"/>
-    </row>
-    <row r="401" spans="1:12">
-      <c r="A401" s="28"/>
-      <c r="B401" s="28"/>
-      <c r="C401" s="24"/>
-      <c r="D401" s="24"/>
-      <c r="E401" s="24"/>
-      <c r="F401" s="24"/>
-      <c r="G401" s="24"/>
-      <c r="H401" s="24"/>
-      <c r="I401" s="24"/>
-      <c r="J401" s="24"/>
-      <c r="K401" s="24"/>
-      <c r="L401" s="24"/>
-    </row>
-    <row r="402" spans="1:12">
-      <c r="A402" s="28"/>
-      <c r="B402" s="28"/>
-      <c r="C402" s="24"/>
-      <c r="D402" s="24"/>
-      <c r="E402" s="24"/>
-      <c r="F402" s="24"/>
-      <c r="G402" s="24"/>
-      <c r="H402" s="24"/>
-      <c r="I402" s="24"/>
-      <c r="J402" s="24"/>
-      <c r="K402" s="24"/>
-      <c r="L402" s="24"/>
-    </row>
-    <row r="403" spans="1:12">
-      <c r="A403" s="28"/>
-      <c r="B403" s="28"/>
-      <c r="C403" s="24"/>
-      <c r="D403" s="24"/>
-      <c r="E403" s="24"/>
-      <c r="F403" s="24"/>
-      <c r="G403" s="24"/>
-      <c r="H403" s="24"/>
-      <c r="I403" s="24"/>
-      <c r="J403" s="24"/>
-      <c r="K403" s="24"/>
-      <c r="L403" s="24"/>
-    </row>
-    <row r="404" spans="1:12">
-      <c r="A404" s="28"/>
-      <c r="B404" s="28"/>
-      <c r="C404" s="24"/>
-      <c r="D404" s="24"/>
-      <c r="E404" s="24"/>
-      <c r="F404" s="24"/>
-      <c r="G404" s="24"/>
-      <c r="H404" s="24"/>
-      <c r="I404" s="24"/>
-      <c r="J404" s="24"/>
-      <c r="K404" s="24"/>
-      <c r="L404" s="24"/>
-    </row>
-    <row r="405" spans="1:12">
-      <c r="A405" s="28"/>
-      <c r="B405" s="28"/>
-      <c r="C405" s="24"/>
-      <c r="D405" s="24"/>
-      <c r="E405" s="24"/>
-      <c r="F405" s="24"/>
-      <c r="G405" s="24"/>
-      <c r="H405" s="24"/>
-      <c r="I405" s="24"/>
-      <c r="J405" s="24"/>
-      <c r="K405" s="24"/>
-      <c r="L405" s="24"/>
-    </row>
-    <row r="406" spans="1:12">
-      <c r="A406" s="28"/>
-      <c r="B406" s="28"/>
-      <c r="C406" s="24"/>
-      <c r="D406" s="24"/>
-      <c r="E406" s="24"/>
-      <c r="F406" s="24"/>
-      <c r="G406" s="24"/>
-      <c r="H406" s="24"/>
-      <c r="I406" s="24"/>
-      <c r="J406" s="24"/>
-      <c r="K406" s="24"/>
-      <c r="L406" s="24"/>
-    </row>
-    <row r="407" spans="1:12">
-      <c r="A407" s="28"/>
-      <c r="B407" s="28"/>
-      <c r="C407" s="24"/>
-      <c r="D407" s="24"/>
-      <c r="E407" s="24"/>
-      <c r="F407" s="24"/>
-      <c r="G407" s="24"/>
-      <c r="H407" s="24"/>
-      <c r="I407" s="24"/>
-      <c r="J407" s="24"/>
-      <c r="K407" s="24"/>
-      <c r="L407" s="24"/>
-    </row>
-    <row r="408" spans="1:12">
-      <c r="A408" s="28"/>
-      <c r="B408" s="28"/>
-      <c r="C408" s="24"/>
-      <c r="D408" s="24"/>
-      <c r="E408" s="24"/>
-      <c r="F408" s="24"/>
-      <c r="G408" s="24"/>
-      <c r="H408" s="24"/>
-      <c r="I408" s="24"/>
-      <c r="J408" s="24"/>
-      <c r="K408" s="24"/>
-      <c r="L408" s="24"/>
-    </row>
-    <row r="409" spans="1:12">
-      <c r="A409" s="28"/>
-      <c r="B409" s="28"/>
-      <c r="C409" s="24"/>
-      <c r="D409" s="24"/>
-      <c r="E409" s="24"/>
-      <c r="F409" s="24"/>
-      <c r="G409" s="24"/>
-      <c r="H409" s="24"/>
-      <c r="I409" s="24"/>
-      <c r="J409" s="24"/>
-      <c r="K409" s="24"/>
-      <c r="L409" s="24"/>
-    </row>
-    <row r="410" spans="1:12">
-      <c r="A410" s="28"/>
-      <c r="B410" s="28"/>
-      <c r="C410" s="24"/>
-      <c r="D410" s="24"/>
-      <c r="E410" s="24"/>
-      <c r="F410" s="24"/>
-      <c r="G410" s="24"/>
-      <c r="H410" s="24"/>
-      <c r="I410" s="24"/>
-      <c r="J410" s="24"/>
-      <c r="K410" s="24"/>
-      <c r="L410" s="24"/>
-    </row>
-    <row r="411" spans="1:12">
-      <c r="A411" s="28"/>
-      <c r="B411" s="28"/>
-      <c r="C411" s="24"/>
-      <c r="D411" s="24"/>
-      <c r="E411" s="24"/>
-      <c r="F411" s="24"/>
-      <c r="G411" s="24"/>
-      <c r="H411" s="24"/>
-      <c r="I411" s="24"/>
-      <c r="J411" s="24"/>
-      <c r="K411" s="24"/>
-      <c r="L411" s="24"/>
-    </row>
-    <row r="412" spans="1:12">
-      <c r="A412" s="28"/>
-      <c r="B412" s="28"/>
-      <c r="C412" s="24"/>
-      <c r="D412" s="24"/>
-      <c r="E412" s="24"/>
-      <c r="F412" s="24"/>
-      <c r="G412" s="24"/>
-      <c r="H412" s="24"/>
-      <c r="I412" s="24"/>
-      <c r="J412" s="24"/>
-      <c r="K412" s="24"/>
-      <c r="L412" s="24"/>
-    </row>
-    <row r="413" spans="1:12">
-      <c r="A413" s="28"/>
-      <c r="B413" s="28"/>
-      <c r="C413" s="24"/>
-      <c r="D413" s="24"/>
-      <c r="E413" s="24"/>
-      <c r="F413" s="24"/>
-      <c r="G413" s="24"/>
-      <c r="H413" s="24"/>
-      <c r="I413" s="24"/>
-      <c r="J413" s="24"/>
-      <c r="K413" s="24"/>
-      <c r="L413" s="24"/>
-    </row>
-    <row r="414" spans="1:12">
-      <c r="A414" s="28"/>
-      <c r="B414" s="28"/>
-      <c r="C414" s="24"/>
-      <c r="D414" s="24"/>
-      <c r="E414" s="24"/>
-      <c r="F414" s="24"/>
-      <c r="G414" s="24"/>
-      <c r="H414" s="24"/>
-      <c r="I414" s="24"/>
-      <c r="J414" s="24"/>
-      <c r="K414" s="24"/>
-      <c r="L414" s="24"/>
-    </row>
-    <row r="415" spans="1:12">
-      <c r="A415" s="28"/>
-      <c r="B415" s="28"/>
-      <c r="C415" s="24"/>
-      <c r="D415" s="24"/>
-      <c r="E415" s="24"/>
-      <c r="F415" s="24"/>
-      <c r="G415" s="24"/>
-      <c r="H415" s="24"/>
-      <c r="I415" s="24"/>
-      <c r="J415" s="24"/>
-      <c r="K415" s="24"/>
-      <c r="L415" s="24"/>
-    </row>
-    <row r="416" spans="1:12">
-      <c r="A416" s="28"/>
-      <c r="B416" s="28"/>
-      <c r="C416" s="24"/>
-      <c r="D416" s="24"/>
-      <c r="E416" s="24"/>
-      <c r="F416" s="24"/>
-      <c r="G416" s="24"/>
-      <c r="H416" s="24"/>
-      <c r="I416" s="24"/>
-      <c r="J416" s="24"/>
-      <c r="K416" s="24"/>
-      <c r="L416" s="24"/>
+      <c r="C384" s="14"/>
+      <c r="D384" s="14"/>
+      <c r="E384" s="14"/>
+      <c r="F384" s="14"/>
+      <c r="G384" s="14"/>
+      <c r="H384" s="14"/>
+      <c r="I384" s="14"/>
+      <c r="J384" s="14"/>
+      <c r="K384" s="14"/>
+      <c r="L384" s="14"/>
+    </row>
+    <row r="385" spans="3:12">
+      <c r="C385" s="14"/>
+      <c r="D385" s="14"/>
+      <c r="E385" s="14"/>
+      <c r="F385" s="14"/>
+      <c r="G385" s="14"/>
+      <c r="H385" s="14"/>
+      <c r="I385" s="14"/>
+      <c r="J385" s="14"/>
+      <c r="K385" s="14"/>
+      <c r="L385" s="14"/>
+    </row>
+    <row r="386" spans="3:12">
+      <c r="C386" s="14"/>
+      <c r="D386" s="14"/>
+      <c r="E386" s="14"/>
+      <c r="F386" s="14"/>
+      <c r="G386" s="14"/>
+      <c r="H386" s="14"/>
+      <c r="I386" s="14"/>
+      <c r="J386" s="14"/>
+      <c r="K386" s="14"/>
+      <c r="L386" s="14"/>
+    </row>
+    <row r="387" spans="3:12">
+      <c r="C387" s="14"/>
+      <c r="D387" s="14"/>
+      <c r="E387" s="14"/>
+      <c r="F387" s="14"/>
+      <c r="G387" s="14"/>
+      <c r="H387" s="14"/>
+      <c r="I387" s="14"/>
+      <c r="J387" s="14"/>
+      <c r="K387" s="14"/>
+      <c r="L387" s="14"/>
+    </row>
+    <row r="388" spans="3:12">
+      <c r="C388" s="14"/>
+      <c r="D388" s="14"/>
+      <c r="E388" s="14"/>
+      <c r="F388" s="14"/>
+      <c r="G388" s="14"/>
+      <c r="H388" s="14"/>
+      <c r="I388" s="14"/>
+      <c r="J388" s="14"/>
+      <c r="K388" s="14"/>
+      <c r="L388" s="14"/>
+    </row>
+    <row r="389" spans="3:12">
+      <c r="C389" s="14"/>
+      <c r="D389" s="14"/>
+      <c r="E389" s="14"/>
+      <c r="F389" s="14"/>
+      <c r="G389" s="14"/>
+      <c r="H389" s="14"/>
+      <c r="I389" s="14"/>
+      <c r="J389" s="14"/>
+      <c r="K389" s="14"/>
+      <c r="L389" s="14"/>
+    </row>
+    <row r="390" spans="3:12">
+      <c r="C390" s="14"/>
+      <c r="D390" s="14"/>
+      <c r="E390" s="14"/>
+      <c r="F390" s="14"/>
+      <c r="G390" s="14"/>
+      <c r="H390" s="14"/>
+      <c r="I390" s="14"/>
+      <c r="J390" s="14"/>
+      <c r="K390" s="14"/>
+      <c r="L390" s="14"/>
+    </row>
+    <row r="391" spans="3:12">
+      <c r="C391" s="14"/>
+      <c r="D391" s="14"/>
+      <c r="E391" s="14"/>
+      <c r="F391" s="14"/>
+      <c r="G391" s="14"/>
+      <c r="H391" s="14"/>
+      <c r="I391" s="14"/>
+      <c r="J391" s="14"/>
+      <c r="K391" s="14"/>
+      <c r="L391" s="14"/>
+    </row>
+    <row r="392" spans="3:12">
+      <c r="C392" s="14"/>
+      <c r="D392" s="14"/>
+      <c r="E392" s="14"/>
+      <c r="F392" s="14"/>
+      <c r="G392" s="14"/>
+      <c r="H392" s="14"/>
+      <c r="I392" s="14"/>
+      <c r="J392" s="14"/>
+      <c r="K392" s="14"/>
+      <c r="L392" s="14"/>
+    </row>
+    <row r="393" spans="3:12">
+      <c r="C393" s="14"/>
+      <c r="D393" s="14"/>
+      <c r="E393" s="14"/>
+      <c r="F393" s="14"/>
+      <c r="G393" s="14"/>
+      <c r="H393" s="14"/>
+      <c r="I393" s="14"/>
+      <c r="J393" s="14"/>
+      <c r="K393" s="14"/>
+      <c r="L393" s="14"/>
+    </row>
+    <row r="394" spans="3:12">
+      <c r="C394" s="14"/>
+      <c r="D394" s="14"/>
+      <c r="E394" s="14"/>
+      <c r="F394" s="14"/>
+      <c r="G394" s="14"/>
+      <c r="H394" s="14"/>
+      <c r="I394" s="14"/>
+      <c r="J394" s="14"/>
+      <c r="K394" s="14"/>
+      <c r="L394" s="14"/>
+    </row>
+    <row r="395" spans="3:12">
+      <c r="C395" s="14"/>
+      <c r="D395" s="14"/>
+      <c r="E395" s="14"/>
+      <c r="F395" s="14"/>
+      <c r="G395" s="14"/>
+      <c r="H395" s="14"/>
+      <c r="I395" s="14"/>
+      <c r="J395" s="14"/>
+      <c r="K395" s="14"/>
+      <c r="L395" s="14"/>
+    </row>
+    <row r="396" spans="3:12">
+      <c r="C396" s="14"/>
+      <c r="D396" s="14"/>
+      <c r="E396" s="14"/>
+      <c r="F396" s="14"/>
+      <c r="G396" s="14"/>
+      <c r="H396" s="14"/>
+      <c r="I396" s="14"/>
+      <c r="J396" s="14"/>
+      <c r="K396" s="14"/>
+      <c r="L396" s="14"/>
+    </row>
+    <row r="397" spans="3:12">
+      <c r="C397" s="14"/>
+      <c r="D397" s="14"/>
+      <c r="E397" s="14"/>
+      <c r="F397" s="14"/>
+      <c r="G397" s="14"/>
+      <c r="H397" s="14"/>
+      <c r="I397" s="14"/>
+      <c r="J397" s="14"/>
+      <c r="K397" s="14"/>
+      <c r="L397" s="14"/>
+    </row>
+    <row r="398" spans="3:12">
+      <c r="C398" s="14"/>
+      <c r="D398" s="14"/>
+      <c r="E398" s="14"/>
+      <c r="F398" s="14"/>
+      <c r="G398" s="14"/>
+      <c r="H398" s="14"/>
+      <c r="I398" s="14"/>
+      <c r="J398" s="14"/>
+      <c r="K398" s="14"/>
+      <c r="L398" s="14"/>
+    </row>
+    <row r="399" spans="3:12">
+      <c r="C399" s="14"/>
+      <c r="D399" s="14"/>
+      <c r="E399" s="14"/>
+      <c r="F399" s="14"/>
+      <c r="G399" s="14"/>
+      <c r="H399" s="14"/>
+      <c r="I399" s="14"/>
+      <c r="J399" s="14"/>
+      <c r="K399" s="14"/>
+      <c r="L399" s="14"/>
+    </row>
+    <row r="400" spans="3:12">
+      <c r="C400" s="14"/>
+      <c r="D400" s="14"/>
+      <c r="E400" s="14"/>
+      <c r="F400" s="14"/>
+      <c r="G400" s="14"/>
+      <c r="H400" s="14"/>
+      <c r="I400" s="14"/>
+      <c r="J400" s="14"/>
+      <c r="K400" s="14"/>
+      <c r="L400" s="14"/>
+    </row>
+    <row r="401" spans="3:12">
+      <c r="C401" s="14"/>
+      <c r="D401" s="14"/>
+      <c r="E401" s="14"/>
+      <c r="F401" s="14"/>
+      <c r="G401" s="14"/>
+      <c r="H401" s="14"/>
+      <c r="I401" s="14"/>
+      <c r="J401" s="14"/>
+      <c r="K401" s="14"/>
+      <c r="L401" s="14"/>
+    </row>
+    <row r="402" spans="3:12">
+      <c r="C402" s="14"/>
+      <c r="D402" s="14"/>
+      <c r="E402" s="14"/>
+      <c r="F402" s="14"/>
+      <c r="G402" s="14"/>
+      <c r="H402" s="14"/>
+      <c r="I402" s="14"/>
+      <c r="J402" s="14"/>
+      <c r="K402" s="14"/>
+      <c r="L402" s="14"/>
+    </row>
+    <row r="403" spans="3:12">
+      <c r="C403" s="14"/>
+      <c r="D403" s="14"/>
+      <c r="E403" s="14"/>
+      <c r="F403" s="14"/>
+      <c r="G403" s="14"/>
+      <c r="H403" s="14"/>
+      <c r="I403" s="14"/>
+      <c r="J403" s="14"/>
+      <c r="K403" s="14"/>
+      <c r="L403" s="14"/>
+    </row>
+    <row r="404" spans="3:12">
+      <c r="C404" s="14"/>
+      <c r="D404" s="14"/>
+      <c r="E404" s="14"/>
+      <c r="F404" s="14"/>
+      <c r="G404" s="14"/>
+      <c r="H404" s="14"/>
+      <c r="I404" s="14"/>
+      <c r="J404" s="14"/>
+      <c r="K404" s="14"/>
+      <c r="L404" s="14"/>
+    </row>
+    <row r="405" spans="3:12">
+      <c r="C405" s="14"/>
+      <c r="D405" s="14"/>
+      <c r="E405" s="14"/>
+      <c r="F405" s="14"/>
+      <c r="G405" s="14"/>
+      <c r="H405" s="14"/>
+      <c r="I405" s="14"/>
+      <c r="J405" s="14"/>
+      <c r="K405" s="14"/>
+      <c r="L405" s="14"/>
+    </row>
+    <row r="406" spans="3:12">
+      <c r="C406" s="14"/>
+      <c r="D406" s="14"/>
+      <c r="E406" s="14"/>
+      <c r="F406" s="14"/>
+      <c r="G406" s="14"/>
+      <c r="H406" s="14"/>
+      <c r="I406" s="14"/>
+      <c r="J406" s="14"/>
+      <c r="K406" s="14"/>
+      <c r="L406" s="14"/>
+    </row>
+    <row r="407" spans="3:12">
+      <c r="C407" s="14"/>
+      <c r="D407" s="14"/>
+      <c r="E407" s="14"/>
+      <c r="F407" s="14"/>
+      <c r="G407" s="14"/>
+      <c r="H407" s="14"/>
+      <c r="I407" s="14"/>
+      <c r="J407" s="14"/>
+      <c r="K407" s="14"/>
+      <c r="L407" s="14"/>
+    </row>
+    <row r="408" spans="3:12">
+      <c r="C408" s="14"/>
+      <c r="D408" s="14"/>
+      <c r="E408" s="14"/>
+      <c r="F408" s="14"/>
+      <c r="G408" s="14"/>
+      <c r="H408" s="14"/>
+      <c r="I408" s="14"/>
+      <c r="J408" s="14"/>
+      <c r="K408" s="14"/>
+      <c r="L408" s="14"/>
+    </row>
+    <row r="409" spans="3:12">
+      <c r="C409" s="14"/>
+      <c r="D409" s="14"/>
+      <c r="E409" s="14"/>
+      <c r="F409" s="14"/>
+      <c r="G409" s="14"/>
+      <c r="H409" s="14"/>
+      <c r="I409" s="14"/>
+      <c r="J409" s="14"/>
+      <c r="K409" s="14"/>
+      <c r="L409" s="14"/>
+    </row>
+    <row r="410" spans="3:12">
+      <c r="C410" s="14"/>
+      <c r="D410" s="14"/>
+      <c r="E410" s="14"/>
+      <c r="F410" s="14"/>
+      <c r="G410" s="14"/>
+      <c r="H410" s="14"/>
+      <c r="I410" s="14"/>
+      <c r="J410" s="14"/>
+      <c r="K410" s="14"/>
+      <c r="L410" s="14"/>
+    </row>
+    <row r="411" spans="3:12">
+      <c r="C411" s="14"/>
+      <c r="D411" s="14"/>
+      <c r="E411" s="14"/>
+      <c r="F411" s="14"/>
+      <c r="G411" s="14"/>
+      <c r="H411" s="14"/>
+      <c r="I411" s="14"/>
+      <c r="J411" s="14"/>
+      <c r="K411" s="14"/>
+      <c r="L411" s="14"/>
+    </row>
+    <row r="412" spans="3:12">
+      <c r="C412" s="14"/>
+      <c r="D412" s="14"/>
+      <c r="E412" s="14"/>
+      <c r="F412" s="14"/>
+      <c r="G412" s="14"/>
+      <c r="H412" s="14"/>
+      <c r="I412" s="14"/>
+      <c r="J412" s="14"/>
+      <c r="K412" s="14"/>
+      <c r="L412" s="14"/>
+    </row>
+    <row r="413" spans="3:12">
+      <c r="C413" s="14"/>
+      <c r="D413" s="14"/>
+      <c r="E413" s="14"/>
+      <c r="F413" s="14"/>
+      <c r="G413" s="14"/>
+      <c r="H413" s="14"/>
+      <c r="I413" s="14"/>
+      <c r="J413" s="14"/>
+      <c r="K413" s="14"/>
+      <c r="L413" s="14"/>
+    </row>
+    <row r="414" spans="3:12">
+      <c r="C414" s="14"/>
+      <c r="D414" s="14"/>
+      <c r="E414" s="14"/>
+      <c r="F414" s="14"/>
+      <c r="G414" s="14"/>
+      <c r="H414" s="14"/>
+      <c r="I414" s="14"/>
+      <c r="J414" s="14"/>
+      <c r="K414" s="14"/>
+      <c r="L414" s="14"/>
+    </row>
+    <row r="415" spans="3:12">
+      <c r="C415" s="14"/>
+      <c r="D415" s="14"/>
+      <c r="E415" s="14"/>
+      <c r="F415" s="14"/>
+      <c r="G415" s="14"/>
+      <c r="H415" s="14"/>
+      <c r="I415" s="14"/>
+      <c r="J415" s="14"/>
+      <c r="K415" s="14"/>
+      <c r="L415" s="14"/>
+    </row>
+    <row r="416" spans="3:12">
+      <c r="C416" s="14"/>
+      <c r="D416" s="14"/>
+      <c r="E416" s="14"/>
+      <c r="F416" s="14"/>
+      <c r="G416" s="14"/>
+      <c r="H416" s="14"/>
+      <c r="I416" s="14"/>
+      <c r="J416" s="14"/>
+      <c r="K416" s="14"/>
+      <c r="L416" s="14"/>
     </row>
     <row r="417" spans="1:12">
-      <c r="A417" s="28"/>
-      <c r="B417" s="28"/>
-      <c r="C417" s="24"/>
-      <c r="D417" s="24"/>
-      <c r="E417" s="24"/>
-      <c r="F417" s="24"/>
-      <c r="G417" s="24"/>
-      <c r="H417" s="24"/>
-      <c r="I417" s="24"/>
-      <c r="J417" s="24"/>
-      <c r="K417" s="24"/>
-      <c r="L417" s="24"/>
+      <c r="C417" s="14"/>
+      <c r="D417" s="14"/>
+      <c r="E417" s="14"/>
+      <c r="F417" s="14"/>
+      <c r="G417" s="14"/>
+      <c r="H417" s="14"/>
+      <c r="I417" s="14"/>
+      <c r="J417" s="14"/>
+      <c r="K417" s="14"/>
+      <c r="L417" s="14"/>
     </row>
     <row r="418" spans="1:12">
-      <c r="A418" s="28"/>
-      <c r="B418" s="28"/>
-      <c r="C418" s="24"/>
-      <c r="D418" s="24"/>
-      <c r="E418" s="24"/>
-      <c r="F418" s="24"/>
-      <c r="G418" s="24"/>
-      <c r="H418" s="24"/>
-      <c r="I418" s="24"/>
-      <c r="J418" s="24"/>
-      <c r="K418" s="24"/>
-      <c r="L418" s="24"/>
+      <c r="C418" s="14"/>
+      <c r="D418" s="14"/>
+      <c r="E418" s="14"/>
+      <c r="F418" s="14"/>
+      <c r="G418" s="14"/>
+      <c r="H418" s="14"/>
+      <c r="I418" s="14"/>
+      <c r="J418" s="14"/>
+      <c r="K418" s="14"/>
+      <c r="L418" s="14"/>
     </row>
     <row r="419" spans="1:12">
-      <c r="A419" s="28"/>
-      <c r="B419" s="28"/>
-      <c r="C419" s="24"/>
-      <c r="D419" s="24"/>
-      <c r="E419" s="24"/>
-      <c r="F419" s="24"/>
-      <c r="G419" s="24"/>
-      <c r="H419" s="24"/>
-      <c r="I419" s="24"/>
-      <c r="J419" s="24"/>
-      <c r="K419" s="24"/>
-      <c r="L419" s="24"/>
+      <c r="C419" s="14"/>
+      <c r="D419" s="14"/>
+      <c r="E419" s="14"/>
+      <c r="F419" s="14"/>
+      <c r="G419" s="14"/>
+      <c r="H419" s="14"/>
+      <c r="I419" s="14"/>
+      <c r="J419" s="14"/>
+      <c r="K419" s="14"/>
+      <c r="L419" s="14"/>
     </row>
     <row r="420" spans="1:12">
-      <c r="A420" s="28"/>
-      <c r="B420" s="28"/>
-      <c r="C420" s="24"/>
-      <c r="D420" s="24"/>
-      <c r="E420" s="24"/>
-      <c r="F420" s="24"/>
-      <c r="G420" s="24"/>
-      <c r="H420" s="24"/>
-      <c r="I420" s="24"/>
-      <c r="J420" s="24"/>
-      <c r="K420" s="24"/>
-      <c r="L420" s="24"/>
+      <c r="C420" s="14"/>
+      <c r="D420" s="14"/>
+      <c r="E420" s="14"/>
+      <c r="F420" s="14"/>
+      <c r="G420" s="14"/>
+      <c r="H420" s="14"/>
+      <c r="I420" s="14"/>
+      <c r="J420" s="14"/>
+      <c r="K420" s="14"/>
+      <c r="L420" s="14"/>
     </row>
     <row r="421" spans="1:12">
-      <c r="A421" s="28"/>
-      <c r="B421" s="28"/>
-      <c r="C421" s="24"/>
-      <c r="D421" s="24"/>
-      <c r="E421" s="24"/>
-      <c r="F421" s="24"/>
-      <c r="G421" s="24"/>
-      <c r="H421" s="24"/>
-      <c r="I421" s="24"/>
-      <c r="J421" s="24"/>
-      <c r="K421" s="24"/>
-      <c r="L421" s="24"/>
+      <c r="C421" s="14"/>
+      <c r="D421" s="14"/>
+      <c r="E421" s="14"/>
+      <c r="F421" s="14"/>
+      <c r="G421" s="14"/>
+      <c r="H421" s="14"/>
+      <c r="I421" s="14"/>
+      <c r="J421" s="14"/>
+      <c r="K421" s="14"/>
+      <c r="L421" s="14"/>
     </row>
     <row r="422" spans="1:12">
-      <c r="A422" s="28"/>
-      <c r="B422" s="28"/>
-      <c r="C422" s="24"/>
-      <c r="D422" s="24"/>
-      <c r="E422" s="24"/>
-      <c r="F422" s="24"/>
-      <c r="G422" s="24"/>
-      <c r="H422" s="24"/>
-      <c r="I422" s="24"/>
-      <c r="J422" s="24"/>
-      <c r="K422" s="24"/>
-      <c r="L422" s="24"/>
+      <c r="C422" s="14"/>
+      <c r="D422" s="14"/>
+      <c r="E422" s="14"/>
+      <c r="F422" s="14"/>
+      <c r="G422" s="14"/>
+      <c r="H422" s="14"/>
+      <c r="I422" s="14"/>
+      <c r="J422" s="14"/>
+      <c r="K422" s="14"/>
+      <c r="L422" s="14"/>
     </row>
     <row r="423" spans="1:12">
-      <c r="A423" s="28"/>
-      <c r="B423" s="28"/>
-      <c r="C423" s="24"/>
-      <c r="D423" s="24"/>
-      <c r="E423" s="24"/>
-      <c r="F423" s="24"/>
-      <c r="G423" s="24"/>
-      <c r="H423" s="24"/>
-      <c r="I423" s="24"/>
-      <c r="J423" s="24"/>
-      <c r="K423" s="24"/>
-      <c r="L423" s="24"/>
+      <c r="C423" s="14"/>
+      <c r="D423" s="14"/>
+      <c r="E423" s="14"/>
+      <c r="F423" s="14"/>
+      <c r="G423" s="14"/>
+      <c r="H423" s="14"/>
+      <c r="I423" s="14"/>
+      <c r="J423" s="14"/>
+      <c r="K423" s="14"/>
+      <c r="L423" s="14"/>
     </row>
     <row r="424" spans="1:12">
-      <c r="A424" s="28"/>
-      <c r="B424" s="28"/>
-      <c r="C424" s="24"/>
-      <c r="D424" s="24"/>
-      <c r="E424" s="24"/>
-      <c r="F424" s="24"/>
-      <c r="G424" s="24"/>
-      <c r="H424" s="24"/>
-      <c r="I424" s="24"/>
-      <c r="J424" s="24"/>
-      <c r="K424" s="24"/>
-      <c r="L424" s="24"/>
+      <c r="C424" s="14"/>
+      <c r="D424" s="14"/>
+      <c r="E424" s="14"/>
+      <c r="F424" s="14"/>
+      <c r="G424" s="14"/>
+      <c r="H424" s="14"/>
+      <c r="I424" s="14"/>
+      <c r="J424" s="14"/>
+      <c r="K424" s="14"/>
+      <c r="L424" s="14"/>
     </row>
     <row r="425" spans="1:12">
-      <c r="A425" s="28"/>
-      <c r="B425" s="28"/>
-      <c r="C425" s="24"/>
-      <c r="D425" s="24"/>
-      <c r="E425" s="24"/>
-      <c r="F425" s="24"/>
-      <c r="G425" s="24"/>
-      <c r="H425" s="24"/>
-      <c r="I425" s="24"/>
-      <c r="J425" s="24"/>
-      <c r="K425" s="24"/>
-      <c r="L425" s="24"/>
+      <c r="C425" s="14"/>
+      <c r="D425" s="14"/>
+      <c r="E425" s="14"/>
+      <c r="F425" s="14"/>
+      <c r="G425" s="14"/>
+      <c r="H425" s="14"/>
+      <c r="I425" s="14"/>
+      <c r="J425" s="14"/>
+      <c r="K425" s="14"/>
+      <c r="L425" s="14"/>
     </row>
     <row r="426" spans="1:12">
-      <c r="A426" s="28"/>
-      <c r="B426" s="28"/>
-      <c r="C426" s="24"/>
-      <c r="D426" s="24"/>
-      <c r="E426" s="24"/>
-      <c r="F426" s="24"/>
-      <c r="G426" s="24"/>
-      <c r="H426" s="24"/>
-      <c r="I426" s="24"/>
-      <c r="J426" s="24"/>
-      <c r="K426" s="24"/>
-      <c r="L426" s="24"/>
+      <c r="C426" s="14"/>
+      <c r="D426" s="14"/>
+      <c r="E426" s="14"/>
+      <c r="F426" s="14"/>
+      <c r="G426" s="14"/>
+      <c r="H426" s="14"/>
+      <c r="I426" s="14"/>
+      <c r="J426" s="14"/>
+      <c r="K426" s="14"/>
+      <c r="L426" s="14"/>
     </row>
     <row r="427" spans="1:12">
-      <c r="A427" s="26"/>
-      <c r="B427" s="26"/>
-      <c r="C427" s="27"/>
-      <c r="D427" s="27"/>
-      <c r="E427" s="27"/>
-      <c r="F427" s="27"/>
-      <c r="G427" s="27"/>
-      <c r="H427" s="27"/>
-      <c r="I427" s="27"/>
-      <c r="J427" s="27"/>
-      <c r="K427" s="27"/>
-      <c r="L427" s="27"/>
+      <c r="A427" s="13"/>
+      <c r="B427" s="13"/>
+      <c r="C427" s="7"/>
+      <c r="D427" s="7"/>
+      <c r="E427" s="7"/>
+      <c r="F427" s="7"/>
+      <c r="G427" s="7"/>
+      <c r="H427" s="7"/>
+      <c r="I427" s="7"/>
+      <c r="J427" s="7"/>
+      <c r="K427" s="7"/>
+      <c r="L427" s="7"/>
     </row>
     <row r="428" spans="1:12">
-      <c r="A428" s="28"/>
-      <c r="B428" s="28"/>
-      <c r="C428" s="24"/>
-      <c r="D428" s="24"/>
-      <c r="E428" s="24"/>
-      <c r="F428" s="24"/>
-      <c r="G428" s="24"/>
-      <c r="H428" s="24"/>
-      <c r="I428" s="24"/>
-      <c r="J428" s="24"/>
-      <c r="K428" s="24"/>
-      <c r="L428" s="24"/>
+      <c r="C428" s="14"/>
+      <c r="D428" s="14"/>
+      <c r="E428" s="14"/>
+      <c r="F428" s="14"/>
+      <c r="G428" s="14"/>
+      <c r="H428" s="14"/>
+      <c r="I428" s="14"/>
+      <c r="J428" s="14"/>
+      <c r="K428" s="14"/>
+      <c r="L428" s="14"/>
     </row>
     <row r="429" spans="1:12">
-      <c r="A429" s="28"/>
-      <c r="B429" s="28"/>
-      <c r="C429" s="24"/>
-      <c r="D429" s="24"/>
-      <c r="E429" s="24"/>
-      <c r="F429" s="24"/>
-      <c r="G429" s="24"/>
-      <c r="H429" s="24"/>
-      <c r="I429" s="24"/>
-      <c r="J429" s="24"/>
-      <c r="K429" s="24"/>
-      <c r="L429" s="24"/>
+      <c r="C429" s="14"/>
+      <c r="D429" s="14"/>
+      <c r="E429" s="14"/>
+      <c r="F429" s="14"/>
+      <c r="G429" s="14"/>
+      <c r="H429" s="14"/>
+      <c r="I429" s="14"/>
+      <c r="J429" s="14"/>
+      <c r="K429" s="14"/>
+      <c r="L429" s="14"/>
     </row>
     <row r="430" spans="1:12">
-      <c r="A430" s="28"/>
-      <c r="B430" s="28"/>
-      <c r="C430" s="24"/>
-      <c r="D430" s="24"/>
-      <c r="E430" s="24"/>
-      <c r="F430" s="24"/>
-      <c r="G430" s="24"/>
-      <c r="H430" s="24"/>
-      <c r="I430" s="24"/>
-      <c r="J430" s="24"/>
-      <c r="K430" s="24"/>
-      <c r="L430" s="24"/>
+      <c r="C430" s="14"/>
+      <c r="D430" s="14"/>
+      <c r="E430" s="14"/>
+      <c r="F430" s="14"/>
+      <c r="G430" s="14"/>
+      <c r="H430" s="14"/>
+      <c r="I430" s="14"/>
+      <c r="J430" s="14"/>
+      <c r="K430" s="14"/>
+      <c r="L430" s="14"/>
     </row>
     <row r="431" spans="1:12">
-      <c r="A431" s="28"/>
-      <c r="B431" s="28"/>
-      <c r="C431" s="24"/>
-      <c r="D431" s="24"/>
-      <c r="E431" s="24"/>
-      <c r="F431" s="24"/>
-      <c r="G431" s="24"/>
-      <c r="H431" s="24"/>
-      <c r="I431" s="24"/>
-      <c r="J431" s="24"/>
-      <c r="K431" s="24"/>
-      <c r="L431" s="24"/>
+      <c r="C431" s="14"/>
+      <c r="D431" s="14"/>
+      <c r="E431" s="14"/>
+      <c r="F431" s="14"/>
+      <c r="G431" s="14"/>
+      <c r="H431" s="14"/>
+      <c r="I431" s="14"/>
+      <c r="J431" s="14"/>
+      <c r="K431" s="14"/>
+      <c r="L431" s="14"/>
     </row>
     <row r="432" spans="1:12">
-      <c r="A432" s="28"/>
-      <c r="B432" s="28"/>
-      <c r="C432" s="24"/>
-      <c r="D432" s="24"/>
-      <c r="E432" s="24"/>
-      <c r="F432" s="24"/>
-      <c r="G432" s="24"/>
-      <c r="H432" s="24"/>
-      <c r="I432" s="24"/>
-      <c r="J432" s="24"/>
-      <c r="K432" s="24"/>
-      <c r="L432" s="24"/>
-    </row>
-    <row r="433" spans="1:12">
-      <c r="A433" s="28"/>
-      <c r="B433" s="28"/>
-      <c r="C433" s="24"/>
-      <c r="D433" s="24"/>
-      <c r="E433" s="24"/>
-      <c r="F433" s="24"/>
-      <c r="G433" s="24"/>
-      <c r="H433" s="24"/>
-      <c r="I433" s="24"/>
-      <c r="J433" s="24"/>
-      <c r="K433" s="24"/>
-      <c r="L433" s="24"/>
-    </row>
-    <row r="434" spans="1:12">
-      <c r="A434" s="28"/>
-      <c r="B434" s="28"/>
-      <c r="C434" s="24"/>
-      <c r="D434" s="24"/>
-      <c r="E434" s="24"/>
-      <c r="F434" s="24"/>
-      <c r="G434" s="24"/>
-      <c r="H434" s="24"/>
-      <c r="I434" s="24"/>
-      <c r="J434" s="24"/>
-      <c r="K434" s="24"/>
-      <c r="L434" s="24"/>
-    </row>
-    <row r="435" spans="1:12">
-      <c r="A435" s="28"/>
-      <c r="B435" s="28"/>
-      <c r="C435" s="24"/>
-      <c r="D435" s="24"/>
-      <c r="E435" s="24"/>
-      <c r="F435" s="24"/>
-      <c r="G435" s="24"/>
-      <c r="H435" s="24"/>
-      <c r="I435" s="24"/>
-      <c r="J435" s="24"/>
-      <c r="K435" s="24"/>
-      <c r="L435" s="24"/>
-    </row>
-    <row r="436" spans="1:12">
-      <c r="A436" s="28"/>
-      <c r="B436" s="28"/>
-      <c r="C436" s="24"/>
-      <c r="D436" s="24"/>
-      <c r="E436" s="24"/>
-      <c r="F436" s="24"/>
-      <c r="G436" s="24"/>
-      <c r="H436" s="24"/>
-      <c r="I436" s="24"/>
-      <c r="J436" s="24"/>
-      <c r="K436" s="24"/>
-      <c r="L436" s="24"/>
-    </row>
-    <row r="437" spans="1:12">
-      <c r="A437" s="28"/>
-      <c r="B437" s="28"/>
-      <c r="C437" s="24"/>
-      <c r="D437" s="24"/>
-      <c r="E437" s="24"/>
-      <c r="F437" s="24"/>
-      <c r="G437" s="24"/>
-      <c r="H437" s="24"/>
-      <c r="I437" s="24"/>
-      <c r="J437" s="24"/>
-      <c r="K437" s="24"/>
-      <c r="L437" s="24"/>
-    </row>
-    <row r="438" spans="1:12">
-      <c r="A438" s="28"/>
-      <c r="B438" s="28"/>
-      <c r="C438" s="24"/>
-      <c r="D438" s="24"/>
-      <c r="E438" s="24"/>
-      <c r="F438" s="24"/>
-      <c r="G438" s="24"/>
-      <c r="H438" s="24"/>
-      <c r="I438" s="24"/>
-      <c r="J438" s="24"/>
-      <c r="K438" s="24"/>
-      <c r="L438" s="24"/>
-    </row>
-    <row r="439" spans="1:12">
-      <c r="A439" s="28"/>
-      <c r="B439" s="28"/>
-      <c r="C439" s="24"/>
-      <c r="D439" s="24"/>
-      <c r="E439" s="24"/>
-      <c r="F439" s="24"/>
-      <c r="G439" s="24"/>
-      <c r="H439" s="24"/>
-      <c r="I439" s="24"/>
-      <c r="J439" s="24"/>
-      <c r="K439" s="24"/>
-      <c r="L439" s="24"/>
-    </row>
-    <row r="440" spans="1:12">
-      <c r="A440" s="28"/>
-      <c r="B440" s="28"/>
-      <c r="C440" s="24"/>
-      <c r="D440" s="24"/>
-      <c r="E440" s="24"/>
-      <c r="F440" s="24"/>
-      <c r="G440" s="24"/>
-      <c r="H440" s="24"/>
-      <c r="I440" s="24"/>
-      <c r="J440" s="24"/>
-      <c r="K440" s="24"/>
-      <c r="L440" s="24"/>
-    </row>
-    <row r="441" spans="1:12">
-      <c r="A441" s="28"/>
-      <c r="B441" s="28"/>
-      <c r="C441" s="24"/>
-      <c r="D441" s="24"/>
-      <c r="E441" s="24"/>
-      <c r="F441" s="24"/>
-      <c r="G441" s="24"/>
-      <c r="H441" s="24"/>
-      <c r="I441" s="24"/>
-      <c r="J441" s="24"/>
-      <c r="K441" s="24"/>
-      <c r="L441" s="24"/>
-    </row>
-    <row r="442" spans="1:12">
-      <c r="A442" s="28"/>
-      <c r="B442" s="28"/>
-      <c r="C442" s="24"/>
-      <c r="D442" s="24"/>
-      <c r="E442" s="24"/>
-      <c r="F442" s="24"/>
-      <c r="G442" s="24"/>
-      <c r="H442" s="24"/>
-      <c r="I442" s="24"/>
-      <c r="J442" s="24"/>
-      <c r="K442" s="24"/>
-      <c r="L442" s="24"/>
-    </row>
-    <row r="443" spans="1:12">
-      <c r="A443" s="28"/>
-      <c r="B443" s="28"/>
-      <c r="C443" s="24"/>
-      <c r="D443" s="24"/>
-      <c r="E443" s="24"/>
-      <c r="F443" s="24"/>
-      <c r="G443" s="24"/>
-      <c r="H443" s="24"/>
-      <c r="I443" s="24"/>
-      <c r="J443" s="24"/>
-      <c r="K443" s="24"/>
-      <c r="L443" s="24"/>
-    </row>
-    <row r="444" spans="1:12">
-      <c r="A444" s="28"/>
-      <c r="B444" s="28"/>
-      <c r="C444" s="24"/>
-      <c r="D444" s="24"/>
-      <c r="E444" s="24"/>
-      <c r="F444" s="24"/>
-      <c r="G444" s="24"/>
-      <c r="H444" s="24"/>
-      <c r="I444" s="24"/>
-      <c r="J444" s="24"/>
-      <c r="K444" s="24"/>
-      <c r="L444" s="24"/>
-    </row>
-    <row r="445" spans="1:12">
-      <c r="A445" s="28"/>
-      <c r="B445" s="28"/>
-      <c r="C445" s="24"/>
-      <c r="D445" s="24"/>
-      <c r="E445" s="24"/>
-      <c r="F445" s="24"/>
-      <c r="G445" s="24"/>
-      <c r="H445" s="24"/>
-      <c r="I445" s="24"/>
-      <c r="J445" s="24"/>
-      <c r="K445" s="24"/>
-      <c r="L445" s="24"/>
-    </row>
-    <row r="446" spans="1:12">
-      <c r="A446" s="28"/>
-      <c r="B446" s="28"/>
-      <c r="C446" s="24"/>
-      <c r="D446" s="24"/>
-      <c r="E446" s="24"/>
-      <c r="F446" s="24"/>
-      <c r="G446" s="24"/>
-      <c r="H446" s="24"/>
-      <c r="I446" s="24"/>
-      <c r="J446" s="24"/>
-      <c r="K446" s="24"/>
-      <c r="L446" s="24"/>
-    </row>
-    <row r="447" spans="1:12">
-      <c r="A447" s="28"/>
-      <c r="B447" s="28"/>
-      <c r="C447" s="24"/>
-      <c r="D447" s="24"/>
-      <c r="E447" s="24"/>
-      <c r="F447" s="24"/>
-      <c r="G447" s="24"/>
-      <c r="H447" s="24"/>
-      <c r="I447" s="24"/>
-      <c r="J447" s="24"/>
-      <c r="K447" s="24"/>
-      <c r="L447" s="24"/>
-    </row>
-    <row r="448" spans="1:12">
-      <c r="A448" s="28"/>
-      <c r="B448" s="28"/>
-      <c r="C448" s="24"/>
-      <c r="D448" s="24"/>
-      <c r="E448" s="24"/>
-      <c r="F448" s="24"/>
-      <c r="G448" s="24"/>
-      <c r="H448" s="24"/>
-      <c r="I448" s="24"/>
-      <c r="J448" s="24"/>
-      <c r="K448" s="24"/>
-      <c r="L448" s="24"/>
-    </row>
-    <row r="449" spans="1:12">
-      <c r="A449" s="28"/>
-      <c r="B449" s="28"/>
-      <c r="C449" s="24"/>
-      <c r="D449" s="24"/>
-      <c r="E449" s="24"/>
-      <c r="F449" s="24"/>
-      <c r="G449" s="24"/>
-      <c r="H449" s="24"/>
-      <c r="I449" s="24"/>
-      <c r="J449" s="24"/>
-      <c r="K449" s="24"/>
-      <c r="L449" s="24"/>
-    </row>
-    <row r="450" spans="1:12">
-      <c r="A450" s="28"/>
-      <c r="B450" s="28"/>
-      <c r="C450" s="24"/>
-      <c r="D450" s="24"/>
-      <c r="E450" s="24"/>
-      <c r="F450" s="24"/>
-      <c r="G450" s="24"/>
-      <c r="H450" s="24"/>
-      <c r="I450" s="24"/>
-      <c r="J450" s="24"/>
-      <c r="K450" s="24"/>
-      <c r="L450" s="24"/>
-    </row>
-    <row r="451" spans="1:12">
-      <c r="A451" s="28"/>
-      <c r="B451" s="28"/>
-      <c r="C451" s="24"/>
-      <c r="D451" s="24"/>
-      <c r="E451" s="24"/>
-      <c r="F451" s="24"/>
-      <c r="G451" s="24"/>
-      <c r="H451" s="24"/>
-      <c r="I451" s="24"/>
-      <c r="J451" s="24"/>
-      <c r="K451" s="24"/>
-      <c r="L451" s="24"/>
-    </row>
-    <row r="452" spans="1:12">
-      <c r="A452" s="28"/>
-      <c r="B452" s="28"/>
-      <c r="C452" s="24"/>
-      <c r="D452" s="24"/>
-      <c r="E452" s="24"/>
-      <c r="F452" s="24"/>
-      <c r="G452" s="24"/>
-      <c r="H452" s="24"/>
-      <c r="I452" s="24"/>
-      <c r="J452" s="24"/>
-      <c r="K452" s="24"/>
-      <c r="L452" s="24"/>
-    </row>
-    <row r="453" spans="1:12">
-      <c r="A453" s="28"/>
-      <c r="B453" s="28"/>
-      <c r="C453" s="24"/>
-      <c r="D453" s="24"/>
-      <c r="E453" s="24"/>
-      <c r="F453" s="24"/>
-      <c r="G453" s="24"/>
-      <c r="H453" s="24"/>
-      <c r="I453" s="24"/>
-      <c r="J453" s="24"/>
-      <c r="K453" s="24"/>
-      <c r="L453" s="24"/>
-    </row>
-    <row r="454" spans="1:12">
-      <c r="A454" s="28"/>
-      <c r="B454" s="28"/>
-      <c r="C454" s="24"/>
-      <c r="D454" s="24"/>
-      <c r="E454" s="24"/>
-      <c r="F454" s="24"/>
-      <c r="G454" s="24"/>
-      <c r="H454" s="24"/>
-      <c r="I454" s="24"/>
-      <c r="J454" s="24"/>
-      <c r="K454" s="24"/>
-      <c r="L454" s="24"/>
-    </row>
-    <row r="455" spans="1:12">
-      <c r="A455" s="28"/>
-      <c r="B455" s="28"/>
-      <c r="C455" s="24"/>
-      <c r="D455" s="24"/>
-      <c r="E455" s="24"/>
-      <c r="F455" s="24"/>
-      <c r="G455" s="24"/>
-      <c r="H455" s="24"/>
-      <c r="I455" s="24"/>
-      <c r="J455" s="24"/>
-      <c r="K455" s="24"/>
-      <c r="L455" s="24"/>
-    </row>
-    <row r="456" spans="1:12">
-      <c r="A456" s="28"/>
-      <c r="B456" s="28"/>
-      <c r="C456" s="24"/>
-      <c r="D456" s="24"/>
-      <c r="E456" s="24"/>
-      <c r="F456" s="24"/>
-      <c r="G456" s="24"/>
-      <c r="H456" s="24"/>
-      <c r="I456" s="24"/>
-      <c r="J456" s="24"/>
-      <c r="K456" s="24"/>
-      <c r="L456" s="24"/>
-    </row>
-    <row r="457" spans="1:12">
-      <c r="A457" s="28"/>
-      <c r="B457" s="28"/>
-      <c r="C457" s="24"/>
-      <c r="D457" s="24"/>
-      <c r="E457" s="24"/>
-      <c r="F457" s="24"/>
-      <c r="G457" s="24"/>
-      <c r="H457" s="24"/>
-      <c r="I457" s="24"/>
-      <c r="J457" s="24"/>
-      <c r="K457" s="24"/>
-      <c r="L457" s="24"/>
-    </row>
-    <row r="458" spans="1:12">
-      <c r="A458" s="28"/>
-      <c r="B458" s="28"/>
-      <c r="C458" s="24"/>
-      <c r="D458" s="24"/>
-      <c r="E458" s="24"/>
-      <c r="F458" s="24"/>
-      <c r="G458" s="24"/>
-      <c r="H458" s="24"/>
-      <c r="I458" s="24"/>
-      <c r="J458" s="24"/>
-      <c r="K458" s="24"/>
-      <c r="L458" s="24"/>
-    </row>
-    <row r="459" spans="1:12">
-      <c r="A459" s="28"/>
-      <c r="B459" s="28"/>
-      <c r="C459" s="24"/>
-      <c r="D459" s="24"/>
-      <c r="E459" s="24"/>
-      <c r="F459" s="24"/>
-      <c r="G459" s="24"/>
-      <c r="H459" s="24"/>
-      <c r="I459" s="24"/>
-      <c r="J459" s="24"/>
-      <c r="K459" s="24"/>
-      <c r="L459" s="24"/>
-    </row>
-    <row r="460" spans="1:12">
-      <c r="A460" s="28"/>
-      <c r="B460" s="28"/>
-      <c r="C460" s="24"/>
-      <c r="D460" s="24"/>
-      <c r="E460" s="24"/>
-      <c r="F460" s="24"/>
-      <c r="G460" s="24"/>
-      <c r="H460" s="24"/>
-      <c r="I460" s="24"/>
-      <c r="J460" s="24"/>
-      <c r="K460" s="24"/>
-      <c r="L460" s="24"/>
-    </row>
-    <row r="461" spans="1:12">
-      <c r="A461" s="28"/>
-      <c r="B461" s="28"/>
-      <c r="C461" s="24"/>
-      <c r="D461" s="24"/>
-      <c r="E461" s="24"/>
-      <c r="F461" s="24"/>
-      <c r="G461" s="24"/>
-      <c r="H461" s="24"/>
-      <c r="I461" s="24"/>
-      <c r="J461" s="24"/>
-      <c r="K461" s="24"/>
-      <c r="L461" s="24"/>
-    </row>
-    <row r="462" spans="1:12">
-      <c r="A462" s="28"/>
-      <c r="B462" s="28"/>
-      <c r="C462" s="24"/>
-      <c r="D462" s="24"/>
-      <c r="E462" s="24"/>
-      <c r="F462" s="24"/>
-      <c r="G462" s="24"/>
-      <c r="H462" s="24"/>
-      <c r="I462" s="24"/>
-      <c r="J462" s="24"/>
-      <c r="K462" s="24"/>
-      <c r="L462" s="24"/>
-    </row>
-    <row r="463" spans="1:12">
-      <c r="A463" s="28"/>
-      <c r="B463" s="28"/>
-      <c r="C463" s="24"/>
-      <c r="D463" s="24"/>
-      <c r="E463" s="24"/>
-      <c r="F463" s="24"/>
-      <c r="G463" s="24"/>
-      <c r="H463" s="24"/>
-      <c r="I463" s="24"/>
-      <c r="J463" s="24"/>
-      <c r="K463" s="24"/>
-      <c r="L463" s="24"/>
-    </row>
-    <row r="464" spans="1:12">
-      <c r="A464" s="28"/>
-      <c r="B464" s="28"/>
-      <c r="C464" s="24"/>
-      <c r="D464" s="24"/>
-      <c r="E464" s="24"/>
-      <c r="F464" s="24"/>
-      <c r="G464" s="24"/>
-      <c r="H464" s="24"/>
-      <c r="I464" s="24"/>
-      <c r="J464" s="24"/>
-      <c r="K464" s="24"/>
-      <c r="L464" s="24"/>
-    </row>
-    <row r="465" spans="1:12">
-      <c r="A465" s="28"/>
-      <c r="B465" s="28"/>
-      <c r="C465" s="24"/>
-      <c r="D465" s="24"/>
-      <c r="E465" s="24"/>
-      <c r="F465" s="24"/>
-      <c r="G465" s="24"/>
-      <c r="H465" s="24"/>
-      <c r="I465" s="24"/>
-      <c r="J465" s="24"/>
-      <c r="K465" s="24"/>
-      <c r="L465" s="24"/>
-    </row>
-    <row r="466" spans="1:12">
-      <c r="A466" s="28"/>
-      <c r="B466" s="28"/>
-      <c r="C466" s="24"/>
-      <c r="D466" s="24"/>
-      <c r="E466" s="24"/>
-      <c r="F466" s="24"/>
-      <c r="G466" s="24"/>
-      <c r="H466" s="24"/>
-      <c r="I466" s="24"/>
-      <c r="J466" s="24"/>
-      <c r="K466" s="24"/>
-      <c r="L466" s="24"/>
-    </row>
-    <row r="467" spans="1:12">
-      <c r="A467" s="28"/>
-      <c r="B467" s="28"/>
-      <c r="C467" s="24"/>
-      <c r="D467" s="24"/>
-      <c r="E467" s="24"/>
-      <c r="F467" s="24"/>
-      <c r="G467" s="24"/>
-      <c r="H467" s="24"/>
-      <c r="I467" s="24"/>
-      <c r="J467" s="24"/>
-      <c r="K467" s="24"/>
-      <c r="L467" s="24"/>
-    </row>
-    <row r="468" spans="1:12">
-      <c r="A468" s="28"/>
-      <c r="B468" s="28"/>
-      <c r="C468" s="24"/>
-      <c r="D468" s="24"/>
-      <c r="E468" s="24"/>
-      <c r="F468" s="24"/>
-      <c r="G468" s="24"/>
-      <c r="H468" s="24"/>
-      <c r="I468" s="24"/>
-      <c r="J468" s="24"/>
-      <c r="K468" s="24"/>
-      <c r="L468" s="24"/>
-    </row>
-    <row r="469" spans="1:12">
-      <c r="A469" s="28"/>
-      <c r="B469" s="28"/>
-      <c r="C469" s="24"/>
-      <c r="D469" s="24"/>
-      <c r="E469" s="24"/>
-      <c r="F469" s="24"/>
-      <c r="G469" s="24"/>
-      <c r="H469" s="24"/>
-      <c r="I469" s="24"/>
-      <c r="J469" s="24"/>
-      <c r="K469" s="24"/>
-      <c r="L469" s="24"/>
-    </row>
-    <row r="470" spans="1:12">
-      <c r="A470" s="28"/>
-      <c r="B470" s="28"/>
-      <c r="C470" s="24"/>
-      <c r="D470" s="24"/>
-      <c r="E470" s="24"/>
-      <c r="F470" s="24"/>
-      <c r="G470" s="24"/>
-      <c r="H470" s="24"/>
-      <c r="I470" s="24"/>
-      <c r="J470" s="24"/>
-      <c r="K470" s="24"/>
-      <c r="L470" s="24"/>
-    </row>
-    <row r="471" spans="1:12">
-      <c r="A471" s="28"/>
-      <c r="B471" s="28"/>
-      <c r="C471" s="24"/>
-      <c r="D471" s="24"/>
-      <c r="E471" s="24"/>
-      <c r="F471" s="24"/>
-      <c r="G471" s="24"/>
-      <c r="H471" s="24"/>
-      <c r="I471" s="24"/>
-      <c r="J471" s="24"/>
-      <c r="K471" s="24"/>
-      <c r="L471" s="24"/>
-    </row>
-    <row r="472" spans="1:12">
-      <c r="A472" s="28"/>
-      <c r="B472" s="28"/>
-      <c r="C472" s="24"/>
-      <c r="D472" s="24"/>
-      <c r="E472" s="24"/>
-      <c r="F472" s="24"/>
-      <c r="G472" s="24"/>
-      <c r="H472" s="24"/>
-      <c r="I472" s="24"/>
-      <c r="J472" s="24"/>
-      <c r="K472" s="24"/>
-      <c r="L472" s="24"/>
-    </row>
-    <row r="473" spans="1:12">
-      <c r="A473" s="28"/>
-      <c r="B473" s="28"/>
-      <c r="C473" s="24"/>
-      <c r="D473" s="24"/>
-      <c r="E473" s="24"/>
-      <c r="F473" s="24"/>
-      <c r="G473" s="24"/>
-      <c r="H473" s="24"/>
-      <c r="I473" s="24"/>
-      <c r="J473" s="24"/>
-      <c r="K473" s="24"/>
-      <c r="L473" s="24"/>
-    </row>
-    <row r="474" spans="1:12">
-      <c r="A474" s="28"/>
-      <c r="B474" s="28"/>
-      <c r="C474" s="24"/>
-      <c r="D474" s="24"/>
-      <c r="E474" s="24"/>
-      <c r="F474" s="24"/>
-      <c r="G474" s="24"/>
-      <c r="H474" s="24"/>
-      <c r="I474" s="24"/>
-      <c r="J474" s="24"/>
-      <c r="K474" s="24"/>
-      <c r="L474" s="24"/>
-    </row>
-    <row r="475" spans="1:12">
-      <c r="A475" s="28"/>
-      <c r="B475" s="28"/>
-      <c r="C475" s="24"/>
-      <c r="D475" s="24"/>
-      <c r="E475" s="24"/>
-      <c r="F475" s="24"/>
-      <c r="G475" s="24"/>
-      <c r="H475" s="24"/>
-      <c r="I475" s="24"/>
-      <c r="J475" s="24"/>
-      <c r="K475" s="24"/>
-      <c r="L475" s="24"/>
-    </row>
-    <row r="476" spans="1:12">
-      <c r="A476" s="28"/>
-      <c r="B476" s="28"/>
-      <c r="C476" s="24"/>
-      <c r="D476" s="24"/>
-      <c r="E476" s="24"/>
-      <c r="F476" s="24"/>
-      <c r="G476" s="24"/>
-      <c r="H476" s="24"/>
-      <c r="I476" s="24"/>
-      <c r="J476" s="24"/>
-      <c r="K476" s="24"/>
-      <c r="L476" s="24"/>
-    </row>
-    <row r="477" spans="1:12">
-      <c r="A477" s="28"/>
-      <c r="B477" s="28"/>
-      <c r="C477" s="24"/>
-      <c r="D477" s="24"/>
-      <c r="E477" s="24"/>
-      <c r="F477" s="24"/>
-      <c r="G477" s="24"/>
-      <c r="H477" s="24"/>
-      <c r="I477" s="24"/>
-      <c r="J477" s="24"/>
-      <c r="K477" s="24"/>
-      <c r="L477" s="24"/>
-    </row>
-    <row r="478" spans="1:12">
-      <c r="A478" s="28"/>
-      <c r="B478" s="28"/>
-      <c r="C478" s="24"/>
-      <c r="D478" s="24"/>
-      <c r="E478" s="24"/>
-      <c r="F478" s="24"/>
-      <c r="G478" s="24"/>
-      <c r="H478" s="24"/>
-      <c r="I478" s="24"/>
-      <c r="J478" s="24"/>
-      <c r="K478" s="24"/>
-      <c r="L478" s="24"/>
-    </row>
-    <row r="479" spans="1:12">
-      <c r="A479" s="28"/>
-      <c r="B479" s="28"/>
-      <c r="C479" s="24"/>
-      <c r="D479" s="24"/>
-      <c r="E479" s="24"/>
-      <c r="F479" s="24"/>
-      <c r="G479" s="24"/>
-      <c r="H479" s="24"/>
-      <c r="I479" s="24"/>
-      <c r="J479" s="24"/>
-      <c r="K479" s="24"/>
-      <c r="L479" s="24"/>
-    </row>
-    <row r="480" spans="1:12">
-      <c r="A480" s="28"/>
-      <c r="B480" s="28"/>
-      <c r="C480" s="24"/>
-      <c r="D480" s="24"/>
-      <c r="E480" s="24"/>
-      <c r="F480" s="24"/>
-      <c r="G480" s="24"/>
-      <c r="H480" s="24"/>
-      <c r="I480" s="24"/>
-      <c r="J480" s="24"/>
-      <c r="K480" s="24"/>
-      <c r="L480" s="24"/>
-    </row>
-    <row r="481" spans="1:12">
-      <c r="A481" s="28"/>
-      <c r="B481" s="28"/>
-      <c r="C481" s="24"/>
-      <c r="D481" s="24"/>
-      <c r="E481" s="24"/>
-      <c r="F481" s="24"/>
-      <c r="G481" s="24"/>
-      <c r="H481" s="24"/>
-      <c r="I481" s="24"/>
-      <c r="J481" s="24"/>
-      <c r="K481" s="24"/>
-      <c r="L481" s="24"/>
-    </row>
-    <row r="482" spans="1:12">
-      <c r="A482" s="28"/>
-      <c r="B482" s="28"/>
-      <c r="C482" s="24"/>
-      <c r="D482" s="24"/>
-      <c r="E482" s="24"/>
-      <c r="F482" s="24"/>
-      <c r="G482" s="24"/>
-      <c r="H482" s="24"/>
-      <c r="I482" s="24"/>
-      <c r="J482" s="24"/>
-      <c r="K482" s="24"/>
-      <c r="L482" s="24"/>
+      <c r="C432" s="14"/>
+      <c r="D432" s="14"/>
+      <c r="E432" s="14"/>
+      <c r="F432" s="14"/>
+      <c r="G432" s="14"/>
+      <c r="H432" s="14"/>
+      <c r="I432" s="14"/>
+      <c r="J432" s="14"/>
+      <c r="K432" s="14"/>
+      <c r="L432" s="14"/>
+    </row>
+    <row r="433" spans="3:12">
+      <c r="C433" s="14"/>
+      <c r="D433" s="14"/>
+      <c r="E433" s="14"/>
+      <c r="F433" s="14"/>
+      <c r="G433" s="14"/>
+      <c r="H433" s="14"/>
+      <c r="I433" s="14"/>
+      <c r="J433" s="14"/>
+      <c r="K433" s="14"/>
+      <c r="L433" s="14"/>
+    </row>
+    <row r="434" spans="3:12">
+      <c r="C434" s="14"/>
+      <c r="D434" s="14"/>
+      <c r="E434" s="14"/>
+      <c r="F434" s="14"/>
+      <c r="G434" s="14"/>
+      <c r="H434" s="14"/>
+      <c r="I434" s="14"/>
+      <c r="J434" s="14"/>
+      <c r="K434" s="14"/>
+      <c r="L434" s="14"/>
+    </row>
+    <row r="435" spans="3:12">
+      <c r="C435" s="14"/>
+      <c r="D435" s="14"/>
+      <c r="E435" s="14"/>
+      <c r="F435" s="14"/>
+      <c r="G435" s="14"/>
+      <c r="H435" s="14"/>
+      <c r="I435" s="14"/>
+      <c r="J435" s="14"/>
+      <c r="K435" s="14"/>
+      <c r="L435" s="14"/>
+    </row>
+    <row r="436" spans="3:12">
+      <c r="C436" s="14"/>
+      <c r="D436" s="14"/>
+      <c r="E436" s="14"/>
+      <c r="F436" s="14"/>
+      <c r="G436" s="14"/>
+      <c r="H436" s="14"/>
+      <c r="I436" s="14"/>
+      <c r="J436" s="14"/>
+      <c r="K436" s="14"/>
+      <c r="L436" s="14"/>
+    </row>
+    <row r="437" spans="3:12">
+      <c r="C437" s="14"/>
+      <c r="D437" s="14"/>
+      <c r="E437" s="14"/>
+      <c r="F437" s="14"/>
+      <c r="G437" s="14"/>
+      <c r="H437" s="14"/>
+      <c r="I437" s="14"/>
+      <c r="J437" s="14"/>
+      <c r="K437" s="14"/>
+      <c r="L437" s="14"/>
+    </row>
+    <row r="438" spans="3:12">
+      <c r="C438" s="14"/>
+      <c r="D438" s="14"/>
+      <c r="E438" s="14"/>
+      <c r="F438" s="14"/>
+      <c r="G438" s="14"/>
+      <c r="H438" s="14"/>
+      <c r="I438" s="14"/>
+      <c r="J438" s="14"/>
+      <c r="K438" s="14"/>
+      <c r="L438" s="14"/>
+    </row>
+    <row r="439" spans="3:12">
+      <c r="C439" s="14"/>
+      <c r="D439" s="14"/>
+      <c r="E439" s="14"/>
+      <c r="F439" s="14"/>
+      <c r="G439" s="14"/>
+      <c r="H439" s="14"/>
+      <c r="I439" s="14"/>
+      <c r="J439" s="14"/>
+      <c r="K439" s="14"/>
+      <c r="L439" s="14"/>
+    </row>
+    <row r="440" spans="3:12">
+      <c r="C440" s="14"/>
+      <c r="D440" s="14"/>
+      <c r="E440" s="14"/>
+      <c r="F440" s="14"/>
+      <c r="G440" s="14"/>
+      <c r="H440" s="14"/>
+      <c r="I440" s="14"/>
+      <c r="J440" s="14"/>
+      <c r="K440" s="14"/>
+      <c r="L440" s="14"/>
+    </row>
+    <row r="441" spans="3:12">
+      <c r="C441" s="14"/>
+      <c r="D441" s="14"/>
+      <c r="E441" s="14"/>
+      <c r="F441" s="14"/>
+      <c r="G441" s="14"/>
+      <c r="H441" s="14"/>
+      <c r="I441" s="14"/>
+      <c r="J441" s="14"/>
+      <c r="K441" s="14"/>
+      <c r="L441" s="14"/>
+    </row>
+    <row r="442" spans="3:12">
+      <c r="C442" s="14"/>
+      <c r="D442" s="14"/>
+      <c r="E442" s="14"/>
+      <c r="F442" s="14"/>
+      <c r="G442" s="14"/>
+      <c r="H442" s="14"/>
+      <c r="I442" s="14"/>
+      <c r="J442" s="14"/>
+      <c r="K442" s="14"/>
+      <c r="L442" s="14"/>
+    </row>
+    <row r="443" spans="3:12">
+      <c r="C443" s="14"/>
+      <c r="D443" s="14"/>
+      <c r="E443" s="14"/>
+      <c r="F443" s="14"/>
+      <c r="G443" s="14"/>
+      <c r="H443" s="14"/>
+      <c r="I443" s="14"/>
+      <c r="J443" s="14"/>
+      <c r="K443" s="14"/>
+      <c r="L443" s="14"/>
+    </row>
+    <row r="444" spans="3:12">
+      <c r="C444" s="14"/>
+      <c r="D444" s="14"/>
+      <c r="E444" s="14"/>
+      <c r="F444" s="14"/>
+      <c r="G444" s="14"/>
+      <c r="H444" s="14"/>
+      <c r="I444" s="14"/>
+      <c r="J444" s="14"/>
+      <c r="K444" s="14"/>
+      <c r="L444" s="14"/>
+    </row>
+    <row r="445" spans="3:12">
+      <c r="C445" s="14"/>
+      <c r="D445" s="14"/>
+      <c r="E445" s="14"/>
+      <c r="F445" s="14"/>
+      <c r="G445" s="14"/>
+      <c r="H445" s="14"/>
+      <c r="I445" s="14"/>
+      <c r="J445" s="14"/>
+      <c r="K445" s="14"/>
+      <c r="L445" s="14"/>
+    </row>
+    <row r="446" spans="3:12">
+      <c r="C446" s="14"/>
+      <c r="D446" s="14"/>
+      <c r="E446" s="14"/>
+      <c r="F446" s="14"/>
+      <c r="G446" s="14"/>
+      <c r="H446" s="14"/>
+      <c r="I446" s="14"/>
+      <c r="J446" s="14"/>
+      <c r="K446" s="14"/>
+      <c r="L446" s="14"/>
+    </row>
+    <row r="447" spans="3:12">
+      <c r="C447" s="14"/>
+      <c r="D447" s="14"/>
+      <c r="E447" s="14"/>
+      <c r="F447" s="14"/>
+      <c r="G447" s="14"/>
+      <c r="H447" s="14"/>
+      <c r="I447" s="14"/>
+      <c r="J447" s="14"/>
+      <c r="K447" s="14"/>
+      <c r="L447" s="14"/>
+    </row>
+    <row r="448" spans="3:12">
+      <c r="C448" s="14"/>
+      <c r="D448" s="14"/>
+      <c r="E448" s="14"/>
+      <c r="F448" s="14"/>
+      <c r="G448" s="14"/>
+      <c r="H448" s="14"/>
+      <c r="I448" s="14"/>
+      <c r="J448" s="14"/>
+      <c r="K448" s="14"/>
+      <c r="L448" s="14"/>
+    </row>
+    <row r="449" spans="3:12">
+      <c r="C449" s="14"/>
+      <c r="D449" s="14"/>
+      <c r="E449" s="14"/>
+      <c r="F449" s="14"/>
+      <c r="G449" s="14"/>
+      <c r="H449" s="14"/>
+      <c r="I449" s="14"/>
+      <c r="J449" s="14"/>
+      <c r="K449" s="14"/>
+      <c r="L449" s="14"/>
+    </row>
+    <row r="450" spans="3:12">
+      <c r="C450" s="14"/>
+      <c r="D450" s="14"/>
+      <c r="E450" s="14"/>
+      <c r="F450" s="14"/>
+      <c r="G450" s="14"/>
+      <c r="H450" s="14"/>
+      <c r="I450" s="14"/>
+      <c r="J450" s="14"/>
+      <c r="K450" s="14"/>
+      <c r="L450" s="14"/>
+    </row>
+    <row r="451" spans="3:12">
+      <c r="C451" s="14"/>
+      <c r="D451" s="14"/>
+      <c r="E451" s="14"/>
+      <c r="F451" s="14"/>
+      <c r="G451" s="14"/>
+      <c r="H451" s="14"/>
+      <c r="I451" s="14"/>
+      <c r="J451" s="14"/>
+      <c r="K451" s="14"/>
+      <c r="L451" s="14"/>
+    </row>
+    <row r="452" spans="3:12">
+      <c r="C452" s="14"/>
+      <c r="D452" s="14"/>
+      <c r="E452" s="14"/>
+      <c r="F452" s="14"/>
+      <c r="G452" s="14"/>
+      <c r="H452" s="14"/>
+      <c r="I452" s="14"/>
+      <c r="J452" s="14"/>
+      <c r="K452" s="14"/>
+      <c r="L452" s="14"/>
+    </row>
+    <row r="453" spans="3:12">
+      <c r="C453" s="14"/>
+      <c r="D453" s="14"/>
+      <c r="E453" s="14"/>
+      <c r="F453" s="14"/>
+      <c r="G453" s="14"/>
+      <c r="H453" s="14"/>
+      <c r="I453" s="14"/>
+      <c r="J453" s="14"/>
+      <c r="K453" s="14"/>
+      <c r="L453" s="14"/>
+    </row>
+    <row r="454" spans="3:12">
+      <c r="C454" s="14"/>
+      <c r="D454" s="14"/>
+      <c r="E454" s="14"/>
+      <c r="F454" s="14"/>
+      <c r="G454" s="14"/>
+      <c r="H454" s="14"/>
+      <c r="I454" s="14"/>
+      <c r="J454" s="14"/>
+      <c r="K454" s="14"/>
+      <c r="L454" s="14"/>
+    </row>
+    <row r="455" spans="3:12">
+      <c r="C455" s="14"/>
+      <c r="D455" s="14"/>
+      <c r="E455" s="14"/>
+      <c r="F455" s="14"/>
+      <c r="G455" s="14"/>
+      <c r="H455" s="14"/>
+      <c r="I455" s="14"/>
+      <c r="J455" s="14"/>
+      <c r="K455" s="14"/>
+      <c r="L455" s="14"/>
+    </row>
+    <row r="456" spans="3:12">
+      <c r="C456" s="14"/>
+      <c r="D456" s="14"/>
+      <c r="E456" s="14"/>
+      <c r="F456" s="14"/>
+      <c r="G456" s="14"/>
+      <c r="H456" s="14"/>
+      <c r="I456" s="14"/>
+      <c r="J456" s="14"/>
+      <c r="K456" s="14"/>
+      <c r="L456" s="14"/>
+    </row>
+    <row r="457" spans="3:12">
+      <c r="C457" s="14"/>
+      <c r="D457" s="14"/>
+      <c r="E457" s="14"/>
+      <c r="F457" s="14"/>
+      <c r="G457" s="14"/>
+      <c r="H457" s="14"/>
+      <c r="I457" s="14"/>
+      <c r="J457" s="14"/>
+      <c r="K457" s="14"/>
+      <c r="L457" s="14"/>
+    </row>
+    <row r="458" spans="3:12">
+      <c r="C458" s="14"/>
+      <c r="D458" s="14"/>
+      <c r="E458" s="14"/>
+      <c r="F458" s="14"/>
+      <c r="G458" s="14"/>
+      <c r="H458" s="14"/>
+      <c r="I458" s="14"/>
+      <c r="J458" s="14"/>
+      <c r="K458" s="14"/>
+      <c r="L458" s="14"/>
+    </row>
+    <row r="459" spans="3:12">
+      <c r="C459" s="14"/>
+      <c r="D459" s="14"/>
+      <c r="E459" s="14"/>
+      <c r="F459" s="14"/>
+      <c r="G459" s="14"/>
+      <c r="H459" s="14"/>
+      <c r="I459" s="14"/>
+      <c r="J459" s="14"/>
+      <c r="K459" s="14"/>
+      <c r="L459" s="14"/>
+    </row>
+    <row r="460" spans="3:12">
+      <c r="C460" s="14"/>
+      <c r="D460" s="14"/>
+      <c r="E460" s="14"/>
+      <c r="F460" s="14"/>
+      <c r="G460" s="14"/>
+      <c r="H460" s="14"/>
+      <c r="I460" s="14"/>
+      <c r="J460" s="14"/>
+      <c r="K460" s="14"/>
+      <c r="L460" s="14"/>
+    </row>
+    <row r="461" spans="3:12">
+      <c r="C461" s="14"/>
+      <c r="D461" s="14"/>
+      <c r="E461" s="14"/>
+      <c r="F461" s="14"/>
+      <c r="G461" s="14"/>
+      <c r="H461" s="14"/>
+      <c r="I461" s="14"/>
+      <c r="J461" s="14"/>
+      <c r="K461" s="14"/>
+      <c r="L461" s="14"/>
+    </row>
+    <row r="462" spans="3:12">
+      <c r="C462" s="14"/>
+      <c r="D462" s="14"/>
+      <c r="E462" s="14"/>
+      <c r="F462" s="14"/>
+      <c r="G462" s="14"/>
+      <c r="H462" s="14"/>
+      <c r="I462" s="14"/>
+      <c r="J462" s="14"/>
+      <c r="K462" s="14"/>
+      <c r="L462" s="14"/>
+    </row>
+    <row r="463" spans="3:12">
+      <c r="C463" s="14"/>
+      <c r="D463" s="14"/>
+      <c r="E463" s="14"/>
+      <c r="F463" s="14"/>
+      <c r="G463" s="14"/>
+      <c r="H463" s="14"/>
+      <c r="I463" s="14"/>
+      <c r="J463" s="14"/>
+      <c r="K463" s="14"/>
+      <c r="L463" s="14"/>
+    </row>
+    <row r="464" spans="3:12">
+      <c r="C464" s="14"/>
+      <c r="D464" s="14"/>
+      <c r="E464" s="14"/>
+      <c r="F464" s="14"/>
+      <c r="G464" s="14"/>
+      <c r="H464" s="14"/>
+      <c r="I464" s="14"/>
+      <c r="J464" s="14"/>
+      <c r="K464" s="14"/>
+      <c r="L464" s="14"/>
+    </row>
+    <row r="465" spans="3:12">
+      <c r="C465" s="14"/>
+      <c r="D465" s="14"/>
+      <c r="E465" s="14"/>
+      <c r="F465" s="14"/>
+      <c r="G465" s="14"/>
+      <c r="H465" s="14"/>
+      <c r="I465" s="14"/>
+      <c r="J465" s="14"/>
+      <c r="K465" s="14"/>
+      <c r="L465" s="14"/>
+    </row>
+    <row r="466" spans="3:12">
+      <c r="C466" s="14"/>
+      <c r="D466" s="14"/>
+      <c r="E466" s="14"/>
+      <c r="F466" s="14"/>
+      <c r="G466" s="14"/>
+      <c r="H466" s="14"/>
+      <c r="I466" s="14"/>
+      <c r="J466" s="14"/>
+      <c r="K466" s="14"/>
+      <c r="L466" s="14"/>
+    </row>
+    <row r="467" spans="3:12">
+      <c r="C467" s="14"/>
+      <c r="D467" s="14"/>
+      <c r="E467" s="14"/>
+      <c r="F467" s="14"/>
+      <c r="G467" s="14"/>
+      <c r="H467" s="14"/>
+      <c r="I467" s="14"/>
+      <c r="J467" s="14"/>
+      <c r="K467" s="14"/>
+      <c r="L467" s="14"/>
+    </row>
+    <row r="468" spans="3:12">
+      <c r="C468" s="14"/>
+      <c r="D468" s="14"/>
+      <c r="E468" s="14"/>
+      <c r="F468" s="14"/>
+      <c r="G468" s="14"/>
+      <c r="H468" s="14"/>
+      <c r="I468" s="14"/>
+      <c r="J468" s="14"/>
+      <c r="K468" s="14"/>
+      <c r="L468" s="14"/>
+    </row>
+    <row r="469" spans="3:12">
+      <c r="C469" s="14"/>
+      <c r="D469" s="14"/>
+      <c r="E469" s="14"/>
+      <c r="F469" s="14"/>
+      <c r="G469" s="14"/>
+      <c r="H469" s="14"/>
+      <c r="I469" s="14"/>
+      <c r="J469" s="14"/>
+      <c r="K469" s="14"/>
+      <c r="L469" s="14"/>
+    </row>
+    <row r="470" spans="3:12">
+      <c r="C470" s="14"/>
+      <c r="D470" s="14"/>
+      <c r="E470" s="14"/>
+      <c r="F470" s="14"/>
+      <c r="G470" s="14"/>
+      <c r="H470" s="14"/>
+      <c r="I470" s="14"/>
+      <c r="J470" s="14"/>
+      <c r="K470" s="14"/>
+      <c r="L470" s="14"/>
+    </row>
+    <row r="471" spans="3:12">
+      <c r="C471" s="14"/>
+      <c r="D471" s="14"/>
+      <c r="E471" s="14"/>
+      <c r="F471" s="14"/>
+      <c r="G471" s="14"/>
+      <c r="H471" s="14"/>
+      <c r="I471" s="14"/>
+      <c r="J471" s="14"/>
+      <c r="K471" s="14"/>
+      <c r="L471" s="14"/>
+    </row>
+    <row r="472" spans="3:12">
+      <c r="C472" s="14"/>
+      <c r="D472" s="14"/>
+      <c r="E472" s="14"/>
+      <c r="F472" s="14"/>
+      <c r="G472" s="14"/>
+      <c r="H472" s="14"/>
+      <c r="I472" s="14"/>
+      <c r="J472" s="14"/>
+      <c r="K472" s="14"/>
+      <c r="L472" s="14"/>
+    </row>
+    <row r="473" spans="3:12">
+      <c r="C473" s="14"/>
+      <c r="D473" s="14"/>
+      <c r="E473" s="14"/>
+      <c r="F473" s="14"/>
+      <c r="G473" s="14"/>
+      <c r="H473" s="14"/>
+      <c r="I473" s="14"/>
+      <c r="J473" s="14"/>
+      <c r="K473" s="14"/>
+      <c r="L473" s="14"/>
+    </row>
+    <row r="474" spans="3:12">
+      <c r="C474" s="14"/>
+      <c r="D474" s="14"/>
+      <c r="E474" s="14"/>
+      <c r="F474" s="14"/>
+      <c r="G474" s="14"/>
+      <c r="H474" s="14"/>
+      <c r="I474" s="14"/>
+      <c r="J474" s="14"/>
+      <c r="K474" s="14"/>
+      <c r="L474" s="14"/>
+    </row>
+    <row r="475" spans="3:12">
+      <c r="C475" s="14"/>
+      <c r="D475" s="14"/>
+      <c r="E475" s="14"/>
+      <c r="F475" s="14"/>
+      <c r="G475" s="14"/>
+      <c r="H475" s="14"/>
+      <c r="I475" s="14"/>
+      <c r="J475" s="14"/>
+      <c r="K475" s="14"/>
+      <c r="L475" s="14"/>
+    </row>
+    <row r="476" spans="3:12">
+      <c r="C476" s="14"/>
+      <c r="D476" s="14"/>
+      <c r="E476" s="14"/>
+      <c r="F476" s="14"/>
+      <c r="G476" s="14"/>
+      <c r="H476" s="14"/>
+      <c r="I476" s="14"/>
+      <c r="J476" s="14"/>
+      <c r="K476" s="14"/>
+      <c r="L476" s="14"/>
+    </row>
+    <row r="477" spans="3:12">
+      <c r="C477" s="14"/>
+      <c r="D477" s="14"/>
+      <c r="E477" s="14"/>
+      <c r="F477" s="14"/>
+      <c r="G477" s="14"/>
+      <c r="H477" s="14"/>
+      <c r="I477" s="14"/>
+      <c r="J477" s="14"/>
+      <c r="K477" s="14"/>
+      <c r="L477" s="14"/>
+    </row>
+    <row r="478" spans="3:12">
+      <c r="C478" s="14"/>
+      <c r="D478" s="14"/>
+      <c r="E478" s="14"/>
+      <c r="F478" s="14"/>
+      <c r="G478" s="14"/>
+      <c r="H478" s="14"/>
+      <c r="I478" s="14"/>
+      <c r="J478" s="14"/>
+      <c r="K478" s="14"/>
+      <c r="L478" s="14"/>
+    </row>
+    <row r="479" spans="3:12">
+      <c r="C479" s="14"/>
+      <c r="D479" s="14"/>
+      <c r="E479" s="14"/>
+      <c r="F479" s="14"/>
+      <c r="G479" s="14"/>
+      <c r="H479" s="14"/>
+      <c r="I479" s="14"/>
+      <c r="J479" s="14"/>
+      <c r="K479" s="14"/>
+      <c r="L479" s="14"/>
+    </row>
+    <row r="480" spans="3:12">
+      <c r="C480" s="14"/>
+      <c r="D480" s="14"/>
+      <c r="E480" s="14"/>
+      <c r="F480" s="14"/>
+      <c r="G480" s="14"/>
+      <c r="H480" s="14"/>
+      <c r="I480" s="14"/>
+      <c r="J480" s="14"/>
+      <c r="K480" s="14"/>
+      <c r="L480" s="14"/>
+    </row>
+    <row r="481" spans="3:12">
+      <c r="C481" s="14"/>
+      <c r="D481" s="14"/>
+      <c r="E481" s="14"/>
+      <c r="F481" s="14"/>
+      <c r="G481" s="14"/>
+      <c r="H481" s="14"/>
+      <c r="I481" s="14"/>
+      <c r="J481" s="14"/>
+      <c r="K481" s="14"/>
+      <c r="L481" s="14"/>
+    </row>
+    <row r="482" spans="3:12">
+      <c r="C482" s="14"/>
+      <c r="D482" s="14"/>
+      <c r="E482" s="14"/>
+      <c r="F482" s="14"/>
+      <c r="G482" s="14"/>
+      <c r="H482" s="14"/>
+      <c r="I482" s="14"/>
+      <c r="J482" s="14"/>
+      <c r="K482" s="14"/>
+      <c r="L482" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
